--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,114 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks FC</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medell</t>
+  </si>
+  <si>
+    <t>Sacramento Republic</t>
+  </si>
+  <si>
+    <t>Azerbaijan</t>
+  </si>
+  <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Malta</t>
+  </si>
+  <si>
+    <t>Republic of Ireland</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>Envigado</t>
+  </si>
+  <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
+    <t>Junior FC Barranquilla</t>
+  </si>
+  <si>
+    <t>Las Vegas Lights FC</t>
+  </si>
+  <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Gibraltar</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Orsomarso</t>
+  </si>
+  <si>
+    <t>2026-09-29 01:21:48</t>
   </si>
 </sst>
 </file>
@@ -585,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +936,2910 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2">
+        <v>1.96</v>
+      </c>
+      <c r="G2">
+        <v>2.12</v>
+      </c>
+      <c r="H2">
+        <v>3.7</v>
+      </c>
+      <c r="I2">
+        <v>4.3</v>
+      </c>
+      <c r="J2">
+        <v>3.85</v>
+      </c>
+      <c r="K2">
+        <v>4.2</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.05</v>
+      </c>
+      <c r="N2">
+        <v>4.2</v>
+      </c>
+      <c r="O2">
+        <v>1.26</v>
+      </c>
+      <c r="P2">
+        <v>2.1</v>
+      </c>
+      <c r="Q2">
+        <v>1.75</v>
+      </c>
+      <c r="R2">
+        <v>1.42</v>
+      </c>
+      <c r="S2">
+        <v>2.92</v>
+      </c>
+      <c r="T2">
+        <v>1.71</v>
+      </c>
+      <c r="U2">
+        <v>2.24</v>
+      </c>
+      <c r="V2">
+        <v>1.31</v>
+      </c>
+      <c r="W2">
+        <v>1.9</v>
+      </c>
+      <c r="X2">
+        <v>20</v>
+      </c>
+      <c r="Y2">
+        <v>19</v>
+      </c>
+      <c r="Z2">
+        <v>36</v>
+      </c>
+      <c r="AA2">
+        <v>90</v>
+      </c>
+      <c r="AB2">
+        <v>12.5</v>
+      </c>
+      <c r="AC2">
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
+        <v>19</v>
+      </c>
+      <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
+        <v>16</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
+        <v>20</v>
+      </c>
+      <c r="AI2">
+        <v>55</v>
+      </c>
+      <c r="AJ2">
+        <v>28</v>
+      </c>
+      <c r="AK2">
+        <v>24</v>
+      </c>
+      <c r="AL2">
+        <v>38</v>
+      </c>
+      <c r="AM2">
+        <v>90</v>
+      </c>
+      <c r="AN2">
+        <v>14.5</v>
+      </c>
+      <c r="AO2">
+        <v>44</v>
+      </c>
+      <c r="AP2">
+        <v>15</v>
+      </c>
+      <c r="AQ2">
+        <v>13.5</v>
+      </c>
+      <c r="AR2">
+        <v>22</v>
+      </c>
+      <c r="AS2">
+        <v>55</v>
+      </c>
+      <c r="AT2">
+        <v>9.4</v>
+      </c>
+      <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>13.5</v>
+      </c>
+      <c r="AW2">
+        <v>34</v>
+      </c>
+      <c r="AX2">
+        <v>12</v>
+      </c>
+      <c r="AY2">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>36</v>
+      </c>
+      <c r="BB2">
+        <v>18.5</v>
+      </c>
+      <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
+        <v>24</v>
+      </c>
+      <c r="BE2">
+        <v>55</v>
+      </c>
+      <c r="BF2">
+        <v>10.5</v>
+      </c>
+      <c r="BG2">
+        <v>29</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.96</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3">
+        <v>1.55</v>
+      </c>
+      <c r="G3">
+        <v>1.61</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
+      </c>
+      <c r="I3">
+        <v>7.4</v>
+      </c>
+      <c r="J3">
+        <v>4.3</v>
+      </c>
+      <c r="K3">
+        <v>4.8</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>4.7</v>
+      </c>
+      <c r="O3">
+        <v>1.23</v>
+      </c>
+      <c r="P3">
+        <v>2.28</v>
+      </c>
+      <c r="Q3">
+        <v>1.71</v>
+      </c>
+      <c r="R3">
+        <v>1.51</v>
+      </c>
+      <c r="S3">
+        <v>2.78</v>
+      </c>
+      <c r="T3">
+        <v>1.81</v>
+      </c>
+      <c r="U3">
+        <v>2.14</v>
+      </c>
+      <c r="V3">
+        <v>1.16</v>
+      </c>
+      <c r="W3">
+        <v>2.64</v>
+      </c>
+      <c r="X3">
+        <v>24</v>
+      </c>
+      <c r="Y3">
+        <v>32</v>
+      </c>
+      <c r="Z3">
+        <v>75</v>
+      </c>
+      <c r="AA3">
+        <v>230</v>
+      </c>
+      <c r="AB3">
+        <v>10.5</v>
+      </c>
+      <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>32</v>
+      </c>
+      <c r="AE3">
+        <v>120</v>
+      </c>
+      <c r="AF3">
+        <v>11</v>
+      </c>
+      <c r="AG3">
+        <v>10.5</v>
+      </c>
+      <c r="AH3">
+        <v>21</v>
+      </c>
+      <c r="AI3">
+        <v>95</v>
+      </c>
+      <c r="AJ3">
+        <v>17.5</v>
+      </c>
+      <c r="AK3">
+        <v>16.5</v>
+      </c>
+      <c r="AL3">
+        <v>34</v>
+      </c>
+      <c r="AM3">
+        <v>120</v>
+      </c>
+      <c r="AN3">
+        <v>7.6</v>
+      </c>
+      <c r="AO3">
+        <v>120</v>
+      </c>
+      <c r="AP3">
+        <v>17</v>
+      </c>
+      <c r="AQ3">
+        <v>21</v>
+      </c>
+      <c r="AR3">
+        <v>6.4</v>
+      </c>
+      <c r="AS3">
+        <v>6.2</v>
+      </c>
+      <c r="AT3">
+        <v>9</v>
+      </c>
+      <c r="AU3">
+        <v>8.6</v>
+      </c>
+      <c r="AV3">
+        <v>21</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY3">
+        <v>9</v>
+      </c>
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>13</v>
+      </c>
+      <c r="BC3">
+        <v>13.5</v>
+      </c>
+      <c r="BD3">
+        <v>7</v>
+      </c>
+      <c r="BE3">
+        <v>6.6</v>
+      </c>
+      <c r="BF3">
+        <v>6.4</v>
+      </c>
+      <c r="BG3">
+        <v>6.6</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4">
+        <v>1.65</v>
+      </c>
+      <c r="G4">
+        <v>1.79</v>
+      </c>
+      <c r="H4">
+        <v>5.3</v>
+      </c>
+      <c r="I4">
+        <v>6.6</v>
+      </c>
+      <c r="J4">
+        <v>3.8</v>
+      </c>
+      <c r="K4">
+        <v>4.3</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.07</v>
+      </c>
+      <c r="N4">
+        <v>3.15</v>
+      </c>
+      <c r="O4">
+        <v>1.34</v>
+      </c>
+      <c r="P4">
+        <v>1.82</v>
+      </c>
+      <c r="Q4">
+        <v>2.04</v>
+      </c>
+      <c r="R4">
+        <v>1.28</v>
+      </c>
+      <c r="S4">
+        <v>3.25</v>
+      </c>
+      <c r="T4">
+        <v>1.91</v>
+      </c>
+      <c r="U4">
+        <v>1.79</v>
+      </c>
+      <c r="V4">
+        <v>1.18</v>
+      </c>
+      <c r="W4">
+        <v>2.26</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>11</v>
+      </c>
+      <c r="AC4">
+        <v>15</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>15</v>
+      </c>
+      <c r="AG4">
+        <v>18</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>9</v>
+      </c>
+      <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>5.8</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>6.6</v>
+      </c>
+      <c r="AY4">
+        <v>7.2</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>10.5</v>
+      </c>
+      <c r="BC4">
+        <v>11</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>7.6</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>2.78</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5">
+        <v>1.18</v>
+      </c>
+      <c r="G5">
+        <v>1.2</v>
+      </c>
+      <c r="H5">
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <v>28</v>
+      </c>
+      <c r="J5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K5">
+        <v>8.6</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>2.36</v>
+      </c>
+      <c r="Q5">
+        <v>1.66</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>2.92</v>
+      </c>
+      <c r="U5">
+        <v>1.45</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>26</v>
+      </c>
+      <c r="Y5">
+        <v>75</v>
+      </c>
+      <c r="Z5">
+        <v>380</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>21</v>
+      </c>
+      <c r="AD5">
+        <v>120</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>6.8</v>
+      </c>
+      <c r="AG5">
+        <v>15</v>
+      </c>
+      <c r="AH5">
+        <v>70</v>
+      </c>
+      <c r="AI5">
+        <v>530</v>
+      </c>
+      <c r="AJ5">
+        <v>8</v>
+      </c>
+      <c r="AK5">
+        <v>17</v>
+      </c>
+      <c r="AL5">
+        <v>75</v>
+      </c>
+      <c r="AM5">
+        <v>520</v>
+      </c>
+      <c r="AN5">
+        <v>4.2</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5">
+        <v>8</v>
+      </c>
+      <c r="AR5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS5">
+        <v>8.6</v>
+      </c>
+      <c r="AT5">
+        <v>7</v>
+      </c>
+      <c r="AU5">
+        <v>16</v>
+      </c>
+      <c r="AV5">
+        <v>8.4</v>
+      </c>
+      <c r="AW5">
+        <v>8.6</v>
+      </c>
+      <c r="AX5">
+        <v>5.6</v>
+      </c>
+      <c r="AY5">
+        <v>12</v>
+      </c>
+      <c r="AZ5">
+        <v>8</v>
+      </c>
+      <c r="BA5">
+        <v>8.6</v>
+      </c>
+      <c r="BB5">
+        <v>6.6</v>
+      </c>
+      <c r="BC5">
+        <v>14</v>
+      </c>
+      <c r="BD5">
+        <v>8</v>
+      </c>
+      <c r="BE5">
+        <v>8.6</v>
+      </c>
+      <c r="BF5">
+        <v>3.6</v>
+      </c>
+      <c r="BG5">
+        <v>8.6</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6">
+        <v>6.4</v>
+      </c>
+      <c r="G6">
+        <v>6.6</v>
+      </c>
+      <c r="H6">
+        <v>1.57</v>
+      </c>
+      <c r="I6">
+        <v>1.58</v>
+      </c>
+      <c r="J6">
+        <v>4.7</v>
+      </c>
+      <c r="K6">
+        <v>4.9</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1.04</v>
+      </c>
+      <c r="N6">
+        <v>5.2</v>
+      </c>
+      <c r="O6">
+        <v>1.21</v>
+      </c>
+      <c r="P6">
+        <v>2.4</v>
+      </c>
+      <c r="Q6">
+        <v>1.66</v>
+      </c>
+      <c r="R6">
+        <v>1.58</v>
+      </c>
+      <c r="S6">
+        <v>2.6</v>
+      </c>
+      <c r="T6">
+        <v>1.77</v>
+      </c>
+      <c r="U6">
+        <v>2.22</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>24</v>
+      </c>
+      <c r="Y6">
+        <v>11</v>
+      </c>
+      <c r="Z6">
+        <v>10.5</v>
+      </c>
+      <c r="AA6">
+        <v>15.5</v>
+      </c>
+      <c r="AB6">
+        <v>32</v>
+      </c>
+      <c r="AC6">
+        <v>10.5</v>
+      </c>
+      <c r="AD6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE6">
+        <v>15.5</v>
+      </c>
+      <c r="AF6">
+        <v>60</v>
+      </c>
+      <c r="AG6">
+        <v>25</v>
+      </c>
+      <c r="AH6">
+        <v>23</v>
+      </c>
+      <c r="AI6">
+        <v>34</v>
+      </c>
+      <c r="AJ6">
+        <v>170</v>
+      </c>
+      <c r="AK6">
+        <v>85</v>
+      </c>
+      <c r="AL6">
+        <v>75</v>
+      </c>
+      <c r="AM6">
+        <v>95</v>
+      </c>
+      <c r="AN6">
+        <v>80</v>
+      </c>
+      <c r="AO6">
+        <v>6.6</v>
+      </c>
+      <c r="AP6">
+        <v>19</v>
+      </c>
+      <c r="AQ6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS6">
+        <v>13.5</v>
+      </c>
+      <c r="AT6">
+        <v>20</v>
+      </c>
+      <c r="AU6">
+        <v>9.4</v>
+      </c>
+      <c r="AV6">
+        <v>9.4</v>
+      </c>
+      <c r="AW6">
+        <v>13.5</v>
+      </c>
+      <c r="AX6">
+        <v>11</v>
+      </c>
+      <c r="AY6">
+        <v>21</v>
+      </c>
+      <c r="AZ6">
+        <v>17.5</v>
+      </c>
+      <c r="BA6">
+        <v>20</v>
+      </c>
+      <c r="BB6">
+        <v>12.5</v>
+      </c>
+      <c r="BC6">
+        <v>11.5</v>
+      </c>
+      <c r="BD6">
+        <v>11.5</v>
+      </c>
+      <c r="BE6">
+        <v>11.5</v>
+      </c>
+      <c r="BF6">
+        <v>11.5</v>
+      </c>
+      <c r="BG6">
+        <v>6</v>
+      </c>
+      <c r="BH6">
+        <v>4.6</v>
+      </c>
+      <c r="BI6">
+        <v>3.35</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>7</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>6.8</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>5</v>
+      </c>
+      <c r="BU6">
+        <v>3.55</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>7</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7">
+        <v>1.29</v>
+      </c>
+      <c r="G7">
+        <v>1.3</v>
+      </c>
+      <c r="H7">
+        <v>12.5</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>6.6</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1.03</v>
+      </c>
+      <c r="N7">
+        <v>6.8</v>
+      </c>
+      <c r="O7">
+        <v>1.15</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>1.46</v>
+      </c>
+      <c r="R7">
+        <v>1.81</v>
+      </c>
+      <c r="S7">
+        <v>2.14</v>
+      </c>
+      <c r="T7">
+        <v>1.95</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>36</v>
+      </c>
+      <c r="Y7">
+        <v>50</v>
+      </c>
+      <c r="Z7">
+        <v>140</v>
+      </c>
+      <c r="AA7">
+        <v>520</v>
+      </c>
+      <c r="AB7">
+        <v>12.5</v>
+      </c>
+      <c r="AC7">
+        <v>16</v>
+      </c>
+      <c r="AD7">
+        <v>46</v>
+      </c>
+      <c r="AE7">
+        <v>200</v>
+      </c>
+      <c r="AF7">
+        <v>9.6</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>29</v>
+      </c>
+      <c r="AI7">
+        <v>150</v>
+      </c>
+      <c r="AJ7">
+        <v>11</v>
+      </c>
+      <c r="AK7">
+        <v>14</v>
+      </c>
+      <c r="AL7">
+        <v>34</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>3.75</v>
+      </c>
+      <c r="AO7">
+        <v>200</v>
+      </c>
+      <c r="AP7">
+        <v>9.6</v>
+      </c>
+      <c r="AQ7">
+        <v>38</v>
+      </c>
+      <c r="AR7">
+        <v>12</v>
+      </c>
+      <c r="AS7">
+        <v>12.5</v>
+      </c>
+      <c r="AT7">
+        <v>11</v>
+      </c>
+      <c r="AU7">
+        <v>13.5</v>
+      </c>
+      <c r="AV7">
+        <v>32</v>
+      </c>
+      <c r="AW7">
+        <v>12</v>
+      </c>
+      <c r="AX7">
+        <v>8.4</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>12</v>
+      </c>
+      <c r="BB7">
+        <v>9.4</v>
+      </c>
+      <c r="BC7">
+        <v>11.5</v>
+      </c>
+      <c r="BD7">
+        <v>9.4</v>
+      </c>
+      <c r="BE7">
+        <v>12</v>
+      </c>
+      <c r="BF7">
+        <v>3.4</v>
+      </c>
+      <c r="BG7">
+        <v>12</v>
+      </c>
+      <c r="BH7">
+        <v>6.2</v>
+      </c>
+      <c r="BI7">
+        <v>4</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>8</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>4.6</v>
+      </c>
+      <c r="BO7">
+        <v>3.3</v>
+      </c>
+      <c r="BP7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ7">
+        <v>5.2</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>11.5</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8">
+        <v>3.35</v>
+      </c>
+      <c r="G8">
+        <v>3.4</v>
+      </c>
+      <c r="H8">
+        <v>2.38</v>
+      </c>
+      <c r="I8">
+        <v>2.4</v>
+      </c>
+      <c r="J8">
+        <v>3.45</v>
+      </c>
+      <c r="K8">
+        <v>3.55</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.89</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1.8</v>
+      </c>
+      <c r="U8">
+        <v>2.16</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>14.5</v>
+      </c>
+      <c r="Y8">
+        <v>10.5</v>
+      </c>
+      <c r="Z8">
+        <v>16</v>
+      </c>
+      <c r="AA8">
+        <v>34</v>
+      </c>
+      <c r="AB8">
+        <v>13.5</v>
+      </c>
+      <c r="AC8">
+        <v>8</v>
+      </c>
+      <c r="AD8">
+        <v>12</v>
+      </c>
+      <c r="AE8">
+        <v>27</v>
+      </c>
+      <c r="AF8">
+        <v>25</v>
+      </c>
+      <c r="AG8">
+        <v>15</v>
+      </c>
+      <c r="AH8">
+        <v>18</v>
+      </c>
+      <c r="AI8">
+        <v>40</v>
+      </c>
+      <c r="AJ8">
+        <v>65</v>
+      </c>
+      <c r="AK8">
+        <v>42</v>
+      </c>
+      <c r="AL8">
+        <v>55</v>
+      </c>
+      <c r="AM8">
+        <v>110</v>
+      </c>
+      <c r="AN8">
+        <v>40</v>
+      </c>
+      <c r="AO8">
+        <v>21</v>
+      </c>
+      <c r="AP8">
+        <v>12</v>
+      </c>
+      <c r="AQ8">
+        <v>9</v>
+      </c>
+      <c r="AR8">
+        <v>13</v>
+      </c>
+      <c r="AS8">
+        <v>7.8</v>
+      </c>
+      <c r="AT8">
+        <v>11.5</v>
+      </c>
+      <c r="AU8">
+        <v>7</v>
+      </c>
+      <c r="AV8">
+        <v>10</v>
+      </c>
+      <c r="AW8">
+        <v>21</v>
+      </c>
+      <c r="AX8">
+        <v>20</v>
+      </c>
+      <c r="AY8">
+        <v>12.5</v>
+      </c>
+      <c r="AZ8">
+        <v>15</v>
+      </c>
+      <c r="BA8">
+        <v>8</v>
+      </c>
+      <c r="BB8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC8">
+        <v>32</v>
+      </c>
+      <c r="BD8">
+        <v>40</v>
+      </c>
+      <c r="BE8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8">
+        <v>30</v>
+      </c>
+      <c r="BG8">
+        <v>17.5</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>3.45</v>
+      </c>
+      <c r="G9">
+        <v>3.55</v>
+      </c>
+      <c r="H9">
+        <v>2.18</v>
+      </c>
+      <c r="I9">
+        <v>2.22</v>
+      </c>
+      <c r="J9">
+        <v>3.75</v>
+      </c>
+      <c r="K9">
+        <v>3.85</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1.05</v>
+      </c>
+      <c r="N9">
+        <v>4.6</v>
+      </c>
+      <c r="O9">
+        <v>1.25</v>
+      </c>
+      <c r="P9">
+        <v>2.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.78</v>
+      </c>
+      <c r="R9">
+        <v>1.49</v>
+      </c>
+      <c r="S9">
+        <v>2.9</v>
+      </c>
+      <c r="T9">
+        <v>1.67</v>
+      </c>
+      <c r="U9">
+        <v>2.4</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>19</v>
+      </c>
+      <c r="Y9">
+        <v>12.5</v>
+      </c>
+      <c r="Z9">
+        <v>15.5</v>
+      </c>
+      <c r="AA9">
+        <v>34</v>
+      </c>
+      <c r="AB9">
+        <v>18</v>
+      </c>
+      <c r="AC9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9">
+        <v>11</v>
+      </c>
+      <c r="AE9">
+        <v>22</v>
+      </c>
+      <c r="AF9">
+        <v>32</v>
+      </c>
+      <c r="AG9">
+        <v>14.5</v>
+      </c>
+      <c r="AH9">
+        <v>15.5</v>
+      </c>
+      <c r="AI9">
+        <v>36</v>
+      </c>
+      <c r="AJ9">
+        <v>70</v>
+      </c>
+      <c r="AK9">
+        <v>38</v>
+      </c>
+      <c r="AL9">
+        <v>55</v>
+      </c>
+      <c r="AM9">
+        <v>80</v>
+      </c>
+      <c r="AN9">
+        <v>36</v>
+      </c>
+      <c r="AO9">
+        <v>13</v>
+      </c>
+      <c r="AP9">
+        <v>16.5</v>
+      </c>
+      <c r="AQ9">
+        <v>10.5</v>
+      </c>
+      <c r="AR9">
+        <v>12.5</v>
+      </c>
+      <c r="AS9">
+        <v>9</v>
+      </c>
+      <c r="AT9">
+        <v>14</v>
+      </c>
+      <c r="AU9">
+        <v>7.8</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>18.5</v>
+      </c>
+      <c r="AX9">
+        <v>19.5</v>
+      </c>
+      <c r="AY9">
+        <v>13</v>
+      </c>
+      <c r="AZ9">
+        <v>14</v>
+      </c>
+      <c r="BA9">
+        <v>9</v>
+      </c>
+      <c r="BB9">
+        <v>10.5</v>
+      </c>
+      <c r="BC9">
+        <v>9.4</v>
+      </c>
+      <c r="BD9">
+        <v>9.6</v>
+      </c>
+      <c r="BE9">
+        <v>10.5</v>
+      </c>
+      <c r="BF9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG9">
+        <v>11.5</v>
+      </c>
+      <c r="BH9">
+        <v>4.3</v>
+      </c>
+      <c r="BI9">
+        <v>3.15</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>6.4</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>9.4</v>
+      </c>
+      <c r="BO9">
+        <v>5.3</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>6.4</v>
+      </c>
+      <c r="BU9">
+        <v>4.1</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>9.4</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10">
+        <v>1.3</v>
+      </c>
+      <c r="G10">
+        <v>1.33</v>
+      </c>
+      <c r="H10">
+        <v>15</v>
+      </c>
+      <c r="I10">
+        <v>19</v>
+      </c>
+      <c r="J10">
+        <v>5.2</v>
+      </c>
+      <c r="K10">
+        <v>5.8</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.74</v>
+      </c>
+      <c r="Q10">
+        <v>2.06</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>2.82</v>
+      </c>
+      <c r="U10">
+        <v>1.47</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>14.5</v>
+      </c>
+      <c r="Y10">
+        <v>36</v>
+      </c>
+      <c r="Z10">
+        <v>210</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>6.2</v>
+      </c>
+      <c r="AC10">
+        <v>14</v>
+      </c>
+      <c r="AD10">
+        <v>85</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>6.4</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>60</v>
+      </c>
+      <c r="AI10">
+        <v>450</v>
+      </c>
+      <c r="AJ10">
+        <v>9.6</v>
+      </c>
+      <c r="AK10">
+        <v>19.5</v>
+      </c>
+      <c r="AL10">
+        <v>95</v>
+      </c>
+      <c r="AM10">
+        <v>560</v>
+      </c>
+      <c r="AN10">
+        <v>7.6</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR10">
+        <v>9.6</v>
+      </c>
+      <c r="AS10">
+        <v>10</v>
+      </c>
+      <c r="AT10">
+        <v>5.2</v>
+      </c>
+      <c r="AU10">
+        <v>11.5</v>
+      </c>
+      <c r="AV10">
+        <v>9.4</v>
+      </c>
+      <c r="AW10">
+        <v>10</v>
+      </c>
+      <c r="AX10">
+        <v>5.4</v>
+      </c>
+      <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
+        <v>9</v>
+      </c>
+      <c r="BA10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB10">
+        <v>7.8</v>
+      </c>
+      <c r="BC10">
+        <v>16</v>
+      </c>
+      <c r="BD10">
+        <v>9</v>
+      </c>
+      <c r="BE10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF10">
+        <v>6.4</v>
+      </c>
+      <c r="BG10">
+        <v>10</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11">
+        <v>3.7</v>
+      </c>
+      <c r="G11">
+        <v>3.8</v>
+      </c>
+      <c r="H11">
+        <v>2.26</v>
+      </c>
+      <c r="I11">
+        <v>2.3</v>
+      </c>
+      <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
+        <v>3.45</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.09</v>
+      </c>
+      <c r="N11">
+        <v>3.2</v>
+      </c>
+      <c r="O11">
+        <v>1.42</v>
+      </c>
+      <c r="P11">
+        <v>1.73</v>
+      </c>
+      <c r="Q11">
+        <v>2.3</v>
+      </c>
+      <c r="R11">
+        <v>1.27</v>
+      </c>
+      <c r="S11">
+        <v>4.4</v>
+      </c>
+      <c r="T11">
+        <v>1.99</v>
+      </c>
+      <c r="U11">
+        <v>1.95</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>12</v>
+      </c>
+      <c r="Y11">
+        <v>9</v>
+      </c>
+      <c r="Z11">
+        <v>13.5</v>
+      </c>
+      <c r="AA11">
+        <v>32</v>
+      </c>
+      <c r="AB11">
+        <v>12</v>
+      </c>
+      <c r="AC11">
+        <v>7.8</v>
+      </c>
+      <c r="AD11">
+        <v>11.5</v>
+      </c>
+      <c r="AE11">
+        <v>30</v>
+      </c>
+      <c r="AF11">
+        <v>27</v>
+      </c>
+      <c r="AG11">
+        <v>16</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
+        <v>55</v>
+      </c>
+      <c r="AJ11">
+        <v>90</v>
+      </c>
+      <c r="AK11">
+        <v>70</v>
+      </c>
+      <c r="AL11">
+        <v>75</v>
+      </c>
+      <c r="AM11">
+        <v>170</v>
+      </c>
+      <c r="AN11">
+        <v>75</v>
+      </c>
+      <c r="AO11">
+        <v>26</v>
+      </c>
+      <c r="AP11">
+        <v>10</v>
+      </c>
+      <c r="AQ11">
+        <v>7.6</v>
+      </c>
+      <c r="AR11">
+        <v>11</v>
+      </c>
+      <c r="AS11">
+        <v>21</v>
+      </c>
+      <c r="AT11">
+        <v>10</v>
+      </c>
+      <c r="AU11">
+        <v>6.6</v>
+      </c>
+      <c r="AV11">
+        <v>10</v>
+      </c>
+      <c r="AW11">
+        <v>20</v>
+      </c>
+      <c r="AX11">
+        <v>20</v>
+      </c>
+      <c r="AY11">
+        <v>13.5</v>
+      </c>
+      <c r="AZ11">
+        <v>17.5</v>
+      </c>
+      <c r="BA11">
+        <v>38</v>
+      </c>
+      <c r="BB11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC11">
+        <v>38</v>
+      </c>
+      <c r="BD11">
+        <v>8.6</v>
+      </c>
+      <c r="BE11">
+        <v>9.4</v>
+      </c>
+      <c r="BF11">
+        <v>46</v>
+      </c>
+      <c r="BG11">
+        <v>18</v>
+      </c>
+      <c r="BH11">
+        <v>3.25</v>
+      </c>
+      <c r="BI11">
+        <v>2.56</v>
+      </c>
+      <c r="BJ11">
+        <v>18</v>
+      </c>
+      <c r="BK11">
+        <v>7.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>9</v>
+      </c>
+      <c r="BO11">
+        <v>5.2</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>5.9</v>
+      </c>
+      <c r="BU11">
+        <v>3.95</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>10.5</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12">
+        <v>3.4</v>
+      </c>
+      <c r="G12">
+        <v>3.5</v>
+      </c>
+      <c r="H12">
+        <v>2.28</v>
+      </c>
+      <c r="I12">
+        <v>2.3</v>
+      </c>
+      <c r="J12">
+        <v>3.65</v>
+      </c>
+      <c r="K12">
+        <v>3.7</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1.06</v>
+      </c>
+      <c r="N12">
+        <v>4.3</v>
+      </c>
+      <c r="O12">
+        <v>1.28</v>
+      </c>
+      <c r="P12">
+        <v>2.14</v>
+      </c>
+      <c r="Q12">
+        <v>1.84</v>
+      </c>
+      <c r="R12">
+        <v>1.44</v>
+      </c>
+      <c r="S12">
+        <v>3.05</v>
+      </c>
+      <c r="T12">
+        <v>1.7</v>
+      </c>
+      <c r="U12">
+        <v>2.34</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>16.5</v>
+      </c>
+      <c r="Y12">
+        <v>11.5</v>
+      </c>
+      <c r="Z12">
+        <v>15.5</v>
+      </c>
+      <c r="AA12">
+        <v>29</v>
+      </c>
+      <c r="AB12">
+        <v>15</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>23</v>
+      </c>
+      <c r="AF12">
+        <v>26</v>
+      </c>
+      <c r="AG12">
+        <v>14.5</v>
+      </c>
+      <c r="AH12">
+        <v>16</v>
+      </c>
+      <c r="AI12">
+        <v>34</v>
+      </c>
+      <c r="AJ12">
+        <v>60</v>
+      </c>
+      <c r="AK12">
+        <v>38</v>
+      </c>
+      <c r="AL12">
+        <v>44</v>
+      </c>
+      <c r="AM12">
+        <v>85</v>
+      </c>
+      <c r="AN12">
+        <v>34</v>
+      </c>
+      <c r="AO12">
+        <v>15</v>
+      </c>
+      <c r="AP12">
+        <v>15</v>
+      </c>
+      <c r="AQ12">
+        <v>10</v>
+      </c>
+      <c r="AR12">
+        <v>13.5</v>
+      </c>
+      <c r="AS12">
+        <v>24</v>
+      </c>
+      <c r="AT12">
+        <v>13.5</v>
+      </c>
+      <c r="AU12">
+        <v>7.6</v>
+      </c>
+      <c r="AV12">
+        <v>10</v>
+      </c>
+      <c r="AW12">
+        <v>20</v>
+      </c>
+      <c r="AX12">
+        <v>19</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
+        <v>14</v>
+      </c>
+      <c r="BA12">
+        <v>28</v>
+      </c>
+      <c r="BB12">
+        <v>42</v>
+      </c>
+      <c r="BC12">
+        <v>32</v>
+      </c>
+      <c r="BD12">
+        <v>38</v>
+      </c>
+      <c r="BE12">
+        <v>14</v>
+      </c>
+      <c r="BF12">
+        <v>28</v>
+      </c>
+      <c r="BG12">
+        <v>13.5</v>
+      </c>
+      <c r="BH12">
+        <v>4.1</v>
+      </c>
+      <c r="BI12">
+        <v>3</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>6.4</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>5.2</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>6.4</v>
+      </c>
+      <c r="BU12">
+        <v>4.2</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13">
+        <v>1.1</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13">
+        <v>1.1</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13">
+        <v>1.1</v>
+      </c>
+      <c r="K13">
+        <v>1000</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.24</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 01:21:48</t>
+    <t>2026-09-29 03:32:40</t>
   </si>
 </sst>
 </file>
@@ -955,10 +955,10 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H2">
         <v>3.7</v>
@@ -988,7 +988,7 @@
         <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R2">
         <v>1.42</v>
@@ -997,7 +997,7 @@
         <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U2">
         <v>2.24</v>
@@ -1120,7 +1120,7 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1200,7 +1200,7 @@
         <v>1.55</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -1209,10 +1209,10 @@
         <v>7.4</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1221,34 +1221,34 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U3">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X3">
         <v>24</v>
@@ -1275,7 +1275,7 @@
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
@@ -1287,7 +1287,7 @@
         <v>95</v>
       </c>
       <c r="AJ3">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK3">
         <v>16.5</v>
@@ -1305,7 +1305,7 @@
         <v>120</v>
       </c>
       <c r="AP3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
         <v>21</v>
@@ -1314,19 +1314,19 @@
         <v>6.4</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>9</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV3">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1335,19 +1335,19 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
         <v>13</v>
       </c>
       <c r="BC3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE3">
         <v>6.6</v>
@@ -1445,7 +1445,7 @@
         <v>1.79</v>
       </c>
       <c r="H4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
         <v>6.6</v>
@@ -1463,28 +1463,28 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.18</v>
@@ -1493,112 +1493,112 @@
         <v>2.26</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4">
         <v>11</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
+        <v>28</v>
+      </c>
+      <c r="AE4">
+        <v>110</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>28</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>23</v>
+      </c>
+      <c r="AK4">
+        <v>24</v>
+      </c>
+      <c r="AL4">
+        <v>48</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
         <v>15</v>
       </c>
-      <c r="AD4">
-        <v>1000</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>15</v>
-      </c>
-      <c r="AG4">
-        <v>18</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AX4">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY4">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB4">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BF4">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1690,10 +1690,10 @@
         <v>23</v>
       </c>
       <c r="I5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>8.6</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>26</v>
       </c>
       <c r="Y5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z5">
         <v>380</v>
@@ -1747,7 +1747,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
         <v>21</v>
@@ -1792,25 +1792,25 @@
         <v>16.5</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
+        <v>8.6</v>
+      </c>
+      <c r="AS5">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AS5">
-        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>7</v>
       </c>
       <c r="AU5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AV5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
         <v>5.6</v>
@@ -1819,19 +1819,19 @@
         <v>12</v>
       </c>
       <c r="AZ5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BA5">
         <v>8.6</v>
       </c>
       <c r="BB5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
         <v>8.6</v>
@@ -1840,7 +1840,7 @@
         <v>3.6</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>6.4</v>
       </c>
       <c r="G6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H6">
+        <v>1.56</v>
+      </c>
+      <c r="I6">
         <v>1.57</v>
-      </c>
-      <c r="I6">
-        <v>1.58</v>
       </c>
       <c r="J6">
         <v>4.7</v>
@@ -1947,13 +1947,13 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
         <v>1.66</v>
@@ -1962,7 +1962,7 @@
         <v>1.58</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T6">
         <v>1.77</v>
@@ -1989,7 +1989,7 @@
         <v>15.5</v>
       </c>
       <c r="AB6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="AU6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV6">
         <v>9.4</v>
@@ -2055,7 +2055,7 @@
         <v>13.5</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY6">
         <v>21</v>
@@ -2067,22 +2067,22 @@
         <v>20</v>
       </c>
       <c r="BB6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH6">
         <v>4.6</v>
@@ -2174,7 +2174,7 @@
         <v>12.5</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J7">
         <v>6.6</v>
@@ -2207,7 +2207,7 @@
         <v>2.14</v>
       </c>
       <c r="T7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -2291,7 +2291,7 @@
         <v>13.5</v>
       </c>
       <c r="AV7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AW7">
         <v>12</v>
@@ -2327,7 +2327,7 @@
         <v>12</v>
       </c>
       <c r="BH7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI7">
         <v>4</v>
@@ -2336,7 +2336,7 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2345,13 +2345,13 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ7">
         <v>5.2</v>
@@ -2467,7 +2467,7 @@
         <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>34</v>
@@ -2524,7 +2524,7 @@
         <v>13</v>
       </c>
       <c r="AS8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT8">
         <v>11.5</v>
@@ -2548,10 +2548,10 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC8">
         <v>32</v>
@@ -2560,7 +2560,7 @@
         <v>40</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8">
         <v>30</v>
@@ -2649,7 +2649,7 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G9">
         <v>3.55</v>
@@ -2658,7 +2658,7 @@
         <v>2.18</v>
       </c>
       <c r="I9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J9">
         <v>3.75</v>
@@ -2688,7 +2688,7 @@
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
         <v>1.67</v>
@@ -2712,7 +2712,7 @@
         <v>15.5</v>
       </c>
       <c r="AA9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB9">
         <v>18</v>
@@ -2733,7 +2733,7 @@
         <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI9">
         <v>36</v>
@@ -2745,19 +2745,19 @@
         <v>38</v>
       </c>
       <c r="AL9">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM9">
         <v>80</v>
       </c>
       <c r="AN9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO9">
         <v>13</v>
       </c>
       <c r="AP9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
@@ -2766,7 +2766,7 @@
         <v>12.5</v>
       </c>
       <c r="AS9">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AT9">
         <v>14</v>
@@ -2790,16 +2790,16 @@
         <v>14</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9">
         <v>10.5</v>
       </c>
       <c r="BC9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD9">
         <v>9.4</v>
-      </c>
-      <c r="BD9">
-        <v>9.6</v>
       </c>
       <c r="BE9">
         <v>10.5</v>
@@ -2811,64 +2811,64 @@
         <v>11.5</v>
       </c>
       <c r="BH9">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK9">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN9">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BO9">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BU9">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2897,13 +2897,13 @@
         <v>1.33</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="I10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K10">
         <v>5.8</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
         <v>1.47</v>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z10">
         <v>210</v>
@@ -2957,13 +2957,13 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>14</v>
       </c>
       <c r="AD10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AE10">
         <v>1000</v>
@@ -2978,19 +2978,19 @@
         <v>60</v>
       </c>
       <c r="AI10">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AJ10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK10">
         <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM10">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
         <v>7.6</v>
@@ -3002,7 +3002,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR10">
         <v>9.6</v>
@@ -3011,13 +3011,13 @@
         <v>10</v>
       </c>
       <c r="AT10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU10">
         <v>11.5</v>
       </c>
       <c r="AV10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW10">
         <v>10</v>
@@ -3026,25 +3026,25 @@
         <v>5.4</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA10">
         <v>9.800000000000001</v>
       </c>
       <c r="BB10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD10">
         <v>9</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
@@ -3133,7 +3133,7 @@
         <v>112</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G11">
         <v>3.8</v>
@@ -3187,19 +3187,19 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
         <v>7.8</v>
@@ -3211,10 +3211,10 @@
         <v>30</v>
       </c>
       <c r="AF11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH11">
         <v>22</v>
@@ -3226,16 +3226,16 @@
         <v>90</v>
       </c>
       <c r="AK11">
+        <v>65</v>
+      </c>
+      <c r="AL11">
         <v>70</v>
       </c>
-      <c r="AL11">
-        <v>75</v>
-      </c>
       <c r="AM11">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO11">
         <v>26</v>
@@ -3253,7 +3253,7 @@
         <v>21</v>
       </c>
       <c r="AT11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
@@ -3265,94 +3265,94 @@
         <v>20</v>
       </c>
       <c r="AX11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY11">
         <v>13.5</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
         <v>38</v>
       </c>
       <c r="BB11">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC11">
         <v>38</v>
       </c>
       <c r="BD11">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF11">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG11">
         <v>18</v>
       </c>
       <c r="BH11">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BI11">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BO11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BT11">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BU11">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW11">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>
@@ -3414,7 +3414,7 @@
         <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T12">
         <v>1.7</v>
@@ -3429,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y12">
         <v>11.5</v>
@@ -3471,10 +3471,10 @@
         <v>38</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN12">
         <v>34</v>
@@ -3483,7 +3483,7 @@
         <v>15</v>
       </c>
       <c r="AP12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12">
         <v>10</v>
@@ -3528,7 +3528,7 @@
         <v>38</v>
       </c>
       <c r="BE12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF12">
         <v>28</v>
@@ -3540,7 +3540,7 @@
         <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 03:32:40</t>
+    <t>2026-09-29 05:48:08</t>
   </si>
 </sst>
 </file>
@@ -955,166 +955,166 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
         <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
         <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AW2">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
+        <v>9</v>
+      </c>
+      <c r="AY2">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2">
+        <v>11</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
         <v>12</v>
       </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>36</v>
-      </c>
-      <c r="BB2">
-        <v>18.5</v>
-      </c>
-      <c r="BC2">
-        <v>17.5</v>
-      </c>
       <c r="BD2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1200,19 +1200,19 @@
         <v>1.55</v>
       </c>
       <c r="G3">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1221,142 +1221,142 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AO3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>1.51</v>
       </c>
       <c r="AQ3">
-        <v>21</v>
+        <v>1.51</v>
       </c>
       <c r="AR3">
-        <v>6.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>1.51</v>
       </c>
       <c r="AT3">
-        <v>9</v>
+        <v>1.39</v>
       </c>
       <c r="AU3">
-        <v>9</v>
+        <v>1.38</v>
       </c>
       <c r="AV3">
-        <v>5.7</v>
+        <v>1.51</v>
       </c>
       <c r="AW3">
-        <v>7.6</v>
+        <v>1.51</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>1.39</v>
       </c>
       <c r="AZ3">
-        <v>6.2</v>
+        <v>1.51</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>1.51</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>1.51</v>
       </c>
       <c r="BC3">
-        <v>14</v>
+        <v>1.51</v>
       </c>
       <c r="BD3">
-        <v>7.2</v>
+        <v>1.51</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="BF3">
-        <v>6.4</v>
+        <v>1.31</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1439,22 +1439,22 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="G4">
         <v>1.79</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1463,148 +1463,148 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
         <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
         <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
         <v>2.26</v>
       </c>
       <c r="X4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
+        <v>11</v>
+      </c>
+      <c r="AC4">
+        <v>14.5</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>15</v>
+      </c>
+      <c r="AG4">
+        <v>17.5</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC4">
+      <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>5.7</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>6.6</v>
+      </c>
+      <c r="AY4">
+        <v>7.2</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>10.5</v>
+      </c>
+      <c r="BC4">
         <v>11</v>
       </c>
-      <c r="AD4">
-        <v>28</v>
-      </c>
-      <c r="AE4">
-        <v>110</v>
-      </c>
-      <c r="AF4">
-        <v>12</v>
-      </c>
-      <c r="AG4">
-        <v>12.5</v>
-      </c>
-      <c r="AH4">
-        <v>28</v>
-      </c>
-      <c r="AI4">
-        <v>110</v>
-      </c>
-      <c r="AJ4">
-        <v>23</v>
-      </c>
-      <c r="AK4">
-        <v>24</v>
-      </c>
-      <c r="AL4">
-        <v>48</v>
-      </c>
-      <c r="AM4">
-        <v>170</v>
-      </c>
-      <c r="AN4">
-        <v>15</v>
-      </c>
-      <c r="AO4">
-        <v>150</v>
-      </c>
-      <c r="AP4">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4">
-        <v>14.5</v>
-      </c>
-      <c r="AR4">
-        <v>32</v>
-      </c>
-      <c r="AS4">
-        <v>110</v>
-      </c>
-      <c r="AT4">
-        <v>6.6</v>
-      </c>
-      <c r="AU4">
-        <v>7.6</v>
-      </c>
-      <c r="AV4">
-        <v>16.5</v>
-      </c>
-      <c r="AW4">
-        <v>60</v>
-      </c>
-      <c r="AX4">
-        <v>8.4</v>
-      </c>
-      <c r="AY4">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4">
-        <v>16.5</v>
-      </c>
-      <c r="BA4">
-        <v>60</v>
-      </c>
-      <c r="BB4">
-        <v>15.5</v>
-      </c>
-      <c r="BC4">
-        <v>16.5</v>
-      </c>
       <c r="BD4">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -1687,22 +1687,22 @@
         <v>1.2</v>
       </c>
       <c r="H5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1735,112 +1735,112 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AC5">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
         <v>1000</v>
       </c>
       <c r="AF5">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>16.5</v>
+        <v>2.06</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>2.06</v>
       </c>
       <c r="AR5">
-        <v>8.6</v>
+        <v>2.06</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="AT5">
-        <v>7</v>
+        <v>1.76</v>
       </c>
       <c r="AU5">
-        <v>15.5</v>
+        <v>2.06</v>
       </c>
       <c r="AV5">
-        <v>8.199999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="AX5">
-        <v>5.6</v>
+        <v>1.65</v>
       </c>
       <c r="AY5">
-        <v>12</v>
+        <v>2.06</v>
       </c>
       <c r="AZ5">
-        <v>7.8</v>
+        <v>2.06</v>
       </c>
       <c r="BA5">
-        <v>8.6</v>
+        <v>2.06</v>
       </c>
       <c r="BB5">
-        <v>6.4</v>
+        <v>1.71</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>2.06</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>2.06</v>
       </c>
       <c r="BF5">
         <v>3.6</v>
       </c>
       <c r="BG5">
-        <v>8.4</v>
+        <v>2.06</v>
       </c>
       <c r="BH5">
         <v>0</v>
@@ -1923,22 +1923,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="G6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I6">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Q6">
         <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S6">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T6">
         <v>1.77</v>
@@ -1977,19 +1977,19 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="Z6">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AA6">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -1998,94 +1998,94 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE6">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="AF6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AP6">
-        <v>19</v>
+        <v>2.28</v>
       </c>
       <c r="AQ6">
+        <v>7.6</v>
+      </c>
+      <c r="AR6">
+        <v>7.2</v>
+      </c>
+      <c r="AS6">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS6">
-        <v>13.5</v>
-      </c>
       <c r="AT6">
-        <v>20</v>
+        <v>2.12</v>
       </c>
       <c r="AU6">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AW6">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX6">
+        <v>2.58</v>
+      </c>
+      <c r="AY6">
+        <v>2.1</v>
+      </c>
+      <c r="AZ6">
         <v>11.5</v>
       </c>
-      <c r="AY6">
-        <v>21</v>
-      </c>
-      <c r="AZ6">
-        <v>17.5</v>
-      </c>
       <c r="BA6">
-        <v>20</v>
+        <v>2.28</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>2.28</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>2.28</v>
       </c>
       <c r="BD6">
-        <v>12</v>
+        <v>2.28</v>
       </c>
       <c r="BE6">
-        <v>12</v>
+        <v>2.28</v>
       </c>
       <c r="BF6">
-        <v>12</v>
+        <v>2.58</v>
       </c>
       <c r="BG6">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI6">
         <v>3.35</v>
@@ -2174,10 +2174,10 @@
         <v>12.5</v>
       </c>
       <c r="I7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -2189,10 +2189,10 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P7">
         <v>3</v>
@@ -2201,10 +2201,10 @@
         <v>1.46</v>
       </c>
       <c r="R7">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T7">
         <v>1.94</v>
@@ -2219,112 +2219,112 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Z7">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
+        <v>23</v>
+      </c>
+      <c r="AC7">
+        <v>18.5</v>
+      </c>
+      <c r="AD7">
+        <v>70</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>11.5</v>
+      </c>
+      <c r="AG7">
+        <v>13</v>
+      </c>
+      <c r="AH7">
+        <v>40</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
         <v>12.5</v>
       </c>
-      <c r="AC7">
-        <v>16</v>
-      </c>
-      <c r="AD7">
-        <v>46</v>
-      </c>
-      <c r="AE7">
-        <v>200</v>
-      </c>
-      <c r="AF7">
-        <v>9.6</v>
-      </c>
-      <c r="AG7">
-        <v>12</v>
-      </c>
-      <c r="AH7">
-        <v>29</v>
-      </c>
-      <c r="AI7">
-        <v>150</v>
-      </c>
-      <c r="AJ7">
-        <v>11</v>
-      </c>
       <c r="AK7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL7">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AO7">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ7">
-        <v>38</v>
+        <v>3.25</v>
       </c>
       <c r="AR7">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="AS7">
+        <v>3.4</v>
+      </c>
+      <c r="AT7">
+        <v>8.6</v>
+      </c>
+      <c r="AU7">
         <v>12.5</v>
       </c>
-      <c r="AT7">
-        <v>11</v>
-      </c>
-      <c r="AU7">
-        <v>13.5</v>
-      </c>
       <c r="AV7">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="AW7">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="AX7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>3.1</v>
       </c>
       <c r="BA7">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="BB7">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD7">
-        <v>9.4</v>
+        <v>3.15</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="BF7">
+        <v>3.25</v>
+      </c>
+      <c r="BG7">
         <v>3.4</v>
-      </c>
-      <c r="BG7">
-        <v>12</v>
       </c>
       <c r="BH7">
         <v>6</v>
@@ -2407,7 +2407,7 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G8">
         <v>3.4</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2461,112 +2461,112 @@
         <v>0</v>
       </c>
       <c r="X8">
+        <v>17</v>
+      </c>
+      <c r="Y8">
+        <v>12.5</v>
+      </c>
+      <c r="Z8">
+        <v>16</v>
+      </c>
+      <c r="AA8">
+        <v>42</v>
+      </c>
+      <c r="AB8">
+        <v>15.5</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>13</v>
+      </c>
+      <c r="AE8">
+        <v>32</v>
+      </c>
+      <c r="AF8">
+        <v>29</v>
+      </c>
+      <c r="AG8">
+        <v>20</v>
+      </c>
+      <c r="AH8">
+        <v>21</v>
+      </c>
+      <c r="AI8">
+        <v>70</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>65</v>
+      </c>
+      <c r="AL8">
+        <v>90</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>70</v>
+      </c>
+      <c r="AO8">
+        <v>25</v>
+      </c>
+      <c r="AP8">
+        <v>9</v>
+      </c>
+      <c r="AQ8">
+        <v>7.2</v>
+      </c>
+      <c r="AR8">
+        <v>11</v>
+      </c>
+      <c r="AS8">
+        <v>3.55</v>
+      </c>
+      <c r="AT8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>5.8</v>
+      </c>
+      <c r="AV8">
+        <v>9.4</v>
+      </c>
+      <c r="AW8">
+        <v>3.45</v>
+      </c>
+      <c r="AX8">
+        <v>3.4</v>
+      </c>
+      <c r="AY8">
+        <v>11</v>
+      </c>
+      <c r="AZ8">
         <v>14.5</v>
       </c>
-      <c r="Y8">
-        <v>10.5</v>
-      </c>
-      <c r="Z8">
-        <v>15.5</v>
-      </c>
-      <c r="AA8">
-        <v>34</v>
-      </c>
-      <c r="AB8">
-        <v>13.5</v>
-      </c>
-      <c r="AC8">
-        <v>8</v>
-      </c>
-      <c r="AD8">
-        <v>12</v>
-      </c>
-      <c r="AE8">
-        <v>27</v>
-      </c>
-      <c r="AF8">
-        <v>25</v>
-      </c>
-      <c r="AG8">
-        <v>15</v>
-      </c>
-      <c r="AH8">
+      <c r="BA8">
+        <v>3.65</v>
+      </c>
+      <c r="BB8">
+        <v>3.9</v>
+      </c>
+      <c r="BC8">
+        <v>3.65</v>
+      </c>
+      <c r="BD8">
+        <v>3.7</v>
+      </c>
+      <c r="BE8">
+        <v>3.9</v>
+      </c>
+      <c r="BF8">
         <v>18</v>
       </c>
-      <c r="AI8">
-        <v>40</v>
-      </c>
-      <c r="AJ8">
-        <v>65</v>
-      </c>
-      <c r="AK8">
-        <v>42</v>
-      </c>
-      <c r="AL8">
-        <v>55</v>
-      </c>
-      <c r="AM8">
-        <v>110</v>
-      </c>
-      <c r="AN8">
-        <v>40</v>
-      </c>
-      <c r="AO8">
-        <v>21</v>
-      </c>
-      <c r="AP8">
-        <v>12</v>
-      </c>
-      <c r="AQ8">
-        <v>9</v>
-      </c>
-      <c r="AR8">
-        <v>13</v>
-      </c>
-      <c r="AS8">
-        <v>8</v>
-      </c>
-      <c r="AT8">
-        <v>11.5</v>
-      </c>
-      <c r="AU8">
-        <v>7</v>
-      </c>
-      <c r="AV8">
-        <v>10</v>
-      </c>
-      <c r="AW8">
-        <v>21</v>
-      </c>
-      <c r="AX8">
-        <v>20</v>
-      </c>
-      <c r="AY8">
-        <v>12.5</v>
-      </c>
-      <c r="AZ8">
-        <v>15</v>
-      </c>
-      <c r="BA8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB8">
-        <v>9</v>
-      </c>
-      <c r="BC8">
-        <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>40</v>
-      </c>
-      <c r="BE8">
-        <v>9.4</v>
-      </c>
-      <c r="BF8">
-        <v>30</v>
-      </c>
       <c r="BG8">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH8">
         <v>0</v>
@@ -2652,16 +2652,16 @@
         <v>3.5</v>
       </c>
       <c r="G9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
         <v>2.2</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
         <v>3.85</v>
@@ -2679,19 +2679,19 @@
         <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
         <v>1.78</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T9">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U9">
         <v>2.4</v>
@@ -2703,172 +2703,172 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="AA9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AD9">
         <v>11</v>
       </c>
       <c r="AE9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH9">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AP9">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS9">
+        <v>17</v>
+      </c>
+      <c r="AT9">
+        <v>10</v>
+      </c>
+      <c r="AU9">
+        <v>7.6</v>
+      </c>
+      <c r="AV9">
+        <v>7.6</v>
+      </c>
+      <c r="AW9">
+        <v>12</v>
+      </c>
+      <c r="AX9">
+        <v>2.56</v>
+      </c>
+      <c r="AY9">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9">
+        <v>10</v>
+      </c>
+      <c r="BA9">
+        <v>2.8</v>
+      </c>
+      <c r="BB9">
+        <v>2.8</v>
+      </c>
+      <c r="BC9">
+        <v>2.8</v>
+      </c>
+      <c r="BD9">
+        <v>2.62</v>
+      </c>
+      <c r="BE9">
+        <v>2.8</v>
+      </c>
+      <c r="BF9">
         <v>20</v>
       </c>
-      <c r="AT9">
-        <v>14</v>
-      </c>
-      <c r="AU9">
-        <v>7.8</v>
-      </c>
-      <c r="AV9">
-        <v>10</v>
-      </c>
-      <c r="AW9">
-        <v>18.5</v>
-      </c>
-      <c r="AX9">
-        <v>19.5</v>
-      </c>
-      <c r="AY9">
-        <v>13</v>
-      </c>
-      <c r="AZ9">
-        <v>14</v>
-      </c>
-      <c r="BA9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB9">
-        <v>10.5</v>
-      </c>
-      <c r="BC9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD9">
+      <c r="BG9">
+        <v>11</v>
+      </c>
+      <c r="BH9">
+        <v>4.3</v>
+      </c>
+      <c r="BI9">
+        <v>3.15</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>6.4</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
         <v>9.4</v>
       </c>
-      <c r="BE9">
-        <v>10.5</v>
-      </c>
-      <c r="BF9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG9">
-        <v>11.5</v>
-      </c>
-      <c r="BH9">
-        <v>3.85</v>
-      </c>
-      <c r="BI9">
-        <v>3.5</v>
-      </c>
-      <c r="BJ9">
-        <v>9</v>
-      </c>
-      <c r="BK9">
-        <v>7.8</v>
-      </c>
-      <c r="BL9">
-        <v>110</v>
-      </c>
-      <c r="BM9">
-        <v>65</v>
-      </c>
-      <c r="BN9">
-        <v>7</v>
-      </c>
       <c r="BO9">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV9">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2894,19 +2894,19 @@
         <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H10">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="I10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2921,136 +2921,136 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
+        <v>2.02</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>2.72</v>
+      </c>
+      <c r="U10">
+        <v>1.44</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>50</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>7.6</v>
+      </c>
+      <c r="AC10">
+        <v>29</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>7.8</v>
+      </c>
+      <c r="AG10">
+        <v>26</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>14.5</v>
+      </c>
+      <c r="AK10">
+        <v>44</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>10</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>2.18</v>
+      </c>
+      <c r="AQ10">
+        <v>2.1</v>
+      </c>
+      <c r="AR10">
+        <v>2.18</v>
+      </c>
+      <c r="AS10">
+        <v>2.18</v>
+      </c>
+      <c r="AT10">
+        <v>4.9</v>
+      </c>
+      <c r="AU10">
+        <v>2.04</v>
+      </c>
+      <c r="AV10">
+        <v>2.18</v>
+      </c>
+      <c r="AW10">
+        <v>2.18</v>
+      </c>
+      <c r="AX10">
+        <v>4.8</v>
+      </c>
+      <c r="AY10">
+        <v>2.02</v>
+      </c>
+      <c r="AZ10">
+        <v>2.18</v>
+      </c>
+      <c r="BA10">
+        <v>2.18</v>
+      </c>
+      <c r="BB10">
+        <v>1.9</v>
+      </c>
+      <c r="BC10">
         <v>2.08</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>2.74</v>
-      </c>
-      <c r="U10">
-        <v>1.47</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>14</v>
-      </c>
-      <c r="Y10">
-        <v>38</v>
-      </c>
-      <c r="Z10">
-        <v>210</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>6</v>
-      </c>
-      <c r="AC10">
-        <v>14</v>
-      </c>
-      <c r="AD10">
-        <v>80</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>6.4</v>
-      </c>
-      <c r="AG10">
-        <v>12.5</v>
-      </c>
-      <c r="AH10">
-        <v>60</v>
-      </c>
-      <c r="AI10">
-        <v>480</v>
-      </c>
-      <c r="AJ10">
-        <v>10</v>
-      </c>
-      <c r="AK10">
-        <v>19.5</v>
-      </c>
-      <c r="AL10">
-        <v>90</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>7.6</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>11.5</v>
-      </c>
-      <c r="AQ10">
-        <v>8.4</v>
-      </c>
-      <c r="AR10">
-        <v>9.6</v>
-      </c>
-      <c r="AS10">
-        <v>10</v>
-      </c>
-      <c r="AT10">
-        <v>5.1</v>
-      </c>
-      <c r="AU10">
-        <v>11.5</v>
-      </c>
-      <c r="AV10">
-        <v>9.6</v>
-      </c>
-      <c r="AW10">
-        <v>10</v>
-      </c>
-      <c r="AX10">
-        <v>5.4</v>
-      </c>
-      <c r="AY10">
+      <c r="BD10">
+        <v>2.18</v>
+      </c>
+      <c r="BE10">
+        <v>2.18</v>
+      </c>
+      <c r="BF10">
+        <v>1.79</v>
+      </c>
+      <c r="BG10">
         <v>10.5</v>
-      </c>
-      <c r="AZ10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB10">
-        <v>8</v>
-      </c>
-      <c r="BC10">
-        <v>16.5</v>
-      </c>
-      <c r="BD10">
-        <v>9</v>
-      </c>
-      <c r="BE10">
-        <v>10</v>
-      </c>
-      <c r="BF10">
-        <v>6.4</v>
-      </c>
-      <c r="BG10">
-        <v>10</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3157,16 +3157,16 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O11">
         <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -3178,7 +3178,7 @@
         <v>1.99</v>
       </c>
       <c r="U11">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3187,172 +3187,172 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD11">
         <v>11.5</v>
       </c>
       <c r="AE11">
+        <v>34</v>
+      </c>
+      <c r="AF11">
         <v>30</v>
       </c>
-      <c r="AF11">
-        <v>26</v>
-      </c>
       <c r="AG11">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AL11">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR11">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AS11">
-        <v>21</v>
+        <v>3.3</v>
       </c>
       <c r="AT11">
+        <v>9.6</v>
+      </c>
+      <c r="AU11">
+        <v>6</v>
+      </c>
+      <c r="AV11">
+        <v>9.6</v>
+      </c>
+      <c r="AW11">
+        <v>3.25</v>
+      </c>
+      <c r="AX11">
+        <v>3.2</v>
+      </c>
+      <c r="AY11">
+        <v>12.5</v>
+      </c>
+      <c r="AZ11">
+        <v>3.2</v>
+      </c>
+      <c r="BA11">
+        <v>3.5</v>
+      </c>
+      <c r="BB11">
+        <v>3.65</v>
+      </c>
+      <c r="BC11">
+        <v>3.5</v>
+      </c>
+      <c r="BD11">
+        <v>3.65</v>
+      </c>
+      <c r="BE11">
+        <v>3.65</v>
+      </c>
+      <c r="BF11">
+        <v>25</v>
+      </c>
+      <c r="BG11">
+        <v>13.5</v>
+      </c>
+      <c r="BH11">
+        <v>3.25</v>
+      </c>
+      <c r="BI11">
+        <v>2.56</v>
+      </c>
+      <c r="BJ11">
+        <v>18</v>
+      </c>
+      <c r="BK11">
+        <v>7.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO11">
+        <v>5.2</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>5.9</v>
+      </c>
+      <c r="BU11">
+        <v>3.95</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
         <v>10.5</v>
       </c>
-      <c r="AU11">
-        <v>6.6</v>
-      </c>
-      <c r="AV11">
-        <v>10</v>
-      </c>
-      <c r="AW11">
-        <v>20</v>
-      </c>
-      <c r="AX11">
-        <v>21</v>
-      </c>
-      <c r="AY11">
-        <v>13.5</v>
-      </c>
-      <c r="AZ11">
-        <v>15.5</v>
-      </c>
-      <c r="BA11">
-        <v>38</v>
-      </c>
-      <c r="BB11">
-        <v>9.4</v>
-      </c>
-      <c r="BC11">
-        <v>38</v>
-      </c>
-      <c r="BD11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE11">
-        <v>10</v>
-      </c>
-      <c r="BF11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG11">
-        <v>18</v>
-      </c>
-      <c r="BH11">
-        <v>2.98</v>
-      </c>
-      <c r="BI11">
-        <v>2.76</v>
-      </c>
-      <c r="BJ11">
-        <v>10.5</v>
-      </c>
-      <c r="BK11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL11">
-        <v>190</v>
-      </c>
-      <c r="BM11">
-        <v>1.01</v>
-      </c>
-      <c r="BN11">
-        <v>7</v>
-      </c>
-      <c r="BO11">
-        <v>6</v>
-      </c>
-      <c r="BP11">
-        <v>40</v>
-      </c>
-      <c r="BQ11">
-        <v>26</v>
-      </c>
-      <c r="BR11">
-        <v>60</v>
-      </c>
-      <c r="BS11">
-        <v>36</v>
-      </c>
-      <c r="BT11">
-        <v>4.9</v>
-      </c>
-      <c r="BU11">
-        <v>4.4</v>
-      </c>
-      <c r="BV11">
-        <v>21</v>
-      </c>
-      <c r="BW11">
-        <v>15</v>
-      </c>
       <c r="BX11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>
@@ -3378,7 +3378,7 @@
         <v>3.4</v>
       </c>
       <c r="G12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
         <v>2.28</v>
@@ -3387,7 +3387,7 @@
         <v>2.3</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
         <v>3.7</v>
@@ -3405,22 +3405,22 @@
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3429,112 +3429,112 @@
         <v>0</v>
       </c>
       <c r="X12">
+        <v>80</v>
+      </c>
+      <c r="Y12">
+        <v>14</v>
+      </c>
+      <c r="Z12">
+        <v>18.5</v>
+      </c>
+      <c r="AA12">
+        <v>50</v>
+      </c>
+      <c r="AB12">
+        <v>18</v>
+      </c>
+      <c r="AC12">
+        <v>9.6</v>
+      </c>
+      <c r="AD12">
+        <v>11.5</v>
+      </c>
+      <c r="AE12">
+        <v>29</v>
+      </c>
+      <c r="AF12">
+        <v>32</v>
+      </c>
+      <c r="AG12">
         <v>17</v>
       </c>
-      <c r="Y12">
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>55</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>60</v>
+      </c>
+      <c r="AL12">
+        <v>75</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>60</v>
+      </c>
+      <c r="AO12">
+        <v>19.5</v>
+      </c>
+      <c r="AP12">
+        <v>10</v>
+      </c>
+      <c r="AQ12">
+        <v>8</v>
+      </c>
+      <c r="AR12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS12">
+        <v>3.2</v>
+      </c>
+      <c r="AT12">
         <v>11.5</v>
       </c>
-      <c r="Z12">
-        <v>15.5</v>
-      </c>
-      <c r="AA12">
-        <v>29</v>
-      </c>
-      <c r="AB12">
-        <v>15</v>
-      </c>
-      <c r="AC12">
-        <v>8.4</v>
-      </c>
-      <c r="AD12">
+      <c r="AU12">
+        <v>6.8</v>
+      </c>
+      <c r="AV12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12">
+        <v>3.05</v>
+      </c>
+      <c r="AX12">
+        <v>3.05</v>
+      </c>
+      <c r="AY12">
         <v>11</v>
       </c>
-      <c r="AE12">
-        <v>23</v>
-      </c>
-      <c r="AF12">
-        <v>26</v>
-      </c>
-      <c r="AG12">
-        <v>14.5</v>
-      </c>
-      <c r="AH12">
-        <v>16</v>
-      </c>
-      <c r="AI12">
-        <v>34</v>
-      </c>
-      <c r="AJ12">
-        <v>60</v>
-      </c>
-      <c r="AK12">
-        <v>38</v>
-      </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
-      <c r="AM12">
-        <v>80</v>
-      </c>
-      <c r="AN12">
-        <v>34</v>
-      </c>
-      <c r="AO12">
-        <v>15</v>
-      </c>
-      <c r="AP12">
-        <v>14.5</v>
-      </c>
-      <c r="AQ12">
-        <v>10</v>
-      </c>
-      <c r="AR12">
-        <v>13.5</v>
-      </c>
-      <c r="AS12">
-        <v>24</v>
-      </c>
-      <c r="AT12">
-        <v>13.5</v>
-      </c>
-      <c r="AU12">
-        <v>7.6</v>
-      </c>
-      <c r="AV12">
-        <v>10</v>
-      </c>
-      <c r="AW12">
-        <v>20</v>
-      </c>
-      <c r="AX12">
-        <v>19</v>
-      </c>
-      <c r="AY12">
-        <v>13</v>
-      </c>
       <c r="AZ12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA12">
-        <v>28</v>
+        <v>3.2</v>
       </c>
       <c r="BB12">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="BC12">
-        <v>32</v>
+        <v>3.2</v>
       </c>
       <c r="BD12">
-        <v>38</v>
+        <v>3.25</v>
       </c>
       <c r="BE12">
-        <v>13.5</v>
+        <v>3.4</v>
       </c>
       <c r="BF12">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH12">
         <v>4.1</v>
@@ -3632,7 +3632,7 @@
         <v>1.1</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="L13">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 05:48:08</t>
+    <t>2026-09-29 07:59:09</t>
   </si>
 </sst>
 </file>
@@ -955,13 +955,13 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G2">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
         <v>4.3</v>
@@ -970,22 +970,22 @@
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
         <v>1.75</v>
@@ -994,127 +994,127 @@
         <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="AC2">
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
+        <v>19</v>
+      </c>
+      <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
+        <v>16</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
+        <v>20</v>
+      </c>
+      <c r="AI2">
+        <v>60</v>
+      </c>
+      <c r="AJ2">
+        <v>28</v>
+      </c>
+      <c r="AK2">
+        <v>24</v>
+      </c>
+      <c r="AL2">
+        <v>38</v>
+      </c>
+      <c r="AM2">
+        <v>90</v>
+      </c>
+      <c r="AN2">
         <v>14.5</v>
       </c>
-      <c r="AD2">
-        <v>1000</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
+      <c r="AO2">
+        <v>46</v>
+      </c>
+      <c r="AP2">
+        <v>15</v>
+      </c>
+      <c r="AQ2">
+        <v>14</v>
+      </c>
+      <c r="AR2">
+        <v>22</v>
+      </c>
+      <c r="AS2">
+        <v>55</v>
+      </c>
+      <c r="AT2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>14</v>
+      </c>
+      <c r="AW2">
+        <v>34</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>36</v>
+      </c>
+      <c r="BB2">
         <v>18.5</v>
       </c>
-      <c r="AH2">
-        <v>1000</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>1000</v>
-      </c>
-      <c r="AL2">
-        <v>1000</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>11</v>
-      </c>
-      <c r="AQ2">
-        <v>10</v>
-      </c>
-      <c r="AR2">
-        <v>1.01</v>
-      </c>
-      <c r="AS2">
-        <v>1.01</v>
-      </c>
-      <c r="AT2">
-        <v>7.4</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>1.01</v>
-      </c>
-      <c r="AX2">
-        <v>9</v>
-      </c>
-      <c r="AY2">
-        <v>7.4</v>
-      </c>
-      <c r="AZ2">
-        <v>11</v>
-      </c>
-      <c r="BA2">
-        <v>1.01</v>
-      </c>
-      <c r="BB2">
-        <v>1.01</v>
-      </c>
       <c r="BC2">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1197,223 +1197,223 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G3">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T3">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF3">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP3">
-        <v>1.51</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>1.51</v>
+        <v>21</v>
       </c>
       <c r="AR3">
-        <v>1.51</v>
+        <v>6.2</v>
       </c>
       <c r="AS3">
-        <v>1.51</v>
+        <v>4.9</v>
       </c>
       <c r="AT3">
-        <v>1.39</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>1.38</v>
+        <v>9</v>
       </c>
       <c r="AV3">
-        <v>1.51</v>
+        <v>4.7</v>
       </c>
       <c r="AW3">
-        <v>1.51</v>
+        <v>5.6</v>
       </c>
       <c r="AX3">
-        <v>1.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>1.39</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>1.51</v>
+        <v>17</v>
       </c>
       <c r="BA3">
-        <v>1.51</v>
+        <v>5</v>
       </c>
       <c r="BB3">
-        <v>1.51</v>
+        <v>13</v>
       </c>
       <c r="BC3">
-        <v>1.51</v>
+        <v>14</v>
       </c>
       <c r="BD3">
-        <v>1.51</v>
+        <v>5.7</v>
       </c>
       <c r="BE3">
-        <v>1.51</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
-        <v>1.31</v>
+        <v>6.4</v>
       </c>
       <c r="BG3">
-        <v>1.51</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1439,220 +1439,220 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
         <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4">
         <v>11</v>
       </c>
-      <c r="AC4">
-        <v>14.5</v>
-      </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>28</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>23</v>
+      </c>
+      <c r="AK4">
+        <v>24</v>
+      </c>
+      <c r="AL4">
+        <v>48</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
         <v>15</v>
       </c>
-      <c r="AG4">
-        <v>17.5</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
+        <v>15</v>
+      </c>
+      <c r="AR4">
+        <v>32</v>
+      </c>
+      <c r="AS4">
+        <v>110</v>
+      </c>
+      <c r="AT4">
+        <v>6.6</v>
+      </c>
+      <c r="AU4">
+        <v>7.6</v>
+      </c>
+      <c r="AV4">
+        <v>16.5</v>
+      </c>
+      <c r="AW4">
+        <v>60</v>
+      </c>
+      <c r="AX4">
+        <v>8.4</v>
+      </c>
+      <c r="AY4">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4">
+        <v>16.5</v>
+      </c>
+      <c r="BA4">
+        <v>60</v>
+      </c>
+      <c r="BB4">
+        <v>15.5</v>
+      </c>
+      <c r="BC4">
+        <v>16.5</v>
+      </c>
+      <c r="BD4">
+        <v>27</v>
+      </c>
+      <c r="BE4">
+        <v>95</v>
+      </c>
+      <c r="BF4">
         <v>10.5</v>
       </c>
-      <c r="AR4">
-        <v>1.01</v>
-      </c>
-      <c r="AS4">
-        <v>1.01</v>
-      </c>
-      <c r="AT4">
-        <v>5.7</v>
-      </c>
-      <c r="AU4">
-        <v>6.6</v>
-      </c>
-      <c r="AV4">
-        <v>1.01</v>
-      </c>
-      <c r="AW4">
-        <v>1.01</v>
-      </c>
-      <c r="AX4">
-        <v>6.6</v>
-      </c>
-      <c r="AY4">
-        <v>7.2</v>
-      </c>
-      <c r="AZ4">
-        <v>1.01</v>
-      </c>
-      <c r="BA4">
-        <v>1.01</v>
-      </c>
-      <c r="BB4">
-        <v>10.5</v>
-      </c>
-      <c r="BC4">
-        <v>11</v>
-      </c>
-      <c r="BD4">
-        <v>1.01</v>
-      </c>
-      <c r="BE4">
-        <v>1.01</v>
-      </c>
-      <c r="BF4">
-        <v>7.8</v>
-      </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1684,19 +1684,19 @@
         <v>1.18</v>
       </c>
       <c r="G5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
         <v>1.67</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1735,112 +1735,112 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AE5">
         <v>1000</v>
       </c>
       <c r="AF5">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AJ5">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AN5">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>2.06</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="AR5">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>2.06</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
-        <v>1.76</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
-        <v>2.06</v>
+        <v>16.5</v>
       </c>
       <c r="AV5">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="AW5">
-        <v>2.06</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>1.65</v>
+        <v>5.7</v>
       </c>
       <c r="AY5">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="BA5">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
-        <v>1.71</v>
+        <v>6.4</v>
       </c>
       <c r="BC5">
-        <v>2.06</v>
+        <v>14</v>
       </c>
       <c r="BD5">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG5">
-        <v>2.06</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>0</v>
@@ -1923,19 +1923,19 @@
         <v>107</v>
       </c>
       <c r="F6">
+        <v>6.4</v>
+      </c>
+      <c r="G6">
         <v>6.8</v>
       </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
       <c r="H6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="I6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -1947,28 +1947,28 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
         <v>2.52</v>
       </c>
       <c r="T6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1977,19 +1977,19 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y6">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="AB6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -1998,91 +1998,91 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE6">
-        <v>48</v>
+        <v>15.5</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO6">
+        <v>6.4</v>
+      </c>
+      <c r="AP6">
+        <v>21</v>
+      </c>
+      <c r="AQ6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR6">
+        <v>9.4</v>
+      </c>
+      <c r="AS6">
+        <v>13</v>
+      </c>
+      <c r="AT6">
+        <v>20</v>
+      </c>
+      <c r="AU6">
+        <v>9.6</v>
+      </c>
+      <c r="AV6">
+        <v>9.4</v>
+      </c>
+      <c r="AW6">
+        <v>13.5</v>
+      </c>
+      <c r="AX6">
         <v>8.6</v>
       </c>
-      <c r="AP6">
-        <v>2.28</v>
-      </c>
-      <c r="AQ6">
-        <v>7.6</v>
-      </c>
-      <c r="AR6">
-        <v>7.2</v>
-      </c>
-      <c r="AS6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT6">
-        <v>2.12</v>
-      </c>
-      <c r="AU6">
-        <v>7.4</v>
-      </c>
-      <c r="AV6">
-        <v>7</v>
-      </c>
-      <c r="AW6">
-        <v>9.6</v>
-      </c>
-      <c r="AX6">
-        <v>2.58</v>
-      </c>
       <c r="AY6">
-        <v>2.1</v>
+        <v>21</v>
       </c>
       <c r="AZ6">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>2.28</v>
+        <v>21</v>
       </c>
       <c r="BB6">
-        <v>2.28</v>
+        <v>9.4</v>
       </c>
       <c r="BC6">
-        <v>2.28</v>
+        <v>9</v>
       </c>
       <c r="BD6">
-        <v>2.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6">
-        <v>2.28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6">
-        <v>2.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
         <v>4.7</v>
@@ -2165,43 +2165,43 @@
         <v>108</v>
       </c>
       <c r="F7">
+        <v>1.27</v>
+      </c>
+      <c r="G7">
         <v>1.29</v>
       </c>
-      <c r="G7">
-        <v>1.3</v>
-      </c>
       <c r="H7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <v>6.8</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P7">
         <v>3</v>
       </c>
       <c r="Q7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S7">
         <v>2.12</v>
@@ -2210,7 +2210,7 @@
         <v>1.94</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2219,112 +2219,112 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y7">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AB7">
+        <v>13</v>
+      </c>
+      <c r="AC7">
+        <v>16.5</v>
+      </c>
+      <c r="AD7">
+        <v>48</v>
+      </c>
+      <c r="AE7">
+        <v>210</v>
+      </c>
+      <c r="AF7">
+        <v>10</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>30</v>
+      </c>
+      <c r="AI7">
+        <v>150</v>
+      </c>
+      <c r="AJ7">
+        <v>11</v>
+      </c>
+      <c r="AK7">
+        <v>14</v>
+      </c>
+      <c r="AL7">
+        <v>34</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>3.7</v>
+      </c>
+      <c r="AO7">
+        <v>210</v>
+      </c>
+      <c r="AP7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ7">
+        <v>34</v>
+      </c>
+      <c r="AR7">
+        <v>10.5</v>
+      </c>
+      <c r="AS7">
+        <v>11</v>
+      </c>
+      <c r="AT7">
+        <v>11</v>
+      </c>
+      <c r="AU7">
+        <v>13.5</v>
+      </c>
+      <c r="AV7">
+        <v>32</v>
+      </c>
+      <c r="AW7">
+        <v>11</v>
+      </c>
+      <c r="AX7">
+        <v>8.6</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>22</v>
+      </c>
+      <c r="BA7">
+        <v>10.5</v>
+      </c>
+      <c r="BB7">
+        <v>9.4</v>
+      </c>
+      <c r="BC7">
+        <v>11.5</v>
+      </c>
+      <c r="BD7">
         <v>23</v>
       </c>
-      <c r="AC7">
-        <v>18.5</v>
-      </c>
-      <c r="AD7">
-        <v>70</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>11.5</v>
-      </c>
-      <c r="AG7">
-        <v>13</v>
-      </c>
-      <c r="AH7">
-        <v>40</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>12.5</v>
-      </c>
-      <c r="AK7">
-        <v>18</v>
-      </c>
-      <c r="AL7">
-        <v>44</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>4.3</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>3.4</v>
-      </c>
-      <c r="AQ7">
-        <v>3.25</v>
-      </c>
-      <c r="AR7">
-        <v>3.4</v>
-      </c>
-      <c r="AS7">
-        <v>3.4</v>
-      </c>
-      <c r="AT7">
-        <v>8.6</v>
-      </c>
-      <c r="AU7">
-        <v>12.5</v>
-      </c>
-      <c r="AV7">
-        <v>3.2</v>
-      </c>
-      <c r="AW7">
-        <v>3.4</v>
-      </c>
-      <c r="AX7">
-        <v>8</v>
-      </c>
-      <c r="AY7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7">
-        <v>3.1</v>
-      </c>
-      <c r="BA7">
-        <v>3.4</v>
-      </c>
-      <c r="BB7">
-        <v>7.4</v>
-      </c>
-      <c r="BC7">
+      <c r="BE7">
         <v>10.5</v>
       </c>
-      <c r="BD7">
-        <v>3.15</v>
-      </c>
-      <c r="BE7">
-        <v>3.4</v>
-      </c>
       <c r="BF7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BG7">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="BH7">
         <v>6</v>
@@ -2366,7 +2366,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2407,19 +2407,19 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H8">
+        <v>2.36</v>
+      </c>
+      <c r="I8">
         <v>2.38</v>
       </c>
-      <c r="I8">
-        <v>2.4</v>
-      </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
         <v>3.55</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2461,112 +2461,112 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y8">
+        <v>10.5</v>
+      </c>
+      <c r="Z8">
+        <v>15.5</v>
+      </c>
+      <c r="AA8">
+        <v>34</v>
+      </c>
+      <c r="AB8">
+        <v>13.5</v>
+      </c>
+      <c r="AC8">
+        <v>8</v>
+      </c>
+      <c r="AD8">
+        <v>12</v>
+      </c>
+      <c r="AE8">
+        <v>27</v>
+      </c>
+      <c r="AF8">
+        <v>25</v>
+      </c>
+      <c r="AG8">
+        <v>15</v>
+      </c>
+      <c r="AH8">
+        <v>18</v>
+      </c>
+      <c r="AI8">
+        <v>42</v>
+      </c>
+      <c r="AJ8">
+        <v>65</v>
+      </c>
+      <c r="AK8">
+        <v>44</v>
+      </c>
+      <c r="AL8">
+        <v>55</v>
+      </c>
+      <c r="AM8">
+        <v>110</v>
+      </c>
+      <c r="AN8">
+        <v>42</v>
+      </c>
+      <c r="AO8">
+        <v>21</v>
+      </c>
+      <c r="AP8">
+        <v>12</v>
+      </c>
+      <c r="AQ8">
+        <v>9</v>
+      </c>
+      <c r="AR8">
+        <v>13</v>
+      </c>
+      <c r="AS8">
+        <v>26</v>
+      </c>
+      <c r="AT8">
+        <v>11.5</v>
+      </c>
+      <c r="AU8">
+        <v>7</v>
+      </c>
+      <c r="AV8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW8">
+        <v>21</v>
+      </c>
+      <c r="AX8">
+        <v>19</v>
+      </c>
+      <c r="AY8">
         <v>12.5</v>
       </c>
-      <c r="Z8">
-        <v>16</v>
-      </c>
-      <c r="AA8">
-        <v>42</v>
-      </c>
-      <c r="AB8">
-        <v>15.5</v>
-      </c>
-      <c r="AC8">
-        <v>9</v>
-      </c>
-      <c r="AD8">
-        <v>13</v>
-      </c>
-      <c r="AE8">
-        <v>32</v>
-      </c>
-      <c r="AF8">
-        <v>29</v>
-      </c>
-      <c r="AG8">
-        <v>20</v>
-      </c>
-      <c r="AH8">
-        <v>21</v>
-      </c>
-      <c r="AI8">
-        <v>70</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>65</v>
-      </c>
-      <c r="AL8">
-        <v>90</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>70</v>
-      </c>
-      <c r="AO8">
-        <v>25</v>
-      </c>
-      <c r="AP8">
-        <v>9</v>
-      </c>
-      <c r="AQ8">
-        <v>7.2</v>
-      </c>
-      <c r="AR8">
-        <v>11</v>
-      </c>
-      <c r="AS8">
-        <v>3.55</v>
-      </c>
-      <c r="AT8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU8">
-        <v>5.8</v>
-      </c>
-      <c r="AV8">
-        <v>9.4</v>
-      </c>
-      <c r="AW8">
-        <v>3.45</v>
-      </c>
-      <c r="AX8">
-        <v>3.4</v>
-      </c>
-      <c r="AY8">
-        <v>11</v>
-      </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="BB8">
-        <v>3.9</v>
+        <v>38</v>
       </c>
       <c r="BC8">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8">
-        <v>3.7</v>
+        <v>38</v>
       </c>
       <c r="BE8">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
         <v>18</v>
       </c>
       <c r="BG8">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BH8">
         <v>0</v>
@@ -2649,16 +2649,16 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G9">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J9">
         <v>3.8</v>
@@ -2673,25 +2673,25 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>1.47</v>
       </c>
       <c r="S9">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T9">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
         <v>2.4</v>
@@ -2703,172 +2703,172 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z9">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC9">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
         <v>11</v>
       </c>
       <c r="AE9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL9">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO9">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AP9">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS9">
         <v>17</v>
       </c>
       <c r="AT9">
+        <v>14</v>
+      </c>
+      <c r="AU9">
+        <v>7.8</v>
+      </c>
+      <c r="AV9">
         <v>10</v>
       </c>
-      <c r="AU9">
-        <v>7.6</v>
-      </c>
-      <c r="AV9">
-        <v>7.6</v>
-      </c>
       <c r="AW9">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AX9">
-        <v>2.56</v>
+        <v>19.5</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AZ9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA9">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="BB9">
-        <v>2.8</v>
+        <v>30</v>
       </c>
       <c r="BC9">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD9">
-        <v>2.62</v>
+        <v>34</v>
       </c>
       <c r="BE9">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
         <v>20</v>
       </c>
       <c r="BG9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BI9">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK9">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BO9">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BU9">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2894,10 +2894,10 @@
         <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="I10">
         <v>19.5</v>
@@ -2906,7 +2906,7 @@
         <v>5.2</v>
       </c>
       <c r="K10">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
         <v>1.44</v>
@@ -2945,109 +2945,109 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y10">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AC10">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
+        <v>6.4</v>
+      </c>
+      <c r="AG10">
+        <v>14.5</v>
+      </c>
+      <c r="AH10">
+        <v>65</v>
+      </c>
+      <c r="AI10">
+        <v>470</v>
+      </c>
+      <c r="AJ10">
+        <v>9.6</v>
+      </c>
+      <c r="AK10">
+        <v>20</v>
+      </c>
+      <c r="AL10">
+        <v>90</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
         <v>7.8</v>
       </c>
-      <c r="AG10">
-        <v>26</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>14.5</v>
-      </c>
-      <c r="AK10">
-        <v>44</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>10</v>
-      </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="AR10">
-        <v>2.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS10">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="AT10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU10">
-        <v>2.04</v>
+        <v>11.5</v>
       </c>
       <c r="AV10">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="AW10">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="AX10">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AY10">
-        <v>2.02</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>2.18</v>
+        <v>34</v>
       </c>
       <c r="BA10">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="BB10">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="BC10">
-        <v>2.08</v>
+        <v>16.5</v>
       </c>
       <c r="BD10">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="BE10">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="BF10">
-        <v>1.79</v>
+        <v>6.4</v>
       </c>
       <c r="BG10">
         <v>10.5</v>
@@ -3136,7 +3136,7 @@
         <v>3.65</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H11">
         <v>2.26</v>
@@ -3145,7 +3145,7 @@
         <v>2.3</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
         <v>3.45</v>
@@ -3160,13 +3160,13 @@
         <v>3.15</v>
       </c>
       <c r="O11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P11">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q11">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -3175,10 +3175,10 @@
         <v>4.4</v>
       </c>
       <c r="T11">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3187,106 +3187,106 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD11">
         <v>11.5</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AG11">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH11">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK11">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO11">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP11">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR11">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AS11">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="AT11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW11">
-        <v>3.25</v>
+        <v>21</v>
       </c>
       <c r="AX11">
-        <v>3.2</v>
+        <v>21</v>
       </c>
       <c r="AY11">
+        <v>13.5</v>
+      </c>
+      <c r="AZ11">
+        <v>16.5</v>
+      </c>
+      <c r="BA11">
+        <v>10.5</v>
+      </c>
+      <c r="BB11">
+        <v>12</v>
+      </c>
+      <c r="BC11">
+        <v>11</v>
+      </c>
+      <c r="BD11">
+        <v>11.5</v>
+      </c>
+      <c r="BE11">
         <v>12.5</v>
-      </c>
-      <c r="AZ11">
-        <v>3.2</v>
-      </c>
-      <c r="BA11">
-        <v>3.5</v>
-      </c>
-      <c r="BB11">
-        <v>3.65</v>
-      </c>
-      <c r="BC11">
-        <v>3.5</v>
-      </c>
-      <c r="BD11">
-        <v>3.65</v>
-      </c>
-      <c r="BE11">
-        <v>3.65</v>
       </c>
       <c r="BF11">
         <v>25</v>
@@ -3295,64 +3295,64 @@
         <v>13.5</v>
       </c>
       <c r="BH11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BI11">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BO11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BT11">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BU11">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW11">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>
@@ -3378,16 +3378,16 @@
         <v>3.4</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H12">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I12">
         <v>2.3</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
         <v>3.7</v>
@@ -3402,19 +3402,19 @@
         <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T12">
         <v>1.69</v>
@@ -3429,112 +3429,112 @@
         <v>0</v>
       </c>
       <c r="X12">
+        <v>17</v>
+      </c>
+      <c r="Y12">
+        <v>11.5</v>
+      </c>
+      <c r="Z12">
+        <v>15.5</v>
+      </c>
+      <c r="AA12">
+        <v>29</v>
+      </c>
+      <c r="AB12">
+        <v>15.5</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>23</v>
+      </c>
+      <c r="AF12">
+        <v>26</v>
+      </c>
+      <c r="AG12">
+        <v>15</v>
+      </c>
+      <c r="AH12">
+        <v>16.5</v>
+      </c>
+      <c r="AI12">
+        <v>34</v>
+      </c>
+      <c r="AJ12">
+        <v>60</v>
+      </c>
+      <c r="AK12">
+        <v>38</v>
+      </c>
+      <c r="AL12">
+        <v>44</v>
+      </c>
+      <c r="AM12">
         <v>80</v>
       </c>
-      <c r="Y12">
+      <c r="AN12">
+        <v>34</v>
+      </c>
+      <c r="AO12">
+        <v>15.5</v>
+      </c>
+      <c r="AP12">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12">
+        <v>10</v>
+      </c>
+      <c r="AR12">
+        <v>13.5</v>
+      </c>
+      <c r="AS12">
+        <v>24</v>
+      </c>
+      <c r="AT12">
+        <v>13</v>
+      </c>
+      <c r="AU12">
+        <v>7.6</v>
+      </c>
+      <c r="AV12">
+        <v>10</v>
+      </c>
+      <c r="AW12">
+        <v>20</v>
+      </c>
+      <c r="AX12">
+        <v>19</v>
+      </c>
+      <c r="AY12">
+        <v>12.5</v>
+      </c>
+      <c r="AZ12">
         <v>14</v>
       </c>
-      <c r="Z12">
-        <v>18.5</v>
-      </c>
-      <c r="AA12">
-        <v>50</v>
-      </c>
-      <c r="AB12">
-        <v>18</v>
-      </c>
-      <c r="AC12">
-        <v>9.6</v>
-      </c>
-      <c r="AD12">
-        <v>11.5</v>
-      </c>
-      <c r="AE12">
-        <v>29</v>
-      </c>
-      <c r="AF12">
+      <c r="BA12">
+        <v>10</v>
+      </c>
+      <c r="BB12">
+        <v>42</v>
+      </c>
+      <c r="BC12">
         <v>32</v>
       </c>
-      <c r="AG12">
-        <v>17</v>
-      </c>
-      <c r="AH12">
-        <v>20</v>
-      </c>
-      <c r="AI12">
-        <v>55</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>60</v>
-      </c>
-      <c r="AL12">
-        <v>75</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>60</v>
-      </c>
-      <c r="AO12">
-        <v>19.5</v>
-      </c>
-      <c r="AP12">
-        <v>10</v>
-      </c>
-      <c r="AQ12">
-        <v>8</v>
-      </c>
-      <c r="AR12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS12">
-        <v>3.2</v>
-      </c>
-      <c r="AT12">
-        <v>11.5</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW12">
-        <v>3.05</v>
-      </c>
-      <c r="AX12">
-        <v>3.05</v>
-      </c>
-      <c r="AY12">
-        <v>11</v>
-      </c>
-      <c r="AZ12">
+      <c r="BD12">
+        <v>32</v>
+      </c>
+      <c r="BE12">
         <v>12</v>
       </c>
-      <c r="BA12">
-        <v>3.2</v>
-      </c>
-      <c r="BB12">
-        <v>25</v>
-      </c>
-      <c r="BC12">
-        <v>3.2</v>
-      </c>
-      <c r="BD12">
-        <v>3.25</v>
-      </c>
-      <c r="BE12">
-        <v>3.4</v>
-      </c>
       <c r="BF12">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BG12">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH12">
         <v>4.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 07:59:09</t>
+    <t>2026-09-29 10:10:53</t>
   </si>
 </sst>
 </file>
@@ -955,25 +955,25 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G2">
         <v>2.12</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M2">
         <v>1.05</v>
@@ -985,16 +985,16 @@
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R2">
         <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T2">
         <v>1.7</v>
@@ -1003,13 +1003,13 @@
         <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
         <v>1.9</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y2">
         <v>19</v>
@@ -1045,7 +1045,7 @@
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK2">
         <v>24</v>
@@ -1066,7 +1066,7 @@
         <v>15</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
         <v>22</v>
@@ -1075,13 +1075,13 @@
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW2">
         <v>34</v>
@@ -1230,7 +1230,7 @@
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
         <v>1.5</v>
@@ -1242,7 +1242,7 @@
         <v>1.82</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.15</v>
@@ -1260,10 +1260,10 @@
         <v>75</v>
       </c>
       <c r="AA3">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
         <v>12</v>
@@ -1287,7 +1287,7 @@
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
@@ -1302,7 +1302,7 @@
         <v>7.8</v>
       </c>
       <c r="AO3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP3">
         <v>16</v>
@@ -1311,10 +1311,10 @@
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
@@ -1323,10 +1323,10 @@
         <v>9</v>
       </c>
       <c r="AV3">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AW3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1338,34 +1338,34 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
         <v>13</v>
       </c>
       <c r="BC3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI3">
         <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1383,19 +1383,19 @@
         <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
@@ -1457,7 +1457,7 @@
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1469,13 +1469,13 @@
         <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
         <v>3.6</v>
@@ -1487,7 +1487,7 @@
         <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
         <v>2.24</v>
@@ -1601,10 +1601,10 @@
         <v>80</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1792,7 +1792,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5">
         <v>8.4</v>
@@ -1819,7 +1819,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA5">
         <v>8.4</v>
@@ -1837,7 +1837,7 @@
         <v>8.4</v>
       </c>
       <c r="BF5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG5">
         <v>8.6</v>
@@ -1923,22 +1923,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G6">
         <v>6.8</v>
       </c>
       <c r="H6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="J6">
+        <v>4.8</v>
+      </c>
+      <c r="K6">
         <v>4.9</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1953,10 +1953,10 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
         <v>1.6</v>
@@ -1965,7 +1965,7 @@
         <v>2.52</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U6">
         <v>2.24</v>
@@ -1980,13 +1980,13 @@
         <v>29</v>
       </c>
       <c r="Y6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z6">
         <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AB6">
         <v>34</v>
@@ -1998,16 +1998,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE6">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AF6">
         <v>65</v>
       </c>
       <c r="AG6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6">
         <v>36</v>
@@ -2028,13 +2028,13 @@
         <v>85</v>
       </c>
       <c r="AO6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP6">
         <v>21</v>
       </c>
       <c r="AQ6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR6">
         <v>9.4</v>
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="AU6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV6">
         <v>9.4</v>
@@ -2055,31 +2055,31 @@
         <v>13.5</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AY6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ6">
         <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB6">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BC6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BD6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF6">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BG6">
         <v>5.7</v>
@@ -2130,7 +2130,7 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2165,7 +2165,7 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G7">
         <v>1.29</v>
@@ -2174,7 +2174,7 @@
         <v>13</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J7">
         <v>6.8</v>
@@ -2189,22 +2189,22 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O7">
         <v>1.15</v>
       </c>
       <c r="P7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T7">
         <v>1.94</v>
@@ -2303,7 +2303,7 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA7">
         <v>10.5</v>
@@ -2321,70 +2321,70 @@
         <v>10.5</v>
       </c>
       <c r="BF7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG7">
         <v>11</v>
       </c>
       <c r="BH7">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BI7">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM7">
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO7">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BQ7">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS7">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU7">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="s">
         <v>115</v>
@@ -2407,13 +2407,13 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G8">
         <v>3.45</v>
       </c>
       <c r="H8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
         <v>2.38</v>
@@ -2422,7 +2422,7 @@
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2494,22 +2494,22 @@
         <v>18</v>
       </c>
       <c r="AI8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ8">
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL8">
         <v>55</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO8">
         <v>21</v>
@@ -2533,13 +2533,13 @@
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW8">
         <v>21</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2548,19 +2548,19 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
         <v>38</v>
       </c>
       <c r="BC8">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BD8">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8">
         <v>18</v>
@@ -2649,16 +2649,16 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G9">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J9">
         <v>3.8</v>
@@ -2670,31 +2670,31 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
         <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2703,19 +2703,19 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9">
         <v>15</v>
       </c>
       <c r="AA9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC9">
         <v>8.800000000000001</v>
@@ -2727,13 +2727,13 @@
         <v>22</v>
       </c>
       <c r="AF9">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG9">
         <v>15</v>
       </c>
       <c r="AH9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
         <v>34</v>
@@ -2751,25 +2751,25 @@
         <v>90</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO9">
         <v>13.5</v>
       </c>
       <c r="AP9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS9">
         <v>17</v>
       </c>
       <c r="AT9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
@@ -2778,31 +2778,31 @@
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AX9">
         <v>19.5</v>
       </c>
       <c r="AY9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
         <v>30</v>
       </c>
       <c r="BC9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD9">
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF9">
         <v>20</v>
@@ -2847,7 +2847,7 @@
         <v>25</v>
       </c>
       <c r="BT9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU9">
         <v>4.6</v>
@@ -2903,10 +2903,10 @@
         <v>19.5</v>
       </c>
       <c r="J10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>1.78</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
         <v>1.44</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
         <v>36</v>
@@ -2972,7 +2972,7 @@
         <v>6.4</v>
       </c>
       <c r="AG10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH10">
         <v>65</v>
@@ -2981,7 +2981,7 @@
         <v>470</v>
       </c>
       <c r="AJ10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AK10">
         <v>20</v>
@@ -3002,13 +3002,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
+        <v>7</v>
+      </c>
+      <c r="AR10">
         <v>7.4</v>
       </c>
-      <c r="AR10">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AS10">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT10">
         <v>5.1</v>
@@ -3017,10 +3017,10 @@
         <v>11.5</v>
       </c>
       <c r="AV10">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW10">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX10">
         <v>5.4</v>
@@ -3029,10 +3029,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BA10">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB10">
         <v>8</v>
@@ -3041,16 +3041,16 @@
         <v>16.5</v>
       </c>
       <c r="BD10">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BE10">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>112</v>
       </c>
       <c r="F11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G11">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H11">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3175,7 +3175,7 @@
         <v>4.4</v>
       </c>
       <c r="T11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U11">
         <v>1.95</v>
@@ -3190,16 +3190,16 @@
         <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA11">
         <v>34</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC11">
         <v>7.8</v>
@@ -3208,10 +3208,10 @@
         <v>11.5</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG11">
         <v>16.5</v>
@@ -3220,10 +3220,10 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK11">
         <v>65</v>
@@ -3238,7 +3238,7 @@
         <v>70</v>
       </c>
       <c r="AO11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3247,16 +3247,16 @@
         <v>7.6</v>
       </c>
       <c r="AR11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11">
         <v>10</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
         <v>10</v>
@@ -3271,22 +3271,22 @@
         <v>13.5</v>
       </c>
       <c r="AZ11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
+        <v>10</v>
+      </c>
+      <c r="BB11">
+        <v>11</v>
+      </c>
+      <c r="BC11">
+        <v>10</v>
+      </c>
+      <c r="BD11">
         <v>10.5</v>
       </c>
-      <c r="BB11">
+      <c r="BE11">
         <v>12</v>
-      </c>
-      <c r="BC11">
-        <v>11</v>
-      </c>
-      <c r="BD11">
-        <v>11.5</v>
-      </c>
-      <c r="BE11">
-        <v>12.5</v>
       </c>
       <c r="BF11">
         <v>25</v>
@@ -3298,13 +3298,13 @@
         <v>3</v>
       </c>
       <c r="BI11">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL11">
         <v>190</v>
@@ -3322,7 +3322,7 @@
         <v>40</v>
       </c>
       <c r="BQ11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BR11">
         <v>60</v>
@@ -3331,7 +3331,7 @@
         <v>36</v>
       </c>
       <c r="BT11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU11">
         <v>4.4</v>
@@ -3402,19 +3402,19 @@
         <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R12">
         <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
         <v>1.69</v>
@@ -3459,7 +3459,7 @@
         <v>15</v>
       </c>
       <c r="AH12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI12">
         <v>34</v>
@@ -3474,13 +3474,13 @@
         <v>44</v>
       </c>
       <c r="AM12">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP12">
         <v>14.5</v>
@@ -3492,7 +3492,7 @@
         <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT12">
         <v>13</v>
@@ -3516,7 +3516,7 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB12">
         <v>42</v>
@@ -3528,73 +3528,73 @@
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF12">
         <v>23</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH12">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BI12">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM12">
         <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO12">
+        <v>6</v>
+      </c>
+      <c r="BP12">
+        <v>32</v>
+      </c>
+      <c r="BQ12">
+        <v>18.5</v>
+      </c>
+      <c r="BR12">
+        <v>42</v>
+      </c>
+      <c r="BS12">
+        <v>24</v>
+      </c>
+      <c r="BT12">
         <v>5.2</v>
       </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.01</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.01</v>
-      </c>
-      <c r="BT12">
-        <v>6.4</v>
-      </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB12" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 10:10:53</t>
+    <t>2026-09-29 12:22:20</t>
   </si>
 </sst>
 </file>
@@ -958,10 +958,10 @@
         <v>1.98</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
         <v>4.1</v>
@@ -979,16 +979,16 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R2">
         <v>1.4</v>
@@ -997,16 +997,16 @@
         <v>2.98</v>
       </c>
       <c r="T2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
         <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
         <v>21</v>
@@ -1063,58 +1063,58 @@
         <v>46</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AW2">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1221,25 +1221,25 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U3">
         <v>2.1</v>
@@ -1266,7 +1266,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD3">
         <v>32</v>
@@ -1287,7 +1287,7 @@
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
@@ -1299,22 +1299,22 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ3">
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AS3">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
@@ -1323,10 +1323,10 @@
         <v>9</v>
       </c>
       <c r="AV3">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1338,25 +1338,25 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB3">
         <v>13</v>
       </c>
       <c r="BC3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH3">
         <v>4.8</v>
@@ -1445,10 +1445,10 @@
         <v>1.8</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
         <v>3.7</v>
@@ -1457,13 +1457,13 @@
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.35</v>
@@ -1481,7 +1481,7 @@
         <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U4">
         <v>1.89</v>
@@ -1505,7 +1505,7 @@
         <v>210</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>11</v>
@@ -1547,28 +1547,28 @@
         <v>150</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
+        <v>5.7</v>
+      </c>
+      <c r="AU4">
         <v>6.6</v>
-      </c>
-      <c r="AU4">
-        <v>7.6</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1580,31 +1580,31 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1625,7 +1625,7 @@
         <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ4">
         <v>8.6</v>
@@ -1643,7 +1643,7 @@
         <v>6.8</v>
       </c>
       <c r="BV4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW4">
         <v>38</v>
@@ -1681,22 +1681,22 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>3</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>20</v>
       </c>
       <c r="AD5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1762,13 +1762,13 @@
         <v>6.8</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH5">
         <v>65</v>
       </c>
       <c r="AI5">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="AJ5">
         <v>7.8</v>
@@ -1792,13 +1792,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
@@ -1807,10 +1807,10 @@
         <v>16.5</v>
       </c>
       <c r="AV5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
         <v>5.7</v>
@@ -1819,10 +1819,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1831,10 +1831,10 @@
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF5">
         <v>3.6</v>
@@ -1953,16 +1953,16 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T6">
         <v>1.75</v>
@@ -2058,13 +2058,13 @@
         <v>8</v>
       </c>
       <c r="AY6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ6">
         <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB6">
         <v>8</v>
@@ -2085,64 +2085,64 @@
         <v>5.7</v>
       </c>
       <c r="BH6">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BI6">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO6">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BT6">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BU6">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW6">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>115</v>
@@ -2174,13 +2174,13 @@
         <v>13</v>
       </c>
       <c r="I7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <v>6.8</v>
       </c>
       <c r="K7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2189,28 +2189,28 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q7">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R7">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="S7">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="U7">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y7">
         <v>55</v>
@@ -2228,28 +2228,28 @@
         <v>150</v>
       </c>
       <c r="AA7">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC7">
         <v>16.5</v>
       </c>
       <c r="AD7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE7">
         <v>210</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>150</v>
@@ -2264,7 +2264,7 @@
         <v>34</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN7">
         <v>3.7</v>
@@ -2273,16 +2273,16 @@
         <v>210</v>
       </c>
       <c r="AP7">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7">
         <v>34</v>
       </c>
       <c r="AR7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT7">
         <v>11</v>
@@ -2294,7 +2294,7 @@
         <v>32</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2306,10 +2306,10 @@
         <v>21</v>
       </c>
       <c r="BA7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7">
         <v>11.5</v>
@@ -2318,13 +2318,13 @@
         <v>23</v>
       </c>
       <c r="BE7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BG7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH7">
         <v>5.1</v>
@@ -2348,13 +2348,13 @@
         <v>4.1</v>
       </c>
       <c r="BO7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
         <v>7</v>
       </c>
       <c r="BQ7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR7">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>14</v>
       </c>
       <c r="BT7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BU7">
         <v>12.5</v>
@@ -2378,7 +2378,7 @@
         <v>85</v>
       </c>
       <c r="BY7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BZ7">
         <v>10</v>
@@ -2407,22 +2407,22 @@
         <v>109</v>
       </c>
       <c r="F8">
+        <v>3.35</v>
+      </c>
+      <c r="G8">
         <v>3.4</v>
       </c>
-      <c r="G8">
-        <v>3.45</v>
-      </c>
       <c r="H8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2554,10 +2554,10 @@
         <v>38</v>
       </c>
       <c r="BC8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD8">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BE8">
         <v>9.4</v>
@@ -2682,7 +2682,7 @@
         <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R9">
         <v>1.46</v>
@@ -2709,7 +2709,7 @@
         <v>11.5</v>
       </c>
       <c r="Z9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA9">
         <v>29</v>
@@ -2778,10 +2778,10 @@
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY9">
         <v>13.5</v>
@@ -2790,19 +2790,19 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB9">
         <v>30</v>
       </c>
       <c r="BC9">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BD9">
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF9">
         <v>20</v>
@@ -2894,7 +2894,7 @@
         <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H10">
         <v>15.5</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2936,7 +2936,7 @@
         <v>2.92</v>
       </c>
       <c r="U10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AC10">
         <v>14.5</v>
@@ -3002,13 +3002,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AR10">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS10">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT10">
         <v>5.1</v>
@@ -3017,10 +3017,10 @@
         <v>11.5</v>
       </c>
       <c r="AV10">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="AW10">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX10">
         <v>5.4</v>
@@ -3029,10 +3029,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BA10">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB10">
         <v>8</v>
@@ -3041,16 +3041,16 @@
         <v>16.5</v>
       </c>
       <c r="BD10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BE10">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>112</v>
       </c>
       <c r="F11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H11">
+        <v>2.26</v>
+      </c>
+      <c r="I11">
         <v>2.3</v>
-      </c>
-      <c r="I11">
-        <v>2.32</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3160,10 +3160,10 @@
         <v>3.15</v>
       </c>
       <c r="O11">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q11">
         <v>2.3</v>
@@ -3175,7 +3175,7 @@
         <v>4.4</v>
       </c>
       <c r="T11">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U11">
         <v>1.95</v>
@@ -3196,16 +3196,16 @@
         <v>13.5</v>
       </c>
       <c r="AA11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB11">
         <v>11.5</v>
       </c>
       <c r="AC11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
         <v>32</v>
@@ -3226,7 +3226,7 @@
         <v>85</v>
       </c>
       <c r="AK11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL11">
         <v>75</v>
@@ -3238,7 +3238,7 @@
         <v>70</v>
       </c>
       <c r="AO11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3250,7 +3250,7 @@
         <v>11.5</v>
       </c>
       <c r="AS11">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11">
         <v>10</v>
@@ -3262,10 +3262,10 @@
         <v>10</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY11">
         <v>13.5</v>
@@ -3274,19 +3274,19 @@
         <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB11">
+        <v>11.5</v>
+      </c>
+      <c r="BC11">
         <v>11</v>
       </c>
-      <c r="BC11">
-        <v>10</v>
-      </c>
       <c r="BD11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF11">
         <v>25</v>
@@ -3322,7 +3322,7 @@
         <v>40</v>
       </c>
       <c r="BQ11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BR11">
         <v>60</v>
@@ -3331,7 +3331,7 @@
         <v>36</v>
       </c>
       <c r="BT11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU11">
         <v>4.4</v>
@@ -3408,19 +3408,19 @@
         <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T12">
         <v>1.69</v>
       </c>
       <c r="U12">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>15.5</v>
       </c>
       <c r="AA12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB12">
         <v>15.5</v>
@@ -3447,7 +3447,7 @@
         <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE12">
         <v>23</v>
@@ -3462,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
         <v>60</v>
@@ -3471,16 +3471,16 @@
         <v>38</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP12">
         <v>14.5</v>
@@ -3489,16 +3489,16 @@
         <v>10</v>
       </c>
       <c r="AR12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT12">
         <v>13</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB12">
         <v>42</v>
@@ -3528,7 +3528,7 @@
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF12">
         <v>23</v>
@@ -3540,7 +3540,7 @@
         <v>3.65</v>
       </c>
       <c r="BI12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12">
         <v>11</v>
@@ -3552,7 +3552,7 @@
         <v>120</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN12">
         <v>6.8</v>
@@ -3564,7 +3564,7 @@
         <v>32</v>
       </c>
       <c r="BQ12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BR12">
         <v>42</v>
@@ -3579,7 +3579,7 @@
         <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW12">
         <v>11.5</v>
@@ -3594,7 +3594,7 @@
         <v>27</v>
       </c>
       <c r="CA12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CB12" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 12:22:20</t>
+    <t>2026-09-29 14:34:15</t>
   </si>
 </sst>
 </file>
@@ -970,16 +970,16 @@
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.26</v>
@@ -994,10 +994,10 @@
         <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
         <v>2.1</v>
@@ -1066,10 +1066,10 @@
         <v>11</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
@@ -1081,7 +1081,7 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AW2">
         <v>1.01</v>
@@ -1099,19 +1099,19 @@
         <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC2">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE2">
         <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1197,7 +1197,7 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G3">
         <v>1.61</v>
@@ -1206,7 +1206,7 @@
         <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>4.2</v>
@@ -1233,19 +1233,19 @@
         <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
         <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W3">
         <v>2.62</v>
@@ -1278,7 +1278,7 @@
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>24</v>
@@ -1287,7 +1287,7 @@
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
@@ -1302,7 +1302,7 @@
         <v>7.4</v>
       </c>
       <c r="AO3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP3">
         <v>17</v>
@@ -1311,22 +1311,22 @@
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="AV3">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AW3">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1338,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
         <v>13</v>
@@ -1350,13 +1350,13 @@
         <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH3">
         <v>4.8</v>
@@ -1457,7 +1457,7 @@
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1505,7 +1505,7 @@
         <v>210</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
         <v>11</v>
@@ -1550,7 +1550,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR4">
         <v>1.01</v>
@@ -1589,22 +1589,22 @@
         <v>16</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE4">
         <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1613,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="BL4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -1634,7 +1634,7 @@
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BT4">
         <v>11</v>
@@ -1649,7 +1649,7 @@
         <v>38</v>
       </c>
       <c r="BX4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY4">
         <v>44</v>
@@ -1681,7 +1681,7 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G5">
         <v>1.2</v>
@@ -1693,49 +1693,49 @@
         <v>29</v>
       </c>
       <c r="J5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
         <v>1.67</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y5">
         <v>65</v>
@@ -1750,7 +1750,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD5">
         <v>110</v>
@@ -1762,43 +1762,43 @@
         <v>6.8</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH5">
         <v>65</v>
       </c>
       <c r="AI5">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
         <v>7.8</v>
       </c>
       <c r="AK5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL5">
         <v>85</v>
       </c>
       <c r="AM5">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
@@ -1810,7 +1810,7 @@
         <v>9.6</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX5">
         <v>5.7</v>
@@ -1822,85 +1822,85 @@
         <v>9</v>
       </c>
       <c r="BA5">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>115</v>
@@ -1923,7 +1923,7 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G6">
         <v>6.8</v>
@@ -1947,28 +1947,28 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1977,22 +1977,22 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
         <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AB6">
         <v>34</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD6">
         <v>9.800000000000001</v>
@@ -2004,7 +2004,7 @@
         <v>65</v>
       </c>
       <c r="AG6">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AH6">
         <v>23</v>
@@ -2022,19 +2022,19 @@
         <v>80</v>
       </c>
       <c r="AM6">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN6">
         <v>85</v>
       </c>
       <c r="AO6">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6">
         <v>9.4</v>
@@ -2043,46 +2043,46 @@
         <v>13</v>
       </c>
       <c r="AT6">
+        <v>22</v>
+      </c>
+      <c r="AU6">
+        <v>9.4</v>
+      </c>
+      <c r="AV6">
+        <v>9</v>
+      </c>
+      <c r="AW6">
+        <v>14.5</v>
+      </c>
+      <c r="AX6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY6">
         <v>20</v>
       </c>
-      <c r="AU6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV6">
-        <v>9.4</v>
-      </c>
-      <c r="AW6">
-        <v>13.5</v>
-      </c>
-      <c r="AX6">
+      <c r="AZ6">
+        <v>17</v>
+      </c>
+      <c r="BA6">
         <v>8</v>
       </c>
-      <c r="AY6">
-        <v>21</v>
-      </c>
-      <c r="AZ6">
-        <v>17.5</v>
-      </c>
-      <c r="BA6">
-        <v>21</v>
-      </c>
       <c r="BB6">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BC6">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD6">
         <v>9.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF6">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH6">
         <v>4.3</v>
@@ -2112,7 +2112,7 @@
         <v>60</v>
       </c>
       <c r="BQ6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BR6">
         <v>60</v>
@@ -2142,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>115</v>
@@ -2198,7 +2198,7 @@
         <v>3.15</v>
       </c>
       <c r="Q7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R7">
         <v>1.86</v>
@@ -2207,10 +2207,10 @@
         <v>2.08</v>
       </c>
       <c r="T7">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2381,7 +2381,7 @@
         <v>50</v>
       </c>
       <c r="BZ7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA7">
         <v>6.2</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U8">
         <v>2.18</v>
@@ -2512,7 +2512,7 @@
         <v>40</v>
       </c>
       <c r="AO8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP8">
         <v>12</v>
@@ -2524,7 +2524,7 @@
         <v>13</v>
       </c>
       <c r="AS8">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8">
         <v>11.5</v>
@@ -2548,7 +2548,7 @@
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB8">
         <v>38</v>
@@ -2560,7 +2560,7 @@
         <v>36</v>
       </c>
       <c r="BE8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
         <v>18</v>
@@ -2649,10 +2649,10 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
         <v>2.16</v>
@@ -2688,13 +2688,13 @@
         <v>1.46</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T9">
         <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>11.5</v>
       </c>
       <c r="Z9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA9">
         <v>29</v>
@@ -2790,7 +2790,7 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
         <v>30</v>
@@ -2802,7 +2802,7 @@
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF9">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         <v>3.8</v>
       </c>
       <c r="BI9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9">
         <v>9</v>
@@ -2844,7 +2844,7 @@
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BT9">
         <v>5.1</v>
@@ -2859,16 +2859,16 @@
         <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BZ9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2891,22 +2891,22 @@
         <v>111</v>
       </c>
       <c r="F10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G10">
         <v>1.32</v>
       </c>
       <c r="H10">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="I10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J10">
         <v>5.3</v>
       </c>
       <c r="K10">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2933,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2945,19 +2945,19 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y10">
         <v>36</v>
       </c>
       <c r="Z10">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC10">
         <v>14.5</v>
@@ -2972,7 +2972,7 @@
         <v>6.4</v>
       </c>
       <c r="AG10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH10">
         <v>65</v>
@@ -2981,7 +2981,7 @@
         <v>470</v>
       </c>
       <c r="AJ10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK10">
         <v>20</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO10">
         <v>1000</v>
@@ -3002,28 +3002,28 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR10">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AS10">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AT10">
         <v>5.1</v>
       </c>
       <c r="AU10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV10">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW10">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AX10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY10">
         <v>10.5</v>
@@ -3032,7 +3032,7 @@
         <v>34</v>
       </c>
       <c r="BA10">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10">
         <v>8</v>
@@ -3041,16 +3041,16 @@
         <v>16.5</v>
       </c>
       <c r="BD10">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE10">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>3.65</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H11">
         <v>2.26</v>
@@ -3163,13 +3163,13 @@
         <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S11">
         <v>4.4</v>
@@ -3196,7 +3196,7 @@
         <v>13.5</v>
       </c>
       <c r="AA11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB11">
         <v>11.5</v>
@@ -3217,7 +3217,7 @@
         <v>16.5</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11">
         <v>55</v>
@@ -3238,7 +3238,7 @@
         <v>70</v>
       </c>
       <c r="AO11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3265,7 +3265,7 @@
         <v>23</v>
       </c>
       <c r="AX11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY11">
         <v>13.5</v>
@@ -3322,7 +3322,7 @@
         <v>40</v>
       </c>
       <c r="BQ11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BR11">
         <v>60</v>
@@ -3331,7 +3331,7 @@
         <v>36</v>
       </c>
       <c r="BT11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU11">
         <v>4.4</v>
@@ -3384,7 +3384,7 @@
         <v>2.26</v>
       </c>
       <c r="I12">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J12">
         <v>3.65</v>
@@ -3399,28 +3399,28 @@
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T12">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>28</v>
       </c>
       <c r="AB12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC12">
         <v>8.4</v>
@@ -3456,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="AG12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
         <v>16</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
         <v>60</v>
@@ -3471,16 +3471,16 @@
         <v>38</v>
       </c>
       <c r="AL12">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP12">
         <v>14.5</v>
@@ -3492,7 +3492,7 @@
         <v>14</v>
       </c>
       <c r="AS12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT12">
         <v>13</v>
@@ -3507,19 +3507,19 @@
         <v>20</v>
       </c>
       <c r="AX12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY12">
         <v>12.5</v>
       </c>
       <c r="AZ12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="BC12">
         <v>32</v>
@@ -3528,13 +3528,13 @@
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF12">
         <v>23</v>
       </c>
       <c r="BG12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH12">
         <v>3.65</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 14:34:15</t>
+    <t>2026-09-29 16:44:36</t>
   </si>
 </sst>
 </file>
@@ -970,10 +970,10 @@
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.05</v>
@@ -1000,7 +1000,7 @@
         <v>1.71</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
         <v>1.32</v>
@@ -1063,7 +1063,7 @@
         <v>46</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
         <v>13.5</v>
@@ -1072,31 +1072,31 @@
         <v>22</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB2">
         <v>18.5</v>
@@ -1108,10 +1108,10 @@
         <v>24</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1230,7 +1230,7 @@
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
         <v>1.51</v>
@@ -1239,13 +1239,13 @@
         <v>2.8</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
         <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
         <v>2.62</v>
@@ -1266,7 +1266,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD3">
         <v>32</v>
@@ -1275,13 +1275,13 @@
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI3">
         <v>100</v>
@@ -1305,28 +1305,28 @@
         <v>120</v>
       </c>
       <c r="AP3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AV3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AW3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1338,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB3">
         <v>13</v>
@@ -1347,25 +1347,25 @@
         <v>14</v>
       </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1383,19 +1383,19 @@
         <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
@@ -1413,7 +1413,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1457,7 +1457,7 @@
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1547,28 +1547,28 @@
         <v>150</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
         <v>15</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="AT4">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1580,31 +1580,31 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
         <v>28</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BF4">
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1613,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="BL4">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -1634,7 +1634,7 @@
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT4">
         <v>11</v>
@@ -1649,7 +1649,7 @@
         <v>38</v>
       </c>
       <c r="BX4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY4">
         <v>44</v>
@@ -1687,13 +1687,13 @@
         <v>1.2</v>
       </c>
       <c r="H5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5">
         <v>29</v>
       </c>
       <c r="J5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K5">
         <v>8.800000000000001</v>
@@ -1726,7 +1726,7 @@
         <v>3.05</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V5">
         <v>1.03</v>
@@ -1747,7 +1747,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
         <v>21</v>
@@ -1765,19 +1765,19 @@
         <v>16</v>
       </c>
       <c r="AH5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AI5">
         <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AK5">
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1795,10 +1795,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
@@ -1807,10 +1807,10 @@
         <v>16.5</v>
       </c>
       <c r="AV5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW5">
         <v>9.6</v>
-      </c>
-      <c r="AW5">
-        <v>9.4</v>
       </c>
       <c r="AX5">
         <v>5.7</v>
@@ -1819,10 +1819,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1831,37 +1831,37 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF5">
         <v>3.55</v>
       </c>
       <c r="BG5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH5">
         <v>5.1</v>
       </c>
       <c r="BI5">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO5">
         <v>2.96</v>
@@ -1870,34 +1870,34 @@
         <v>6.2</v>
       </c>
       <c r="BQ5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="BW5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX5">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CA5">
         <v>7</v>
@@ -1926,7 +1926,7 @@
         <v>6.4</v>
       </c>
       <c r="G6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H6">
         <v>1.56</v>
@@ -1938,148 +1938,148 @@
         <v>4.8</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q6">
         <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U6">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
         <v>23</v>
       </c>
       <c r="Y6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA6">
         <v>15</v>
       </c>
       <c r="AB6">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AC6">
         <v>11</v>
       </c>
       <c r="AD6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE6">
+        <v>15</v>
+      </c>
+      <c r="AF6">
+        <v>55</v>
+      </c>
+      <c r="AG6">
+        <v>24</v>
+      </c>
+      <c r="AH6">
+        <v>20</v>
+      </c>
+      <c r="AI6">
+        <v>29</v>
+      </c>
+      <c r="AJ6">
+        <v>180</v>
+      </c>
+      <c r="AK6">
+        <v>85</v>
+      </c>
+      <c r="AL6">
+        <v>70</v>
+      </c>
+      <c r="AM6">
+        <v>90</v>
+      </c>
+      <c r="AN6">
+        <v>75</v>
+      </c>
+      <c r="AO6">
+        <v>6.4</v>
+      </c>
+      <c r="AP6">
+        <v>21</v>
+      </c>
+      <c r="AQ6">
+        <v>10</v>
+      </c>
+      <c r="AR6">
+        <v>9.6</v>
+      </c>
+      <c r="AS6">
+        <v>14</v>
+      </c>
+      <c r="AT6">
+        <v>24</v>
+      </c>
+      <c r="AU6">
+        <v>10</v>
+      </c>
+      <c r="AV6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW6">
+        <v>14</v>
+      </c>
+      <c r="AX6">
+        <v>50</v>
+      </c>
+      <c r="AY6">
+        <v>22</v>
+      </c>
+      <c r="AZ6">
         <v>18</v>
       </c>
-      <c r="AF6">
+      <c r="BA6">
+        <v>26</v>
+      </c>
+      <c r="BB6">
+        <v>25</v>
+      </c>
+      <c r="BC6">
         <v>65</v>
       </c>
-      <c r="AG6">
-        <v>23</v>
-      </c>
-      <c r="AH6">
-        <v>23</v>
-      </c>
-      <c r="AI6">
-        <v>36</v>
-      </c>
-      <c r="AJ6">
-        <v>200</v>
-      </c>
-      <c r="AK6">
-        <v>95</v>
-      </c>
-      <c r="AL6">
-        <v>80</v>
-      </c>
-      <c r="AM6">
-        <v>95</v>
-      </c>
-      <c r="AN6">
-        <v>85</v>
-      </c>
-      <c r="AO6">
-        <v>7.2</v>
-      </c>
-      <c r="AP6">
-        <v>19.5</v>
-      </c>
-      <c r="AQ6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR6">
-        <v>9.4</v>
-      </c>
-      <c r="AS6">
-        <v>13</v>
-      </c>
-      <c r="AT6">
-        <v>22</v>
-      </c>
-      <c r="AU6">
-        <v>9.4</v>
-      </c>
-      <c r="AV6">
-        <v>9</v>
-      </c>
-      <c r="AW6">
-        <v>14.5</v>
-      </c>
-      <c r="AX6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY6">
-        <v>20</v>
-      </c>
-      <c r="AZ6">
-        <v>17</v>
-      </c>
-      <c r="BA6">
-        <v>8</v>
-      </c>
-      <c r="BB6">
-        <v>9.6</v>
-      </c>
-      <c r="BC6">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BD6">
-        <v>9.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="BE6">
-        <v>9.4</v>
+        <v>70</v>
       </c>
       <c r="BF6">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BG6">
         <v>6</v>
@@ -2100,7 +2100,7 @@
         <v>120</v>
       </c>
       <c r="BM6">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="BN6">
         <v>12</v>
@@ -2112,7 +2112,7 @@
         <v>60</v>
       </c>
       <c r="BQ6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BR6">
         <v>60</v>
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
         <v>9.800000000000001</v>
@@ -2174,7 +2174,7 @@
         <v>13</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J7">
         <v>6.8</v>
@@ -2183,13 +2183,13 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M7">
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O7">
         <v>1.14</v>
@@ -2201,112 +2201,112 @@
         <v>1.43</v>
       </c>
       <c r="R7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S7">
         <v>2.08</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U7">
         <v>2.1</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y7">
         <v>55</v>
       </c>
       <c r="Z7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA7">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD7">
         <v>46</v>
       </c>
       <c r="AE7">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AF7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ7">
         <v>11</v>
       </c>
       <c r="AK7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7">
         <v>3.7</v>
       </c>
       <c r="AO7">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AP7">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AQ7">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AR7">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AS7">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AT7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AW7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA7">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BB7">
         <v>9.800000000000001</v>
@@ -2315,19 +2315,19 @@
         <v>11.5</v>
       </c>
       <c r="BD7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE7">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF7">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BG7">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BH7">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BI7">
         <v>4.6</v>
@@ -2342,7 +2342,7 @@
         <v>140</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN7">
         <v>4.1</v>
@@ -2351,7 +2351,7 @@
         <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BQ7">
         <v>6</v>
@@ -2360,10 +2360,10 @@
         <v>24</v>
       </c>
       <c r="BS7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BT7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BU7">
         <v>12.5</v>
@@ -2372,16 +2372,16 @@
         <v>110</v>
       </c>
       <c r="BW7">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="BX7">
         <v>85</v>
       </c>
       <c r="BY7">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="BZ7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA7">
         <v>6.2</v>
@@ -2416,7 +2416,7 @@
         <v>2.36</v>
       </c>
       <c r="I8">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J8">
         <v>3.55</v>
@@ -2425,16 +2425,16 @@
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
         <v>1.93</v>
@@ -2443,34 +2443,34 @@
         <v>2</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y8">
         <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB8">
         <v>13.5</v>
@@ -2479,19 +2479,19 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
         <v>40</v>
@@ -2500,16 +2500,16 @@
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>100</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO8">
         <v>20</v>
@@ -2518,115 +2518,115 @@
         <v>12</v>
       </c>
       <c r="AQ8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS8">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AT8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>10</v>
       </c>
       <c r="AW8">
+        <v>22</v>
+      </c>
+      <c r="AX8">
         <v>21</v>
       </c>
-      <c r="AX8">
-        <v>20</v>
-      </c>
       <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
+        <v>15.5</v>
+      </c>
+      <c r="BA8">
+        <v>34</v>
+      </c>
+      <c r="BB8">
+        <v>50</v>
+      </c>
+      <c r="BC8">
+        <v>34</v>
+      </c>
+      <c r="BD8">
+        <v>44</v>
+      </c>
+      <c r="BE8">
         <v>12.5</v>
       </c>
-      <c r="AZ8">
-        <v>15</v>
-      </c>
-      <c r="BA8">
-        <v>8.4</v>
-      </c>
-      <c r="BB8">
+      <c r="BF8">
+        <v>32</v>
+      </c>
+      <c r="BG8">
+        <v>17.5</v>
+      </c>
+      <c r="BH8">
+        <v>3.65</v>
+      </c>
+      <c r="BI8">
+        <v>2.8</v>
+      </c>
+      <c r="BJ8">
+        <v>11.5</v>
+      </c>
+      <c r="BK8">
+        <v>7.2</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>21</v>
+      </c>
+      <c r="BN8">
+        <v>7.8</v>
+      </c>
+      <c r="BO8">
+        <v>5.1</v>
+      </c>
+      <c r="BP8">
         <v>38</v>
       </c>
-      <c r="BC8">
-        <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>36</v>
-      </c>
-      <c r="BE8">
-        <v>9.6</v>
-      </c>
-      <c r="BF8">
-        <v>18</v>
-      </c>
-      <c r="BG8">
-        <v>17</v>
-      </c>
-      <c r="BH8">
-        <v>0</v>
-      </c>
-      <c r="BI8">
-        <v>0</v>
-      </c>
-      <c r="BJ8">
-        <v>0</v>
-      </c>
-      <c r="BK8">
-        <v>0</v>
-      </c>
-      <c r="BL8">
-        <v>0</v>
-      </c>
-      <c r="BM8">
-        <v>0</v>
-      </c>
-      <c r="BN8">
-        <v>0</v>
-      </c>
-      <c r="BO8">
-        <v>0</v>
-      </c>
-      <c r="BP8">
-        <v>0</v>
-      </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CB8" t="s">
         <v>115</v>
@@ -2649,13 +2649,13 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G9">
         <v>3.6</v>
       </c>
       <c r="H9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I9">
         <v>2.2</v>
@@ -2667,7 +2667,7 @@
         <v>3.85</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -2694,16 +2694,16 @@
         <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y9">
         <v>11.5</v>
@@ -2712,7 +2712,7 @@
         <v>15</v>
       </c>
       <c r="AA9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB9">
         <v>15.5</v>
@@ -2736,22 +2736,22 @@
         <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AK9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL9">
         <v>44</v>
       </c>
       <c r="AM9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO9">
         <v>13.5</v>
@@ -2766,10 +2766,10 @@
         <v>13</v>
       </c>
       <c r="AS9">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AT9">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
@@ -2781,40 +2781,40 @@
         <v>19</v>
       </c>
       <c r="AX9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY9">
         <v>13.5</v>
       </c>
       <c r="AZ9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BB9">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BC9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BG9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH9">
         <v>3.8</v>
       </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
         <v>9</v>
@@ -2826,7 +2826,7 @@
         <v>110</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN9">
         <v>7</v>
@@ -2844,16 +2844,16 @@
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT9">
         <v>5.1</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW9">
         <v>12.5</v>
@@ -2862,13 +2862,13 @@
         <v>30</v>
       </c>
       <c r="BY9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BZ9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2894,7 +2894,7 @@
         <v>1.31</v>
       </c>
       <c r="G10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H10">
         <v>14.5</v>
@@ -2906,43 +2906,43 @@
         <v>5.3</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
         <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
         <v>1.44</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X10">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>14.5</v>
@@ -3002,16 +3002,16 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR10">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU10">
         <v>12</v>
@@ -3020,7 +3020,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX10">
         <v>5.3</v>
@@ -3032,85 +3032,85 @@
         <v>34</v>
       </c>
       <c r="BA10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10">
         <v>8</v>
       </c>
       <c r="BC10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3133,7 +3133,7 @@
         <v>112</v>
       </c>
       <c r="F11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G11">
         <v>3.75</v>
@@ -3142,7 +3142,7 @@
         <v>2.26</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3151,7 +3151,7 @@
         <v>3.45</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3166,7 +3166,7 @@
         <v>1.73</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
         <v>1.26</v>
@@ -3181,22 +3181,22 @@
         <v>1.95</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y11">
         <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB11">
         <v>11.5</v>
@@ -3208,37 +3208,37 @@
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ11">
         <v>85</v>
       </c>
       <c r="AK11">
+        <v>55</v>
+      </c>
+      <c r="AL11">
         <v>70</v>
       </c>
-      <c r="AL11">
-        <v>75</v>
-      </c>
       <c r="AM11">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3250,49 +3250,49 @@
         <v>11.5</v>
       </c>
       <c r="AS11">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AT11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA11">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BB11">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BC11">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BD11">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BE11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BF11">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BG11">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BH11">
         <v>3</v>
@@ -3310,7 +3310,7 @@
         <v>190</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN11">
         <v>7</v>
@@ -3393,49 +3393,49 @@
         <v>3.7</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M12">
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
         <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U12">
         <v>2.36</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X12">
         <v>17</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA12">
         <v>28</v>
@@ -3447,31 +3447,31 @@
         <v>8.4</v>
       </c>
       <c r="AD12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF12">
         <v>26</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12">
         <v>16</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM12">
         <v>75</v>
@@ -3480,22 +3480,22 @@
         <v>32</v>
       </c>
       <c r="AO12">
+        <v>15</v>
+      </c>
+      <c r="AP12">
         <v>15.5</v>
       </c>
-      <c r="AP12">
-        <v>14.5</v>
-      </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR12">
         <v>14</v>
       </c>
       <c r="AS12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AT12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU12">
         <v>7.8</v>
@@ -3507,31 +3507,31 @@
         <v>20</v>
       </c>
       <c r="AX12">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AY12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BB12">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="BC12">
         <v>32</v>
       </c>
       <c r="BD12">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE12">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BF12">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BG12">
         <v>13.5</v>
@@ -3552,7 +3552,7 @@
         <v>120</v>
       </c>
       <c r="BM12">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>6.8</v>
@@ -3564,7 +3564,7 @@
         <v>32</v>
       </c>
       <c r="BQ12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BR12">
         <v>42</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 16:44:36</t>
+    <t>2026-09-29 18:55:09</t>
   </si>
 </sst>
 </file>
@@ -973,10 +973,10 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
         <v>4.1</v>
@@ -985,22 +985,22 @@
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S2">
         <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.32</v>
@@ -1009,22 +1009,22 @@
         <v>1.92</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA2">
         <v>90</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2">
         <v>19</v>
@@ -1033,13 +1033,13 @@
         <v>55</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>60</v>
@@ -1057,16 +1057,16 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>46</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2">
         <v>22</v>
@@ -1075,7 +1075,7 @@
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
@@ -1093,7 +1093,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA2">
         <v>36</v>
@@ -1102,7 +1102,7 @@
         <v>18.5</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BD2">
         <v>24</v>
@@ -1206,7 +1206,7 @@
         <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
         <v>4.2</v>
@@ -1221,7 +1221,7 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
         <v>1.24</v>
@@ -1230,28 +1230,28 @@
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T3">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y3">
         <v>32</v>
@@ -1263,7 +1263,7 @@
         <v>230</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3">
         <v>12.5</v>
@@ -1275,19 +1275,19 @@
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI3">
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
@@ -1305,52 +1305,52 @@
         <v>120</v>
       </c>
       <c r="AP3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
         <v>21</v>
       </c>
       <c r="AR3">
+        <v>5.9</v>
+      </c>
+      <c r="AS3">
+        <v>6.2</v>
+      </c>
+      <c r="AT3">
+        <v>8.6</v>
+      </c>
+      <c r="AU3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>5.7</v>
+      </c>
+      <c r="AW3">
         <v>6</v>
-      </c>
-      <c r="AS3">
-        <v>5.9</v>
-      </c>
-      <c r="AT3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU3">
-        <v>9</v>
-      </c>
-      <c r="AV3">
-        <v>5.8</v>
-      </c>
-      <c r="AW3">
-        <v>7.2</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
         <v>13</v>
       </c>
       <c r="BC3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
@@ -1359,13 +1359,13 @@
         <v>7</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1383,19 +1383,19 @@
         <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
@@ -1413,7 +1413,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1457,7 +1457,7 @@
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1601,7 +1601,7 @@
         <v>85</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
         <v>2.94</v>
@@ -1684,10 +1684,10 @@
         <v>1.18</v>
       </c>
       <c r="G5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5">
         <v>29</v>
@@ -1699,28 +1699,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
         <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
         <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
         <v>3.05</v>
@@ -1732,13 +1732,13 @@
         <v>1.03</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X5">
         <v>24</v>
       </c>
       <c r="Y5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Z5">
         <v>380</v>
@@ -1747,13 +1747,13 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>21</v>
       </c>
       <c r="AD5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1771,7 +1771,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AK5">
         <v>18</v>
@@ -1792,13 +1792,13 @@
         <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR5">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>7.2</v>
@@ -1807,22 +1807,22 @@
         <v>16.5</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY5">
         <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BA5">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1831,16 +1831,16 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
+        <v>7.8</v>
+      </c>
+      <c r="BE5">
         <v>8.6</v>
       </c>
-      <c r="BE5">
-        <v>9.6</v>
-      </c>
       <c r="BF5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
         <v>5.1</v>
@@ -1855,7 +1855,7 @@
         <v>5.2</v>
       </c>
       <c r="BL5">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="BM5">
         <v>6.8</v>
@@ -1885,13 +1885,13 @@
         <v>5.7</v>
       </c>
       <c r="BV5">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="BW5">
         <v>6.8</v>
       </c>
       <c r="BX5">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="BY5">
         <v>6.8</v>
@@ -1923,10 +1923,10 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H6">
         <v>1.56</v>
@@ -1935,13 +1935,13 @@
         <v>1.57</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -1953,22 +1953,22 @@
         <v>1.21</v>
       </c>
       <c r="P6">
+        <v>2.52</v>
+      </c>
+      <c r="Q6">
+        <v>1.61</v>
+      </c>
+      <c r="R6">
+        <v>1.6</v>
+      </c>
+      <c r="S6">
         <v>2.48</v>
       </c>
-      <c r="Q6">
-        <v>1.64</v>
-      </c>
-      <c r="R6">
-        <v>1.58</v>
-      </c>
-      <c r="S6">
-        <v>2.56</v>
-      </c>
       <c r="T6">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>2.74</v>
@@ -1977,19 +1977,19 @@
         <v>1.17</v>
       </c>
       <c r="X6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA6">
         <v>15</v>
       </c>
       <c r="AB6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC6">
         <v>11</v>
@@ -2001,22 +2001,22 @@
         <v>15</v>
       </c>
       <c r="AF6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH6">
         <v>20</v>
       </c>
       <c r="AI6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ6">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL6">
         <v>70</v>
@@ -2025,7 +2025,7 @@
         <v>90</v>
       </c>
       <c r="AN6">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AO6">
         <v>6.4</v>
@@ -2034,10 +2034,10 @@
         <v>21</v>
       </c>
       <c r="AQ6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
         <v>14</v>
@@ -2052,7 +2052,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX6">
         <v>50</v>
@@ -2061,28 +2061,28 @@
         <v>22</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB6">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BC6">
         <v>65</v>
       </c>
       <c r="BD6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE6">
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BG6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH6">
         <v>4.3</v>
@@ -2094,7 +2094,7 @@
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6">
         <v>120</v>
@@ -2106,7 +2106,7 @@
         <v>12</v>
       </c>
       <c r="BO6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP6">
         <v>60</v>
@@ -2127,7 +2127,7 @@
         <v>4</v>
       </c>
       <c r="BV6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BW6">
         <v>8.4</v>
@@ -2136,13 +2136,13 @@
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BZ6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>115</v>
@@ -2165,16 +2165,16 @@
         <v>108</v>
       </c>
       <c r="F7">
+        <v>1.27</v>
+      </c>
+      <c r="G7">
         <v>1.28</v>
       </c>
-      <c r="G7">
-        <v>1.29</v>
-      </c>
       <c r="H7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="I7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="J7">
         <v>6.8</v>
@@ -2183,7 +2183,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M7">
         <v>1.02</v>
@@ -2195,28 +2195,28 @@
         <v>1.14</v>
       </c>
       <c r="P7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T7">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="X7">
         <v>36</v>
@@ -2228,7 +2228,7 @@
         <v>140</v>
       </c>
       <c r="AA7">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="AB7">
         <v>13</v>
@@ -2237,22 +2237,22 @@
         <v>16</v>
       </c>
       <c r="AD7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE7">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ7">
         <v>11</v>
@@ -2267,22 +2267,22 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AO7">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AP7">
         <v>30</v>
       </c>
       <c r="AQ7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR7">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AS7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2294,97 +2294,97 @@
         <v>38</v>
       </c>
       <c r="AW7">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA7">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BB7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC7">
         <v>11.5</v>
       </c>
       <c r="BD7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BG7">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BH7">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI7">
+        <v>4</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>8</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
         <v>4.6</v>
       </c>
-      <c r="BJ7">
-        <v>14</v>
-      </c>
-      <c r="BK7">
-        <v>10</v>
-      </c>
-      <c r="BL7">
-        <v>140</v>
-      </c>
-      <c r="BM7">
-        <v>21</v>
-      </c>
-      <c r="BN7">
-        <v>4.1</v>
-      </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BP7">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BQ7">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BR7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BT7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BV7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>115</v>
@@ -2410,10 +2410,10 @@
         <v>3.35</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H8">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="I8">
         <v>2.38</v>
@@ -2425,25 +2425,25 @@
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
         <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
         <v>3.6</v>
@@ -2455,10 +2455,10 @@
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X8">
         <v>14</v>
@@ -2488,7 +2488,7 @@
         <v>24</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
@@ -2500,19 +2500,19 @@
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM8">
         <v>100</v>
       </c>
       <c r="AN8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP8">
         <v>12</v>
@@ -2521,10 +2521,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT8">
         <v>12</v>
@@ -2557,16 +2557,16 @@
         <v>34</v>
       </c>
       <c r="BD8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF8">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BG8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH8">
         <v>3.65</v>
@@ -2578,7 +2578,7 @@
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2626,7 +2626,7 @@
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CB8" t="s">
         <v>115</v>
@@ -2655,46 +2655,46 @@
         <v>3.6</v>
       </c>
       <c r="H9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
         <v>2.2</v>
       </c>
       <c r="J9">
+        <v>3.75</v>
+      </c>
+      <c r="K9">
         <v>3.8</v>
       </c>
-      <c r="K9">
-        <v>3.85</v>
-      </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V9">
         <v>1.83</v>
@@ -2703,37 +2703,37 @@
         <v>1.38</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z9">
         <v>15</v>
       </c>
       <c r="AA9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB9">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC9">
         <v>8.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI9">
         <v>32</v>
@@ -2742,10 +2742,10 @@
         <v>65</v>
       </c>
       <c r="AK9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM9">
         <v>75</v>
@@ -2754,16 +2754,16 @@
         <v>32</v>
       </c>
       <c r="AO9">
+        <v>13</v>
+      </c>
+      <c r="AP9">
+        <v>16</v>
+      </c>
+      <c r="AQ9">
+        <v>10.5</v>
+      </c>
+      <c r="AR9">
         <v>13.5</v>
-      </c>
-      <c r="AP9">
-        <v>15</v>
-      </c>
-      <c r="AQ9">
-        <v>10</v>
-      </c>
-      <c r="AR9">
-        <v>13</v>
       </c>
       <c r="AS9">
         <v>24</v>
@@ -2772,7 +2772,7 @@
         <v>15</v>
       </c>
       <c r="AU9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9">
         <v>10</v>
@@ -2790,37 +2790,37 @@
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB9">
         <v>55</v>
       </c>
       <c r="BC9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="BF9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BG9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
         <v>3.8</v>
       </c>
       <c r="BI9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ9">
         <v>9</v>
       </c>
       <c r="BK9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL9">
         <v>110</v>
@@ -2835,7 +2835,7 @@
         <v>6.2</v>
       </c>
       <c r="BP9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ9">
         <v>20</v>
@@ -2847,19 +2847,19 @@
         <v>25</v>
       </c>
       <c r="BT9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU9">
         <v>4.7</v>
       </c>
       <c r="BV9">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW9">
         <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BY9">
         <v>19</v>
@@ -2891,22 +2891,22 @@
         <v>111</v>
       </c>
       <c r="F10">
+        <v>1.29</v>
+      </c>
+      <c r="G10">
         <v>1.31</v>
       </c>
-      <c r="G10">
-        <v>1.33</v>
-      </c>
       <c r="H10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="I10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K10">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2915,10 +2915,10 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
         <v>1.79</v>
@@ -2927,25 +2927,25 @@
         <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V10">
         <v>1.06</v>
       </c>
       <c r="W10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X10">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y10">
         <v>36</v>
@@ -2963,10 +2963,10 @@
         <v>14.5</v>
       </c>
       <c r="AD10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="AF10">
         <v>6.4</v>
@@ -2975,22 +2975,22 @@
         <v>13</v>
       </c>
       <c r="AH10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI10">
         <v>470</v>
       </c>
       <c r="AJ10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AN10">
         <v>7.6</v>
@@ -3002,28 +3002,28 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AR10">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AS10">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT10">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU10">
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AW10">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX10">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AY10">
         <v>10.5</v>
@@ -3032,7 +3032,7 @@
         <v>34</v>
       </c>
       <c r="BA10">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BB10">
         <v>8</v>
@@ -3041,16 +3041,16 @@
         <v>17</v>
       </c>
       <c r="BD10">
-        <v>8.4</v>
+        <v>60</v>
       </c>
       <c r="BE10">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3133,16 +3133,16 @@
         <v>112</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G11">
         <v>3.75</v>
       </c>
       <c r="H11">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3154,7 +3154,7 @@
         <v>1.5</v>
       </c>
       <c r="M11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
         <v>3.15</v>
@@ -3163,28 +3163,28 @@
         <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
         <v>2.32</v>
       </c>
       <c r="R11">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
         <v>4.4</v>
       </c>
       <c r="T11">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U11">
         <v>1.95</v>
       </c>
       <c r="V11">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X11">
         <v>11</v>
@@ -3193,7 +3193,7 @@
         <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA11">
         <v>32</v>
@@ -3208,13 +3208,13 @@
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF11">
         <v>25</v>
       </c>
       <c r="AG11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH11">
         <v>21</v>
@@ -3223,25 +3223,25 @@
         <v>50</v>
       </c>
       <c r="AJ11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK11">
         <v>55</v>
       </c>
       <c r="AL11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM11">
         <v>150</v>
       </c>
       <c r="AN11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO11">
         <v>25</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
         <v>7.6</v>
@@ -3256,7 +3256,7 @@
         <v>11</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
         <v>10.5</v>
@@ -3265,10 +3265,10 @@
         <v>24</v>
       </c>
       <c r="AX11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY11">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11">
         <v>19</v>
@@ -3280,13 +3280,13 @@
         <v>55</v>
       </c>
       <c r="BC11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD11">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="BE11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF11">
         <v>50</v>
@@ -3375,94 +3375,94 @@
         <v>113</v>
       </c>
       <c r="F12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H12">
+        <v>2.22</v>
+      </c>
+      <c r="I12">
         <v>2.26</v>
       </c>
-      <c r="I12">
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
+        <v>3.75</v>
+      </c>
+      <c r="L12">
+        <v>1.31</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.6</v>
+      </c>
+      <c r="O12">
+        <v>1.24</v>
+      </c>
+      <c r="P12">
         <v>2.28</v>
       </c>
-      <c r="J12">
-        <v>3.65</v>
-      </c>
-      <c r="K12">
-        <v>3.7</v>
-      </c>
-      <c r="L12">
-        <v>1.35</v>
-      </c>
-      <c r="M12">
-        <v>1.06</v>
-      </c>
-      <c r="N12">
-        <v>4.3</v>
-      </c>
-      <c r="O12">
-        <v>1.28</v>
-      </c>
-      <c r="P12">
-        <v>2.16</v>
-      </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="U12">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="V12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W12">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X12">
+        <v>18</v>
+      </c>
+      <c r="Y12">
+        <v>12</v>
+      </c>
+      <c r="Z12">
+        <v>15.5</v>
+      </c>
+      <c r="AA12">
+        <v>27</v>
+      </c>
+      <c r="AB12">
         <v>17</v>
       </c>
-      <c r="Y12">
-        <v>11</v>
-      </c>
-      <c r="Z12">
-        <v>15</v>
-      </c>
-      <c r="AA12">
-        <v>28</v>
-      </c>
-      <c r="AB12">
-        <v>15</v>
-      </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12">
         <v>26</v>
       </c>
       <c r="AG12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ12">
         <v>60</v>
@@ -3471,88 +3471,88 @@
         <v>36</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO12">
+        <v>13.5</v>
+      </c>
+      <c r="AP12">
+        <v>16.5</v>
+      </c>
+      <c r="AQ12">
+        <v>11.5</v>
+      </c>
+      <c r="AR12">
         <v>15</v>
       </c>
-      <c r="AP12">
-        <v>15.5</v>
-      </c>
-      <c r="AQ12">
-        <v>10.5</v>
-      </c>
-      <c r="AR12">
-        <v>14</v>
-      </c>
       <c r="AS12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT12">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY12">
         <v>13</v>
       </c>
       <c r="AZ12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC12">
         <v>32</v>
       </c>
       <c r="BD12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE12">
-        <v>18.5</v>
+        <v>50</v>
       </c>
       <c r="BF12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH12">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BI12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BK12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN12">
         <v>6.8</v>
@@ -3561,13 +3561,13 @@
         <v>6</v>
       </c>
       <c r="BP12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BR12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS12">
         <v>24</v>
@@ -3579,19 +3579,19 @@
         <v>4.8</v>
       </c>
       <c r="BV12">
+        <v>15.5</v>
+      </c>
+      <c r="BW12">
+        <v>13</v>
+      </c>
+      <c r="BX12">
+        <v>32</v>
+      </c>
+      <c r="BY12">
         <v>19</v>
       </c>
-      <c r="BW12">
-        <v>11.5</v>
-      </c>
-      <c r="BX12">
-        <v>34</v>
-      </c>
-      <c r="BY12">
-        <v>19.5</v>
-      </c>
       <c r="BZ12">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CA12">
         <v>15.5</v>
@@ -3617,226 +3617,226 @@
         <v>114</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
-        <v>920</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 18:55:09</t>
+    <t>2026-09-29 21:05:23</t>
   </si>
 </sst>
 </file>
@@ -955,25 +955,25 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H2">
+        <v>3.6</v>
+      </c>
+      <c r="I2">
+        <v>3.95</v>
+      </c>
+      <c r="J2">
         <v>3.7</v>
-      </c>
-      <c r="I2">
-        <v>4.1</v>
-      </c>
-      <c r="J2">
-        <v>3.85</v>
       </c>
       <c r="K2">
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -982,67 +982,67 @@
         <v>4.1</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
         <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
         <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>19</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>29</v>
@@ -1057,10 +1057,10 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP2">
         <v>14.5</v>
@@ -1069,49 +1069,49 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC2">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1200,19 +1200,19 @@
         <v>1.57</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H3">
         <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1236,37 +1236,37 @@
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X3">
         <v>23</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z3">
         <v>75</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB3">
         <v>10</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD3">
         <v>32</v>
@@ -1284,10 +1284,10 @@
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
@@ -1305,28 +1305,28 @@
         <v>120</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3">
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
         <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AV3">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1335,10 +1335,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB3">
         <v>13</v>
@@ -1347,25 +1347,25 @@
         <v>13.5</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1383,19 +1383,19 @@
         <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
@@ -1413,7 +1413,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1451,13 +1451,13 @@
         <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1478,10 +1478,10 @@
         <v>1.32</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
         <v>1.89</v>
@@ -1508,7 +1508,7 @@
         <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>28</v>
@@ -1547,28 +1547,28 @@
         <v>150</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
@@ -1580,31 +1580,31 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD4">
         <v>28</v>
       </c>
       <c r="BE4">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1684,10 +1684,10 @@
         <v>1.18</v>
       </c>
       <c r="G5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>29</v>
@@ -1702,7 +1702,7 @@
         <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
         <v>4.8</v>
@@ -1723,7 +1723,7 @@
         <v>2.58</v>
       </c>
       <c r="T5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
         <v>1.43</v>
@@ -1732,7 +1732,7 @@
         <v>1.03</v>
       </c>
       <c r="W5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -1753,7 +1753,7 @@
         <v>21</v>
       </c>
       <c r="AD5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1777,7 +1777,7 @@
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1798,31 +1798,31 @@
         <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV5">
         <v>8.800000000000001</v>
       </c>
       <c r="AW5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX5">
+        <v>5.6</v>
+      </c>
+      <c r="AY5">
+        <v>13</v>
+      </c>
+      <c r="AZ5">
         <v>8.6</v>
       </c>
-      <c r="AX5">
-        <v>5.5</v>
-      </c>
-      <c r="AY5">
-        <v>12.5</v>
-      </c>
-      <c r="AZ5">
-        <v>8.4</v>
-      </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1831,16 +1831,16 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
         <v>3.45</v>
       </c>
       <c r="BG5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>5.1</v>
@@ -1849,16 +1849,16 @@
         <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL5">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BN5">
         <v>3.45</v>
@@ -1867,7 +1867,7 @@
         <v>2.96</v>
       </c>
       <c r="BP5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BQ5">
         <v>5</v>
@@ -1876,25 +1876,25 @@
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BT5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="BW5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX5">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BY5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
         <v>11</v>
@@ -1929,49 +1929,49 @@
         <v>6.8</v>
       </c>
       <c r="H6">
+        <v>1.55</v>
+      </c>
+      <c r="I6">
         <v>1.56</v>
       </c>
-      <c r="I6">
-        <v>1.57</v>
-      </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6">
         <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q6">
         <v>1.61</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T6">
         <v>1.75</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W6">
         <v>1.17</v>
@@ -1986,7 +1986,7 @@
         <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB6">
         <v>28</v>
@@ -2022,13 +2022,13 @@
         <v>70</v>
       </c>
       <c r="AM6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN6">
         <v>90</v>
       </c>
       <c r="AO6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP6">
         <v>21</v>
@@ -2040,16 +2040,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU6">
         <v>10</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
         <v>13.5</v>
@@ -2067,7 +2067,7 @@
         <v>25</v>
       </c>
       <c r="BB6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC6">
         <v>65</v>
@@ -2082,19 +2082,19 @@
         <v>65</v>
       </c>
       <c r="BG6">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
         <v>4.3</v>
       </c>
       <c r="BI6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL6">
         <v>120</v>
@@ -2121,25 +2121,25 @@
         <v>32</v>
       </c>
       <c r="BT6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU6">
         <v>4</v>
       </c>
       <c r="BV6">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BW6">
         <v>8.4</v>
       </c>
       <c r="BX6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY6">
         <v>17</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA6">
         <v>9.6</v>
@@ -2171,19 +2171,19 @@
         <v>1.28</v>
       </c>
       <c r="H7">
+        <v>13.5</v>
+      </c>
+      <c r="I7">
         <v>14.5</v>
       </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
       <c r="J7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K7">
         <v>7</v>
       </c>
       <c r="L7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M7">
         <v>1.02</v>
@@ -2195,7 +2195,7 @@
         <v>1.14</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q7">
         <v>1.45</v>
@@ -2207,16 +2207,16 @@
         <v>2.1</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
         <v>1.07</v>
       </c>
       <c r="W7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="X7">
         <v>36</v>
@@ -2228,7 +2228,7 @@
         <v>140</v>
       </c>
       <c r="AA7">
-        <v>530</v>
+        <v>610</v>
       </c>
       <c r="AB7">
         <v>13</v>
@@ -2240,16 +2240,16 @@
         <v>48</v>
       </c>
       <c r="AE7">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7">
         <v>140</v>
@@ -2270,16 +2270,16 @@
         <v>3.6</v>
       </c>
       <c r="AO7">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AP7">
         <v>30</v>
       </c>
       <c r="AQ7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS7">
         <v>16</v>
@@ -2294,10 +2294,10 @@
         <v>38</v>
       </c>
       <c r="AW7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2306,7 +2306,7 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB7">
         <v>9.6</v>
@@ -2315,10 +2315,10 @@
         <v>11.5</v>
       </c>
       <c r="BD7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF7">
         <v>3.4</v>
@@ -2330,7 +2330,7 @@
         <v>6.2</v>
       </c>
       <c r="BI7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2354,7 +2354,7 @@
         <v>9</v>
       </c>
       <c r="BQ7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2410,10 +2410,10 @@
         <v>3.35</v>
       </c>
       <c r="G8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
         <v>2.38</v>
@@ -2425,13 +2425,13 @@
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O8">
         <v>1.33</v>
@@ -2440,16 +2440,16 @@
         <v>1.92</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
         <v>1.36</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U8">
         <v>2.18</v>
@@ -2458,16 +2458,16 @@
         <v>1.72</v>
       </c>
       <c r="W8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
         <v>14</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>32</v>
@@ -2488,7 +2488,7 @@
         <v>24</v>
       </c>
       <c r="AG8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
@@ -2500,31 +2500,31 @@
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM8">
         <v>100</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP8">
         <v>12</v>
       </c>
       <c r="AQ8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR8">
         <v>13</v>
       </c>
       <c r="AS8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT8">
         <v>12</v>
@@ -2533,7 +2533,7 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW8">
         <v>22</v>
@@ -2560,25 +2560,25 @@
         <v>42</v>
       </c>
       <c r="BE8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF8">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BG8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH8">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2590,7 +2590,7 @@
         <v>7.8</v>
       </c>
       <c r="BO8">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP8">
         <v>38</v>
@@ -2626,7 +2626,7 @@
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CB8" t="s">
         <v>115</v>
@@ -2673,7 +2673,7 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O9">
         <v>1.26</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="Z9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA9">
         <v>27</v>
@@ -2757,7 +2757,7 @@
         <v>13</v>
       </c>
       <c r="AP9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
@@ -2802,13 +2802,13 @@
         <v>36</v>
       </c>
       <c r="BE9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF9">
         <v>26</v>
       </c>
       <c r="BG9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH9">
         <v>3.8</v>
@@ -2835,7 +2835,7 @@
         <v>6.2</v>
       </c>
       <c r="BP9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BQ9">
         <v>20</v>
@@ -2856,19 +2856,19 @@
         <v>14.5</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>25</v>
       </c>
       <c r="BY9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BZ9">
         <v>23</v>
       </c>
       <c r="CA9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2891,10 +2891,10 @@
         <v>111</v>
       </c>
       <c r="F10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H10">
         <v>15.5</v>
@@ -2903,10 +2903,10 @@
         <v>20</v>
       </c>
       <c r="J10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2915,7 +2915,7 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O10">
         <v>1.35</v>
@@ -2924,55 +2924,55 @@
         <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V10">
         <v>1.06</v>
       </c>
       <c r="W10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y10">
         <v>36</v>
       </c>
       <c r="Z10">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD10">
         <v>70</v>
       </c>
       <c r="AE10">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="AF10">
         <v>6.4</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
         <v>60</v>
@@ -2990,10 +2990,10 @@
         <v>110</v>
       </c>
       <c r="AM10">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="AN10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO10">
         <v>1000</v>
@@ -3005,13 +3005,13 @@
         <v>29</v>
       </c>
       <c r="AR10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AS10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
         <v>12</v>
@@ -3020,37 +3020,37 @@
         <v>50</v>
       </c>
       <c r="AW10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX10">
         <v>5.6</v>
       </c>
       <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>44</v>
+      </c>
+      <c r="BA10">
         <v>10.5</v>
       </c>
-      <c r="AZ10">
-        <v>34</v>
-      </c>
-      <c r="BA10">
-        <v>12.5</v>
-      </c>
       <c r="BB10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD10">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BE10">
+        <v>10.5</v>
+      </c>
+      <c r="BF10">
+        <v>6.2</v>
+      </c>
+      <c r="BG10">
         <v>11</v>
-      </c>
-      <c r="BF10">
-        <v>6.4</v>
-      </c>
-      <c r="BG10">
-        <v>12.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3059,10 +3059,10 @@
         <v>2.78</v>
       </c>
       <c r="BJ10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BK10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3074,25 +3074,25 @@
         <v>4.3</v>
       </c>
       <c r="BO10">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BP10">
         <v>10.5</v>
       </c>
       <c r="BQ10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS10">
         <v>21</v>
       </c>
       <c r="BT10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BU10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3107,10 +3107,10 @@
         <v>21</v>
       </c>
       <c r="BZ10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3145,16 +3145,16 @@
         <v>2.3</v>
       </c>
       <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
         <v>3.4</v>
-      </c>
-      <c r="K11">
-        <v>3.45</v>
       </c>
       <c r="L11">
         <v>1.5</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
         <v>3.15</v>
@@ -3166,7 +3166,7 @@
         <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -3184,13 +3184,13 @@
         <v>1.76</v>
       </c>
       <c r="W11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X11">
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11">
         <v>13.5</v>
@@ -3199,7 +3199,7 @@
         <v>32</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
@@ -3211,10 +3211,10 @@
         <v>28</v>
       </c>
       <c r="AF11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH11">
         <v>21</v>
@@ -3226,13 +3226,13 @@
         <v>75</v>
       </c>
       <c r="AK11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL11">
         <v>75</v>
       </c>
       <c r="AM11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN11">
         <v>60</v>
@@ -3241,10 +3241,10 @@
         <v>25</v>
       </c>
       <c r="AP11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR11">
         <v>11.5</v>
@@ -3265,34 +3265,34 @@
         <v>24</v>
       </c>
       <c r="AX11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY11">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ11">
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB11">
         <v>55</v>
       </c>
       <c r="BC11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BD11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BE11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BF11">
         <v>50</v>
       </c>
       <c r="BG11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH11">
         <v>3</v>
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="BU11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV11">
         <v>21</v>
@@ -3349,7 +3349,7 @@
         <v>27</v>
       </c>
       <c r="BZ11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA11">
         <v>27</v>
@@ -3378,13 +3378,13 @@
         <v>3.5</v>
       </c>
       <c r="G12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J12">
         <v>3.7</v>
@@ -3393,49 +3393,49 @@
         <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
         <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R12">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S12">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U12">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y12">
         <v>12</v>
       </c>
       <c r="Z12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA12">
         <v>27</v>
@@ -3453,13 +3453,13 @@
         <v>21</v>
       </c>
       <c r="AF12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI12">
         <v>30</v>
@@ -3474,40 +3474,40 @@
         <v>40</v>
       </c>
       <c r="AM12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12">
         <v>19</v>
       </c>
       <c r="AX12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY12">
         <v>13</v>
@@ -3528,22 +3528,22 @@
         <v>36</v>
       </c>
       <c r="BE12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI12">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK12">
         <v>7.8</v>
@@ -3558,7 +3558,7 @@
         <v>6.8</v>
       </c>
       <c r="BO12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP12">
         <v>30</v>
@@ -3567,7 +3567,7 @@
         <v>18</v>
       </c>
       <c r="BR12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS12">
         <v>24</v>
@@ -3585,13 +3585,13 @@
         <v>13</v>
       </c>
       <c r="BX12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY12">
         <v>19</v>
       </c>
       <c r="BZ12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA12">
         <v>15.5</v>
@@ -3617,7 +3617,7 @@
         <v>114</v>
       </c>
       <c r="F13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G13">
         <v>1.86</v>
@@ -3638,7 +3638,7 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
         <v>2.66</v>
@@ -3650,7 +3650,7 @@
         <v>1.52</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>2.12</v>
       </c>
       <c r="R13">
         <v>1.19</v>
@@ -3659,7 +3659,7 @@
         <v>3.4</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U13">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -361,7 +361,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 21:05:23</t>
+    <t>2026-09-29 23:15:49</t>
   </si>
 </sst>
 </file>
@@ -955,25 +955,25 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
         <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -982,7 +982,7 @@
         <v>4.1</v>
       </c>
       <c r="O2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P2">
         <v>2.06</v>
@@ -994,7 +994,7 @@
         <v>1.43</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
         <v>1.73</v>
@@ -1003,7 +1003,7 @@
         <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
         <v>1.89</v>
@@ -1066,7 +1066,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR2">
         <v>17.5</v>
@@ -1087,7 +1087,7 @@
         <v>24</v>
       </c>
       <c r="AX2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
         <v>8.800000000000001</v>
@@ -1102,7 +1102,7 @@
         <v>22</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
         <v>22</v>
@@ -1111,7 +1111,7 @@
         <v>42</v>
       </c>
       <c r="BF2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1203,7 +1203,7 @@
         <v>1.62</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>7.4</v>
@@ -1215,49 +1215,49 @@
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
         <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T3">
         <v>1.83</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
         <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X3">
         <v>23</v>
       </c>
       <c r="Y3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA3">
         <v>220</v>
@@ -1266,31 +1266,31 @@
         <v>10</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK3">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL3">
         <v>34</v>
@@ -1299,7 +1299,7 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO3">
         <v>120</v>
@@ -1308,55 +1308,55 @@
         <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AR3">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3">
         <v>6.6</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB3">
+        <v>12.5</v>
+      </c>
+      <c r="BC3">
+        <v>14</v>
+      </c>
+      <c r="BD3">
         <v>7</v>
       </c>
-      <c r="BB3">
-        <v>13</v>
-      </c>
-      <c r="BC3">
-        <v>13.5</v>
-      </c>
-      <c r="BD3">
-        <v>7.2</v>
-      </c>
       <c r="BE3">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
@@ -1442,28 +1442,28 @@
         <v>1.67</v>
       </c>
       <c r="G4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H4">
         <v>5.5</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.35</v>
@@ -1475,73 +1475,73 @@
         <v>2.02</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
         <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AO4">
         <v>150</v>
@@ -1550,37 +1550,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX4">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY4">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB4">
         <v>15</v>
@@ -1589,13 +1589,13 @@
         <v>16</v>
       </c>
       <c r="BD4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
@@ -1604,7 +1604,7 @@
         <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1649,7 +1649,7 @@
         <v>38</v>
       </c>
       <c r="BX4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY4">
         <v>44</v>
@@ -1687,13 +1687,13 @@
         <v>1.2</v>
       </c>
       <c r="H5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5">
         <v>29</v>
       </c>
       <c r="J5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K5">
         <v>8.800000000000001</v>
@@ -1717,16 +1717,16 @@
         <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
         <v>2.58</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
         <v>1.03</v>
@@ -1798,7 +1798,7 @@
         <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>7.4</v>
@@ -1807,10 +1807,10 @@
         <v>17</v>
       </c>
       <c r="AV5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
         <v>5.6</v>
@@ -1819,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BA5">
         <v>8.6</v>
@@ -1831,10 +1831,10 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
         <v>3.45</v>
@@ -1843,7 +1843,7 @@
         <v>8.6</v>
       </c>
       <c r="BH5">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
         <v>3.8</v>
@@ -1852,16 +1852,16 @@
         <v>19</v>
       </c>
       <c r="BK5">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="BM5">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BO5">
         <v>2.96</v>
@@ -1876,25 +1876,25 @@
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BT5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BV5">
-        <v>350</v>
+        <v>440</v>
       </c>
       <c r="BW5">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
         <v>11</v>
@@ -1923,10 +1923,10 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>1.55</v>
@@ -1935,7 +1935,7 @@
         <v>1.56</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
         <v>4.9</v>
@@ -1956,7 +1956,7 @@
         <v>2.54</v>
       </c>
       <c r="Q6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R6">
         <v>1.62</v>
@@ -2070,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="BC6">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BD6">
         <v>55</v>
@@ -2082,7 +2082,7 @@
         <v>65</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH6">
         <v>4.3</v>
@@ -2112,7 +2112,7 @@
         <v>60</v>
       </c>
       <c r="BQ6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BR6">
         <v>60</v>
@@ -2121,7 +2121,7 @@
         <v>32</v>
       </c>
       <c r="BT6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU6">
         <v>4</v>
@@ -2142,7 +2142,7 @@
         <v>15.5</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>115</v>
@@ -2177,13 +2177,13 @@
         <v>14.5</v>
       </c>
       <c r="J7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K7">
         <v>7</v>
       </c>
       <c r="L7">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M7">
         <v>1.02</v>
@@ -2207,7 +2207,7 @@
         <v>2.1</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
         <v>2.04</v>
@@ -2228,7 +2228,7 @@
         <v>140</v>
       </c>
       <c r="AA7">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="AB7">
         <v>13</v>
@@ -2306,7 +2306,7 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BB7">
         <v>9.6</v>
@@ -2324,7 +2324,7 @@
         <v>3.4</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BH7">
         <v>6.2</v>
@@ -2339,7 +2339,7 @@
         <v>8</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM7">
         <v>1.01</v>
@@ -2434,7 +2434,7 @@
         <v>3.8</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P8">
         <v>1.92</v>
@@ -2446,7 +2446,7 @@
         <v>1.36</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T8">
         <v>1.78</v>
@@ -2503,13 +2503,13 @@
         <v>40</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM8">
         <v>100</v>
       </c>
       <c r="AN8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO8">
         <v>20</v>
@@ -2578,10 +2578,10 @@
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM8">
         <v>21</v>
@@ -2599,7 +2599,7 @@
         <v>16.5</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS8">
         <v>21</v>
@@ -2626,7 +2626,7 @@
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CB8" t="s">
         <v>115</v>
@@ -2649,16 +2649,16 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G9">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H9">
         <v>2.16</v>
       </c>
       <c r="I9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J9">
         <v>3.75</v>
@@ -2676,7 +2676,7 @@
         <v>4.7</v>
       </c>
       <c r="O9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
         <v>2.26</v>
@@ -2697,10 +2697,10 @@
         <v>2.42</v>
       </c>
       <c r="V9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X9">
         <v>19.5</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="Z9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA9">
         <v>27</v>
@@ -2727,7 +2727,7 @@
         <v>21</v>
       </c>
       <c r="AF9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2796,19 +2796,19 @@
         <v>55</v>
       </c>
       <c r="BC9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD9">
         <v>36</v>
       </c>
       <c r="BE9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
         <v>3.8</v>
@@ -2835,10 +2835,10 @@
         <v>6.2</v>
       </c>
       <c r="BP9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR9">
         <v>40</v>
@@ -2856,7 +2856,7 @@
         <v>14.5</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
         <v>25</v>
@@ -2865,7 +2865,7 @@
         <v>19.5</v>
       </c>
       <c r="BZ9">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="CA9">
         <v>15.5</v>
@@ -2891,16 +2891,16 @@
         <v>111</v>
       </c>
       <c r="F10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G10">
         <v>1.32</v>
       </c>
       <c r="H10">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="I10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J10">
         <v>5.6</v>
@@ -2915,28 +2915,28 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
         <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T10">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V10">
         <v>1.06</v>
@@ -2945,7 +2945,7 @@
         <v>4.1</v>
       </c>
       <c r="X10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y10">
         <v>36</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC10">
         <v>14</v>
@@ -2966,7 +2966,7 @@
         <v>70</v>
       </c>
       <c r="AE10">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="AF10">
         <v>6.4</v>
@@ -2975,10 +2975,10 @@
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI10">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="AJ10">
         <v>10</v>
@@ -2987,19 +2987,19 @@
         <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AM10">
-        <v>640</v>
+        <v>510</v>
       </c>
       <c r="AN10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AP10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
         <v>29</v>
@@ -3008,49 +3008,49 @@
         <v>10</v>
       </c>
       <c r="AS10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT10">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU10">
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AW10">
+        <v>8.6</v>
+      </c>
+      <c r="AX10">
+        <v>5.7</v>
+      </c>
+      <c r="AY10">
         <v>10.5</v>
       </c>
-      <c r="AX10">
-        <v>5.6</v>
-      </c>
-      <c r="AY10">
-        <v>11</v>
-      </c>
       <c r="AZ10">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BA10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB10">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD10">
         <v>46</v>
       </c>
       <c r="BE10">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3065,7 +3065,7 @@
         <v>10</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM10">
         <v>21</v>
@@ -3074,7 +3074,7 @@
         <v>4.3</v>
       </c>
       <c r="BO10">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="BP10">
         <v>10.5</v>
@@ -3133,13 +3133,13 @@
         <v>112</v>
       </c>
       <c r="F11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H11">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I11">
         <v>2.3</v>
@@ -3190,7 +3190,7 @@
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z11">
         <v>13.5</v>
@@ -3211,7 +3211,7 @@
         <v>28</v>
       </c>
       <c r="AF11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG11">
         <v>15.5</v>
@@ -3226,7 +3226,7 @@
         <v>75</v>
       </c>
       <c r="AK11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL11">
         <v>75</v>
@@ -3235,16 +3235,16 @@
         <v>140</v>
       </c>
       <c r="AN11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO11">
         <v>25</v>
       </c>
       <c r="AP11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR11">
         <v>11.5</v>
@@ -3283,10 +3283,10 @@
         <v>42</v>
       </c>
       <c r="BD11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF11">
         <v>50</v>
@@ -3307,7 +3307,7 @@
         <v>9</v>
       </c>
       <c r="BL11">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM11">
         <v>21</v>
@@ -3375,16 +3375,16 @@
         <v>113</v>
       </c>
       <c r="F12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G12">
         <v>3.6</v>
       </c>
       <c r="H12">
+        <v>2.18</v>
+      </c>
+      <c r="I12">
         <v>2.2</v>
-      </c>
-      <c r="I12">
-        <v>2.24</v>
       </c>
       <c r="J12">
         <v>3.7</v>
@@ -3414,16 +3414,16 @@
         <v>1.51</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W12">
         <v>1.38</v>
@@ -3435,7 +3435,7 @@
         <v>12</v>
       </c>
       <c r="Z12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA12">
         <v>27</v>
@@ -3444,7 +3444,7 @@
         <v>17</v>
       </c>
       <c r="AC12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12">
         <v>10.5</v>
@@ -3510,7 +3510,7 @@
         <v>26</v>
       </c>
       <c r="AY12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12">
         <v>14.5</v>
@@ -3519,7 +3519,7 @@
         <v>28</v>
       </c>
       <c r="BB12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC12">
         <v>32</v>
@@ -3531,7 +3531,7 @@
         <v>46</v>
       </c>
       <c r="BF12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG12">
         <v>11.5</v>
@@ -3540,7 +3540,7 @@
         <v>3.9</v>
       </c>
       <c r="BI12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ12">
         <v>8.800000000000001</v>
@@ -3555,7 +3555,7 @@
         <v>21</v>
       </c>
       <c r="BN12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO12">
         <v>6.2</v>
@@ -3567,19 +3567,19 @@
         <v>18</v>
       </c>
       <c r="BR12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BT12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU12">
         <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW12">
         <v>13</v>
@@ -3588,13 +3588,13 @@
         <v>30</v>
       </c>
       <c r="BY12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BZ12">
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB12" t="s">
         <v>115</v>
@@ -3617,22 +3617,22 @@
         <v>114</v>
       </c>
       <c r="F13">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="G13">
         <v>1.86</v>
       </c>
       <c r="H13">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I13">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>3.3</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3653,10 +3653,10 @@
         <v>2.12</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="T13">
         <v>2.16</v>
@@ -3665,7 +3665,7 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
         <v>2.16</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,15 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-10-01</t>
   </si>
   <si>
@@ -289,6 +298,15 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Tulsa Roughnecks FC</t>
   </si>
   <si>
@@ -325,6 +343,15 @@
     <t>Envigado</t>
   </si>
   <si>
+    <t>Dominica</t>
+  </si>
+  <si>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -361,7 +388,16 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-09-29 23:15:49</t>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Trinidad &amp; Tobago</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>2026-09-30 01:26:25</t>
   </si>
 </sst>
 </file>
@@ -693,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -943,19 +979,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F2">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
         <v>2.12</v>
@@ -973,28 +1009,28 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R2">
         <v>1.43</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
         <v>1.73</v>
@@ -1027,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
         <v>50</v>
@@ -1057,64 +1093,64 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>44</v>
       </c>
       <c r="AP2">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
         <v>17.5</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1177,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1185,76 +1221,76 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G3">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S3">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z3">
         <v>70</v>
@@ -1269,7 +1305,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE3">
         <v>110</v>
@@ -1278,10 +1314,10 @@
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3">
         <v>100</v>
@@ -1299,34 +1335,34 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO3">
         <v>120</v>
       </c>
       <c r="AP3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AR3">
         <v>42</v>
       </c>
       <c r="AS3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU3">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1338,7 +1374,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
         <v>12.5</v>
@@ -1347,22 +1383,22 @@
         <v>14</v>
       </c>
       <c r="BD3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF3">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
@@ -1377,25 +1413,25 @@
         <v>1.02</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3">
         <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
@@ -1413,13 +1449,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1427,73 +1463,73 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G4">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
         <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T4">
         <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y4">
         <v>18.5</v>
@@ -1502,22 +1538,22 @@
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1529,76 +1565,76 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR4">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY4">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
@@ -1643,13 +1679,13 @@
         <v>6.8</v>
       </c>
       <c r="BV4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW4">
         <v>38</v>
       </c>
       <c r="BX4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY4">
         <v>44</v>
@@ -1661,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1669,16 +1705,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F5">
         <v>1.18</v>
@@ -1690,13 +1726,13 @@
         <v>22</v>
       </c>
       <c r="I5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5">
         <v>8.4</v>
       </c>
       <c r="K5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1705,28 +1741,28 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
         <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
         <v>2.58</v>
       </c>
       <c r="T5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V5">
         <v>1.03</v>
@@ -1747,19 +1783,19 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AE5">
         <v>1000</v>
       </c>
       <c r="AF5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG5">
         <v>16</v>
@@ -1777,13 +1813,13 @@
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AO5">
         <v>1000</v>
@@ -1792,25 +1828,25 @@
         <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AV5">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX5">
         <v>5.6</v>
@@ -1819,10 +1855,10 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1831,28 +1867,28 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL5">
         <v>380</v>
@@ -1867,10 +1903,10 @@
         <v>2.96</v>
       </c>
       <c r="BP5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
         <v>32</v>
@@ -1879,31 +1915,31 @@
         <v>7.4</v>
       </c>
       <c r="BT5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BU5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV5">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="BW5">
         <v>9.4</v>
       </c>
       <c r="BX5">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1911,16 +1947,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F6">
         <v>6.8</v>
@@ -1929,10 +1965,10 @@
         <v>7</v>
       </c>
       <c r="H6">
+        <v>1.54</v>
+      </c>
+      <c r="I6">
         <v>1.55</v>
-      </c>
-      <c r="I6">
-        <v>1.56</v>
       </c>
       <c r="J6">
         <v>4.7</v>
@@ -1941,7 +1977,7 @@
         <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -1956,7 +1992,7 @@
         <v>2.54</v>
       </c>
       <c r="Q6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R6">
         <v>1.62</v>
@@ -1974,7 +2010,7 @@
         <v>2.78</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
         <v>24</v>
@@ -1986,7 +2022,7 @@
         <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AB6">
         <v>28</v>
@@ -2043,13 +2079,13 @@
         <v>13.5</v>
       </c>
       <c r="AT6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU6">
         <v>10</v>
       </c>
       <c r="AV6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>13.5</v>
@@ -2067,10 +2103,10 @@
         <v>25</v>
       </c>
       <c r="BB6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BD6">
         <v>55</v>
@@ -2082,7 +2118,7 @@
         <v>65</v>
       </c>
       <c r="BG6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
         <v>4.3</v>
@@ -2112,7 +2148,7 @@
         <v>60</v>
       </c>
       <c r="BQ6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BR6">
         <v>60</v>
@@ -2121,7 +2157,7 @@
         <v>32</v>
       </c>
       <c r="BT6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU6">
         <v>4</v>
@@ -2145,7 +2181,7 @@
         <v>9.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2153,16 +2189,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F7">
         <v>1.27</v>
@@ -2198,10 +2234,10 @@
         <v>3.15</v>
       </c>
       <c r="Q7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R7">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S7">
         <v>2.1</v>
@@ -2228,7 +2264,7 @@
         <v>140</v>
       </c>
       <c r="AA7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="AB7">
         <v>13</v>
@@ -2249,13 +2285,13 @@
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>140</v>
       </c>
       <c r="AJ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK7">
         <v>13.5</v>
@@ -2270,19 +2306,19 @@
         <v>3.6</v>
       </c>
       <c r="AO7">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP7">
         <v>30</v>
       </c>
       <c r="AQ7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR7">
         <v>15.5</v>
       </c>
       <c r="AS7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2294,7 +2330,7 @@
         <v>38</v>
       </c>
       <c r="AW7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2306,7 +2342,7 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BB7">
         <v>9.6</v>
@@ -2315,7 +2351,7 @@
         <v>11.5</v>
       </c>
       <c r="BD7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE7">
         <v>16.5</v>
@@ -2387,7 +2423,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2395,16 +2431,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F8">
         <v>3.35</v>
@@ -2422,7 +2458,7 @@
         <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.41</v>
@@ -2440,13 +2476,13 @@
         <v>1.92</v>
       </c>
       <c r="Q8">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
         <v>1.78</v>
@@ -2500,7 +2536,7 @@
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8">
         <v>65</v>
@@ -2509,16 +2545,16 @@
         <v>100</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP8">
         <v>12</v>
       </c>
       <c r="AQ8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8">
         <v>13</v>
@@ -2560,7 +2596,7 @@
         <v>42</v>
       </c>
       <c r="BE8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF8">
         <v>30</v>
@@ -2629,7 +2665,7 @@
         <v>16.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2637,19 +2673,19 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G9">
         <v>3.7</v>
@@ -2685,7 +2721,7 @@
         <v>1.77</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
         <v>2.88</v>
@@ -2727,7 +2763,7 @@
         <v>21</v>
       </c>
       <c r="AF9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2871,7 +2907,7 @@
         <v>15.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2879,16 +2915,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F10">
         <v>1.31</v>
@@ -2897,7 +2933,7 @@
         <v>1.32</v>
       </c>
       <c r="H10">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="I10">
         <v>16</v>
@@ -2906,7 +2942,7 @@
         <v>5.6</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2915,28 +2951,28 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T10">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V10">
         <v>1.06</v>
@@ -2945,7 +2981,7 @@
         <v>4.1</v>
       </c>
       <c r="X10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y10">
         <v>36</v>
@@ -2978,7 +3014,7 @@
         <v>55</v>
       </c>
       <c r="AI10">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AJ10">
         <v>10</v>
@@ -3005,10 +3041,10 @@
         <v>29</v>
       </c>
       <c r="AR10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT10">
         <v>5.7</v>
@@ -3017,10 +3053,10 @@
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AW10">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX10">
         <v>5.7</v>
@@ -3044,13 +3080,13 @@
         <v>46</v>
       </c>
       <c r="BE10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF10">
         <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3113,7 +3149,7 @@
         <v>9.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3121,19 +3157,19 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G11">
         <v>3.8</v>
@@ -3151,7 +3187,7 @@
         <v>3.4</v>
       </c>
       <c r="L11">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3184,7 +3220,7 @@
         <v>1.76</v>
       </c>
       <c r="W11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X11">
         <v>11</v>
@@ -3232,7 +3268,7 @@
         <v>75</v>
       </c>
       <c r="AM11">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN11">
         <v>65</v>
@@ -3355,7 +3391,7 @@
         <v>27</v>
       </c>
       <c r="CB11" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3363,28 +3399,28 @@
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F12">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H12">
+        <v>2.14</v>
+      </c>
+      <c r="I12">
         <v>2.18</v>
-      </c>
-      <c r="I12">
-        <v>2.2</v>
       </c>
       <c r="J12">
         <v>3.7</v>
@@ -3405,16 +3441,16 @@
         <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q12">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S12">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
         <v>1.64</v>
@@ -3423,10 +3459,10 @@
         <v>2.48</v>
       </c>
       <c r="V12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X12">
         <v>18.5</v>
@@ -3438,7 +3474,7 @@
         <v>15.5</v>
       </c>
       <c r="AA12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB12">
         <v>17</v>
@@ -3450,10 +3486,10 @@
         <v>10.5</v>
       </c>
       <c r="AE12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG12">
         <v>14</v>
@@ -3465,7 +3501,7 @@
         <v>30</v>
       </c>
       <c r="AJ12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK12">
         <v>36</v>
@@ -3477,10 +3513,10 @@
         <v>65</v>
       </c>
       <c r="AN12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP12">
         <v>17</v>
@@ -3492,13 +3528,13 @@
         <v>14.5</v>
       </c>
       <c r="AS12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV12">
         <v>10</v>
@@ -3516,10 +3552,10 @@
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB12">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BC12">
         <v>32</v>
@@ -3534,7 +3570,7 @@
         <v>26</v>
       </c>
       <c r="BG12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH12">
         <v>3.9</v>
@@ -3558,10 +3594,10 @@
         <v>7</v>
       </c>
       <c r="BO12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ12">
         <v>18</v>
@@ -3573,22 +3609,22 @@
         <v>23</v>
       </c>
       <c r="BT12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU12">
         <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BW12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX12">
         <v>30</v>
       </c>
       <c r="BY12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BZ12">
         <v>23</v>
@@ -3597,7 +3633,7 @@
         <v>13.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3605,22 +3641,22 @@
         <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F13">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G13">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="H13">
         <v>5.1</v>
@@ -3653,10 +3689,10 @@
         <v>2.12</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S13">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="T13">
         <v>2.16</v>
@@ -3668,178 +3704,904 @@
         <v>1.15</v>
       </c>
       <c r="W13">
+        <v>2.08</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G14">
+        <v>23</v>
+      </c>
+      <c r="H14">
+        <v>1.29</v>
+      </c>
+      <c r="I14">
+        <v>1.31</v>
+      </c>
+      <c r="J14">
+        <v>4.9</v>
+      </c>
+      <c r="K14">
+        <v>7.2</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>4.4</v>
+      </c>
+      <c r="O14">
+        <v>1.2</v>
+      </c>
+      <c r="P14">
+        <v>2.2</v>
+      </c>
+      <c r="Q14">
+        <v>1.64</v>
+      </c>
+      <c r="R14">
+        <v>1.37</v>
+      </c>
+      <c r="S14">
+        <v>2.58</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.47</v>
+      </c>
+      <c r="V14">
+        <v>4</v>
+      </c>
+      <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
+        <v>28</v>
+      </c>
+      <c r="Y14">
+        <v>11</v>
+      </c>
+      <c r="Z14">
+        <v>10</v>
+      </c>
+      <c r="AA14">
+        <v>12.5</v>
+      </c>
+      <c r="AB14">
+        <v>65</v>
+      </c>
+      <c r="AC14">
+        <v>21</v>
+      </c>
+      <c r="AD14">
+        <v>15.5</v>
+      </c>
+      <c r="AE14">
+        <v>22</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>90</v>
+      </c>
+      <c r="AH14">
+        <v>55</v>
+      </c>
+      <c r="AI14">
+        <v>70</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>5.3</v>
+      </c>
+      <c r="AR14">
+        <v>4.8</v>
+      </c>
+      <c r="AS14">
+        <v>6.4</v>
+      </c>
+      <c r="AT14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV14">
+        <v>7.4</v>
+      </c>
+      <c r="AW14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <v>1.74</v>
+      </c>
+      <c r="G15">
+        <v>1.82</v>
+      </c>
+      <c r="H15">
+        <v>5.2</v>
+      </c>
+      <c r="I15">
+        <v>5.8</v>
+      </c>
+      <c r="J15">
+        <v>3.7</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.07</v>
+      </c>
+      <c r="N15">
+        <v>3.35</v>
+      </c>
+      <c r="O15">
+        <v>1.35</v>
+      </c>
+      <c r="P15">
+        <v>1.85</v>
+      </c>
+      <c r="Q15">
+        <v>2.02</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
+        <v>3.5</v>
+      </c>
+      <c r="T15">
+        <v>1.91</v>
+      </c>
+      <c r="U15">
+        <v>1.84</v>
+      </c>
+      <c r="V15">
+        <v>1.21</v>
+      </c>
+      <c r="W15">
+        <v>2.2</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>25</v>
+      </c>
+      <c r="Z15">
+        <v>60</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>11.5</v>
+      </c>
+      <c r="AC15">
+        <v>12.5</v>
+      </c>
+      <c r="AD15">
+        <v>30</v>
+      </c>
+      <c r="AE15">
+        <v>100</v>
+      </c>
+      <c r="AF15">
+        <v>15</v>
+      </c>
+      <c r="AG15">
+        <v>15</v>
+      </c>
+      <c r="AH15">
+        <v>30</v>
+      </c>
+      <c r="AI15">
+        <v>100</v>
+      </c>
+      <c r="AJ15">
+        <v>28</v>
+      </c>
+      <c r="AK15">
+        <v>29</v>
+      </c>
+      <c r="AL15">
+        <v>55</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>2.18</v>
+      </c>
+      <c r="AQ15">
+        <v>2</v>
+      </c>
+      <c r="AR15">
+        <v>2.1</v>
+      </c>
+      <c r="AS15">
+        <v>2.18</v>
+      </c>
+      <c r="AT15">
+        <v>1.82</v>
+      </c>
+      <c r="AU15">
+        <v>7.2</v>
+      </c>
+      <c r="AV15">
+        <v>15</v>
+      </c>
+      <c r="AW15">
+        <v>2.14</v>
+      </c>
+      <c r="AX15">
+        <v>1.9</v>
+      </c>
+      <c r="AY15">
+        <v>1.9</v>
+      </c>
+      <c r="AZ15">
+        <v>17.5</v>
+      </c>
+      <c r="BA15">
+        <v>2.14</v>
+      </c>
+      <c r="BB15">
+        <v>13.5</v>
+      </c>
+      <c r="BC15">
+        <v>16</v>
+      </c>
+      <c r="BD15">
+        <v>2.1</v>
+      </c>
+      <c r="BE15">
+        <v>2.18</v>
+      </c>
+      <c r="BF15">
+        <v>2.18</v>
+      </c>
+      <c r="BG15">
+        <v>2.18</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>2.8</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16">
+        <v>2.6</v>
+      </c>
+      <c r="G16">
+        <v>2.86</v>
+      </c>
+      <c r="H16">
+        <v>2.92</v>
+      </c>
+      <c r="I16">
+        <v>3.3</v>
+      </c>
+      <c r="J16">
+        <v>2.96</v>
+      </c>
+      <c r="K16">
+        <v>3.45</v>
+      </c>
+      <c r="L16">
+        <v>1.41</v>
+      </c>
+      <c r="M16">
+        <v>1.09</v>
+      </c>
+      <c r="N16">
+        <v>3.05</v>
+      </c>
+      <c r="O16">
+        <v>1.4</v>
+      </c>
+      <c r="P16">
+        <v>1.66</v>
+      </c>
+      <c r="Q16">
         <v>2.16</v>
       </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13">
-        <v>1.01</v>
-      </c>
-      <c r="AR13">
-        <v>1.01</v>
-      </c>
-      <c r="AS13">
-        <v>1.01</v>
-      </c>
-      <c r="AT13">
-        <v>1.01</v>
-      </c>
-      <c r="AU13">
-        <v>1.01</v>
-      </c>
-      <c r="AV13">
-        <v>1.01</v>
-      </c>
-      <c r="AW13">
-        <v>1.01</v>
-      </c>
-      <c r="AX13">
-        <v>1.01</v>
-      </c>
-      <c r="AY13">
-        <v>1.01</v>
-      </c>
-      <c r="AZ13">
-        <v>1.01</v>
-      </c>
-      <c r="BA13">
-        <v>1.01</v>
-      </c>
-      <c r="BB13">
-        <v>1.01</v>
-      </c>
-      <c r="BC13">
-        <v>1.01</v>
-      </c>
-      <c r="BD13">
-        <v>1.01</v>
-      </c>
-      <c r="BE13">
-        <v>1.01</v>
-      </c>
-      <c r="BF13">
-        <v>1.01</v>
-      </c>
-      <c r="BG13">
-        <v>1.01</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.01</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.01</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.01</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.01</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>1.01</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>115</v>
+      <c r="R16">
+        <v>1.28</v>
+      </c>
+      <c r="S16">
+        <v>4</v>
+      </c>
+      <c r="T16">
+        <v>1.81</v>
+      </c>
+      <c r="U16">
+        <v>1.89</v>
+      </c>
+      <c r="V16">
+        <v>1.45</v>
+      </c>
+      <c r="W16">
+        <v>1.54</v>
+      </c>
+      <c r="X16">
+        <v>21</v>
+      </c>
+      <c r="Y16">
+        <v>970</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>970</v>
+      </c>
+      <c r="AC16">
+        <v>7.6</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>48</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>50</v>
+      </c>
+      <c r="AP16">
+        <v>1.41</v>
+      </c>
+      <c r="AQ16">
+        <v>1.39</v>
+      </c>
+      <c r="AR16">
+        <v>1.5</v>
+      </c>
+      <c r="AS16">
+        <v>1.5</v>
+      </c>
+      <c r="AT16">
+        <v>1.38</v>
+      </c>
+      <c r="AU16">
+        <v>1.26</v>
+      </c>
+      <c r="AV16">
+        <v>1.5</v>
+      </c>
+      <c r="AW16">
+        <v>1.46</v>
+      </c>
+      <c r="AX16">
+        <v>1.5</v>
+      </c>
+      <c r="AY16">
+        <v>1.5</v>
+      </c>
+      <c r="AZ16">
+        <v>1.5</v>
+      </c>
+      <c r="BA16">
+        <v>1.5</v>
+      </c>
+      <c r="BB16">
+        <v>1.51</v>
+      </c>
+      <c r="BC16">
+        <v>1.5</v>
+      </c>
+      <c r="BD16">
+        <v>1.51</v>
+      </c>
+      <c r="BE16">
+        <v>1.5</v>
+      </c>
+      <c r="BF16">
+        <v>1.5</v>
+      </c>
+      <c r="BG16">
+        <v>1.46</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -397,7 +397,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 01:26:25</t>
+    <t>2026-09-30 03:37:03</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
         <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
         <v>3.8</v>
@@ -1009,13 +1009,13 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.29</v>
@@ -1033,10 +1033,10 @@
         <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="V2">
         <v>1.35</v>
@@ -1048,7 +1048,7 @@
         <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
         <v>32</v>
@@ -1087,13 +1087,13 @@
         <v>24</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM2">
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO2">
         <v>44</v>
@@ -1105,7 +1105,7 @@
         <v>1.03</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
         <v>1.03</v>
@@ -1114,7 +1114,7 @@
         <v>9.4</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>13.5</v>
@@ -1123,7 +1123,7 @@
         <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY2">
         <v>9.800000000000001</v>
@@ -1150,61 +1150,61 @@
         <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI2">
         <v>3</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G3">
         <v>1.58</v>
@@ -1242,13 +1242,13 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
         <v>1.33</v>
@@ -1266,19 +1266,19 @@
         <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T3">
         <v>1.82</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
         <v>1.15</v>
@@ -1287,7 +1287,7 @@
         <v>2.72</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y3">
         <v>29</v>
@@ -1305,7 +1305,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE3">
         <v>110</v>
@@ -1320,10 +1320,10 @@
         <v>20</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK3">
         <v>17</v>
@@ -1350,16 +1350,16 @@
         <v>42</v>
       </c>
       <c r="AS3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AW3">
         <v>8.6</v>
@@ -1371,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA3">
         <v>8.6</v>
@@ -1380,19 +1380,19 @@
         <v>12.5</v>
       </c>
       <c r="BC3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3">
         <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
@@ -1413,7 +1413,7 @@
         <v>1.02</v>
       </c>
       <c r="BN3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO3">
         <v>3.3</v>
@@ -1449,10 +1449,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
@@ -1484,7 +1484,7 @@
         <v>5.6</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>3.95</v>
@@ -1499,7 +1499,7 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
         <v>1.36</v>
@@ -1517,10 +1517,10 @@
         <v>3.85</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.2</v>
@@ -1583,13 +1583,13 @@
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AS4">
         <v>1.03</v>
@@ -1598,7 +1598,7 @@
         <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>1.03</v>
@@ -1607,25 +1607,25 @@
         <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA4">
         <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
@@ -1634,7 +1634,7 @@
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
@@ -1726,7 +1726,7 @@
         <v>22</v>
       </c>
       <c r="I5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5">
         <v>8.4</v>
@@ -1741,13 +1741,13 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
         <v>1.67</v>
@@ -1756,10 +1756,10 @@
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
         <v>1.43</v>
@@ -1768,7 +1768,7 @@
         <v>1.03</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -1783,7 +1783,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>22</v>
@@ -1819,19 +1819,19 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AS5">
         <v>10</v>
@@ -1843,7 +1843,7 @@
         <v>17.5</v>
       </c>
       <c r="AV5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AW5">
         <v>10</v>
@@ -1852,13 +1852,13 @@
         <v>5.6</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BA5">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1867,7 +1867,7 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BE5">
         <v>10</v>
@@ -1900,7 +1900,7 @@
         <v>3.4</v>
       </c>
       <c r="BO5">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BP5">
         <v>5.9</v>
@@ -1959,16 +1959,16 @@
         <v>116</v>
       </c>
       <c r="F6">
+        <v>6.6</v>
+      </c>
+      <c r="G6">
         <v>6.8</v>
       </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
       <c r="H6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J6">
         <v>4.7</v>
@@ -1977,7 +1977,7 @@
         <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -1998,10 +1998,10 @@
         <v>1.62</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
         <v>2.26</v>
@@ -2010,7 +2010,7 @@
         <v>2.78</v>
       </c>
       <c r="W6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
         <v>24</v>
@@ -2028,7 +2028,7 @@
         <v>28</v>
       </c>
       <c r="AC6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD6">
         <v>9.6</v>
@@ -2037,7 +2037,7 @@
         <v>15</v>
       </c>
       <c r="AF6">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AG6">
         <v>25</v>
@@ -2052,7 +2052,7 @@
         <v>200</v>
       </c>
       <c r="AK6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL6">
         <v>70</v>
@@ -2064,7 +2064,7 @@
         <v>90</v>
       </c>
       <c r="AO6">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AP6">
         <v>21</v>
@@ -2079,10 +2079,10 @@
         <v>13.5</v>
       </c>
       <c r="AT6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2118,10 +2118,10 @@
         <v>65</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI6">
         <v>3.95</v>
@@ -2151,13 +2151,13 @@
         <v>34</v>
       </c>
       <c r="BR6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS6">
         <v>32</v>
       </c>
       <c r="BT6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU6">
         <v>4</v>
@@ -2246,13 +2246,13 @@
         <v>1.9</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
         <v>1.07</v>
       </c>
       <c r="W7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="X7">
         <v>36</v>
@@ -2264,7 +2264,7 @@
         <v>140</v>
       </c>
       <c r="AA7">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="AB7">
         <v>13</v>
@@ -2276,10 +2276,10 @@
         <v>48</v>
       </c>
       <c r="AE7">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AF7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
@@ -2306,7 +2306,7 @@
         <v>3.6</v>
       </c>
       <c r="AO7">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP7">
         <v>30</v>
@@ -2315,10 +2315,10 @@
         <v>48</v>
       </c>
       <c r="AR7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2351,16 +2351,16 @@
         <v>11.5</v>
       </c>
       <c r="BD7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE7">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF7">
         <v>3.4</v>
       </c>
       <c r="BG7">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BH7">
         <v>6.2</v>
@@ -2449,7 +2449,7 @@
         <v>3.4</v>
       </c>
       <c r="H8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I8">
         <v>2.38</v>
@@ -2467,28 +2467,28 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V8">
         <v>1.72</v>
@@ -2512,7 +2512,7 @@
         <v>13.5</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2536,7 +2536,7 @@
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL8">
         <v>65</v>
@@ -2548,13 +2548,13 @@
         <v>38</v>
       </c>
       <c r="AO8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP8">
         <v>12</v>
       </c>
       <c r="AQ8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR8">
         <v>13</v>
@@ -2569,7 +2569,7 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW8">
         <v>22</v>
@@ -2578,7 +2578,7 @@
         <v>21</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>15.5</v>
@@ -2635,7 +2635,7 @@
         <v>16.5</v>
       </c>
       <c r="BR8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS8">
         <v>21</v>
@@ -2662,7 +2662,7 @@
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="CB8" t="s">
         <v>127</v>
@@ -2685,22 +2685,22 @@
         <v>119</v>
       </c>
       <c r="F9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G9">
         <v>3.7</v>
       </c>
       <c r="H9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I9">
         <v>2.18</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
         <v>1.36</v>
@@ -2709,16 +2709,16 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
         <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q9">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R9">
         <v>1.5</v>
@@ -2733,7 +2733,7 @@
         <v>2.42</v>
       </c>
       <c r="V9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W9">
         <v>1.37</v>
@@ -2808,13 +2808,13 @@
         <v>15</v>
       </c>
       <c r="AU9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV9">
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX9">
         <v>23</v>
@@ -2841,7 +2841,7 @@
         <v>14</v>
       </c>
       <c r="BF9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG9">
         <v>11.5</v>
@@ -2850,7 +2850,7 @@
         <v>3.8</v>
       </c>
       <c r="BI9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
         <v>9</v>
@@ -2892,7 +2892,7 @@
         <v>14.5</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX9">
         <v>25</v>
@@ -2901,7 +2901,7 @@
         <v>19.5</v>
       </c>
       <c r="BZ9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA9">
         <v>15.5</v>
@@ -2933,7 +2933,7 @@
         <v>1.32</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I10">
         <v>16</v>
@@ -2942,37 +2942,37 @@
         <v>5.6</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V10">
         <v>1.06</v>
@@ -2981,19 +2981,19 @@
         <v>4.1</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y10">
         <v>36</v>
       </c>
       <c r="Z10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC10">
         <v>14</v>
@@ -3002,10 +3002,10 @@
         <v>70</v>
       </c>
       <c r="AE10">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="AF10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -3014,7 +3014,7 @@
         <v>55</v>
       </c>
       <c r="AI10">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AJ10">
         <v>10</v>
@@ -3023,127 +3023,127 @@
         <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AM10">
         <v>510</v>
       </c>
       <c r="AN10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO10">
         <v>990</v>
       </c>
       <c r="AP10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10">
         <v>29</v>
       </c>
       <c r="AR10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS10">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU10">
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AW10">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX10">
         <v>5.7</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BA10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB10">
         <v>8.199999999999999</v>
       </c>
       <c r="BC10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD10">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE10">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG10">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI10">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="BK10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BL10">
-        <v>250</v>
+        <v>420</v>
       </c>
       <c r="BM10">
         <v>21</v>
       </c>
       <c r="BN10">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BO10">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="BP10">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BQ10">
         <v>4.9</v>
       </c>
       <c r="BR10">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BS10">
         <v>21</v>
       </c>
       <c r="BT10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BU10">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BW10">
         <v>21</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BY10">
         <v>21</v>
       </c>
       <c r="BZ10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="CA10">
         <v>9.6</v>
@@ -3172,13 +3172,13 @@
         <v>3.75</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3199,7 +3199,7 @@
         <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q11">
         <v>2.3</v>
@@ -3211,13 +3211,13 @@
         <v>4.4</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U11">
         <v>1.95</v>
       </c>
       <c r="V11">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W11">
         <v>1.35</v>
@@ -3229,7 +3229,7 @@
         <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA11">
         <v>32</v>
@@ -3244,13 +3244,13 @@
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF11">
         <v>25</v>
       </c>
       <c r="AG11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH11">
         <v>21</v>
@@ -3259,16 +3259,16 @@
         <v>50</v>
       </c>
       <c r="AJ11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK11">
+        <v>55</v>
+      </c>
+      <c r="AL11">
         <v>70</v>
       </c>
-      <c r="AL11">
-        <v>75</v>
-      </c>
       <c r="AM11">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN11">
         <v>65</v>
@@ -3286,7 +3286,7 @@
         <v>11.5</v>
       </c>
       <c r="AS11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT11">
         <v>11</v>
@@ -3316,13 +3316,13 @@
         <v>55</v>
       </c>
       <c r="BC11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BE11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11">
         <v>50</v>
@@ -3367,10 +3367,10 @@
         <v>36</v>
       </c>
       <c r="BT11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV11">
         <v>21</v>
@@ -3417,7 +3417,7 @@
         <v>3.7</v>
       </c>
       <c r="H12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I12">
         <v>2.18</v>
@@ -3429,28 +3429,28 @@
         <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T12">
         <v>1.64</v>
@@ -3465,13 +3465,13 @@
         <v>1.37</v>
       </c>
       <c r="X12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA12">
         <v>26</v>
@@ -3483,7 +3483,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE12">
         <v>20</v>
@@ -3492,10 +3492,10 @@
         <v>28</v>
       </c>
       <c r="AG12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
         <v>30</v>
@@ -3504,16 +3504,16 @@
         <v>65</v>
       </c>
       <c r="AK12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM12">
         <v>65</v>
       </c>
       <c r="AN12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO12">
         <v>12</v>
@@ -3522,19 +3522,19 @@
         <v>17</v>
       </c>
       <c r="AQ12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS12">
         <v>24</v>
       </c>
       <c r="AT12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU12">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12">
         <v>10</v>
@@ -3546,7 +3546,7 @@
         <v>26</v>
       </c>
       <c r="AY12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ12">
         <v>14.5</v>
@@ -3555,19 +3555,19 @@
         <v>27</v>
       </c>
       <c r="BB12">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC12">
         <v>32</v>
       </c>
       <c r="BD12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE12">
         <v>46</v>
       </c>
       <c r="BF12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG12">
         <v>11</v>
@@ -3618,7 +3618,7 @@
         <v>17.5</v>
       </c>
       <c r="BW12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX12">
         <v>30</v>
@@ -3656,7 +3656,7 @@
         <v>1.68</v>
       </c>
       <c r="G13">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H13">
         <v>5.1</v>
@@ -3665,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
         <v>3.9</v>
@@ -3674,43 +3674,43 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N13">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O13">
         <v>1.46</v>
       </c>
       <c r="P13">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="Q13">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R13">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="T13">
         <v>2.16</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W13">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X13">
         <v>1000</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z13">
         <v>1000</v>
@@ -3719,25 +3719,25 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE13">
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG13">
         <v>1000</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI13">
         <v>1000</v>
@@ -3755,7 +3755,7 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3764,7 +3764,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR13">
         <v>1.01</v>
@@ -3779,7 +3779,7 @@
         <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -3791,7 +3791,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA13">
         <v>1.01</v>
@@ -3809,7 +3809,7 @@
         <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG13">
         <v>1.01</v>
@@ -3895,10 +3895,10 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H14">
         <v>1.29</v>
@@ -3907,7 +3907,7 @@
         <v>1.31</v>
       </c>
       <c r="J14">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K14">
         <v>7.2</v>
@@ -3916,13 +3916,13 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
         <v>2.2</v>
@@ -3931,100 +3931,100 @@
         <v>1.64</v>
       </c>
       <c r="R14">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S14">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U14">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AA14">
+        <v>9.6</v>
+      </c>
+      <c r="AB14">
+        <v>48</v>
+      </c>
+      <c r="AC14">
+        <v>15.5</v>
+      </c>
+      <c r="AD14">
         <v>12.5</v>
       </c>
-      <c r="AB14">
+      <c r="AE14">
+        <v>16.5</v>
+      </c>
+      <c r="AF14">
+        <v>220</v>
+      </c>
+      <c r="AG14">
         <v>65</v>
       </c>
-      <c r="AC14">
-        <v>21</v>
-      </c>
-      <c r="AD14">
+      <c r="AH14">
+        <v>42</v>
+      </c>
+      <c r="AI14">
+        <v>55</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>440</v>
+      </c>
+      <c r="AL14">
+        <v>310</v>
+      </c>
+      <c r="AM14">
+        <v>320</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>5.6</v>
+      </c>
+      <c r="AP14">
         <v>15.5</v>
       </c>
-      <c r="AE14">
-        <v>22</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
-        <v>90</v>
-      </c>
-      <c r="AH14">
-        <v>55</v>
-      </c>
-      <c r="AI14">
-        <v>70</v>
-      </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
       <c r="AQ14">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AR14">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS14">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT14">
         <v>8.800000000000001</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AV14">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AX14">
         <v>8.800000000000001</v>
@@ -4054,7 +4054,7 @@
         <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4140,10 +4140,10 @@
         <v>1.74</v>
       </c>
       <c r="G15">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H15">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I15">
         <v>5.8</v>
@@ -4161,142 +4161,142 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
         <v>1.35</v>
       </c>
       <c r="P15">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T15">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U15">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V15">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W15">
         <v>2.2</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y15">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="Z15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB15">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AE15">
         <v>100</v>
       </c>
       <c r="AF15">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AG15">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI15">
         <v>100</v>
       </c>
       <c r="AJ15">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AK15">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AL15">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP15">
-        <v>2.18</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AR15">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="AS15">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="AT15">
-        <v>1.82</v>
+        <v>7</v>
       </c>
       <c r="AU15">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV15">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AW15">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="AX15">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="AY15">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA15">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="BB15">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BC15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD15">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE15">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BF15">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="BG15">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4379,22 +4379,22 @@
         <v>126</v>
       </c>
       <c r="F16">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G16">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H16">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J16">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K16">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L16">
         <v>1.41</v>
@@ -4403,142 +4403,142 @@
         <v>1.09</v>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P16">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Q16">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S16">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T16">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="U16">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W16">
         <v>1.54</v>
       </c>
       <c r="X16">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Y16">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC16">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO16">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP16">
-        <v>1.41</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16">
-        <v>1.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT16">
-        <v>1.38</v>
+        <v>8.6</v>
       </c>
       <c r="AU16">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="AV16">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="AW16">
-        <v>1.46</v>
+        <v>5.7</v>
       </c>
       <c r="AX16">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="AY16">
-        <v>1.5</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>1.5</v>
+        <v>16</v>
       </c>
       <c r="BA16">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="BB16">
-        <v>1.51</v>
+        <v>5.8</v>
       </c>
       <c r="BC16">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD16">
-        <v>1.51</v>
+        <v>5.9</v>
       </c>
       <c r="BE16">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF16">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG16">
-        <v>1.46</v>
+        <v>5.7</v>
       </c>
       <c r="BH16">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -397,7 +397,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 03:37:03</t>
+    <t>2026-09-30 05:48:49</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
         <v>112</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G2">
         <v>2.12</v>
@@ -1000,7 +1000,7 @@
         <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
         <v>3.8</v>
@@ -1024,7 +1024,7 @@
         <v>2.1</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R2">
         <v>1.43</v>
@@ -1036,7 +1036,7 @@
         <v>1.72</v>
       </c>
       <c r="U2">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
         <v>1.35</v>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
         <v>21</v>
@@ -1093,22 +1093,22 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
         <v>44</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AQ2">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS2">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT2">
         <v>9.4</v>
@@ -1120,7 +1120,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1132,34 +1132,34 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF2">
         <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
         <v>3</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
         <v>7.2</v>
@@ -1204,7 +1204,7 @@
         <v>44</v>
       </c>
       <c r="BY2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         <v>113</v>
       </c>
       <c r="F3">
+        <v>1.52</v>
+      </c>
+      <c r="G3">
         <v>1.54</v>
       </c>
-      <c r="G3">
-        <v>1.58</v>
-      </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.33</v>
@@ -1260,13 +1260,13 @@
         <v>5</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
         <v>1.53</v>
@@ -1275,16 +1275,16 @@
         <v>2.76</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X3">
         <v>26</v>
@@ -1293,7 +1293,7 @@
         <v>29</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA3">
         <v>220</v>
@@ -1305,25 +1305,25 @@
         <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE3">
         <v>110</v>
       </c>
       <c r="AF3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK3">
         <v>17</v>
@@ -1335,7 +1335,7 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO3">
         <v>120</v>
@@ -1347,37 +1347,37 @@
         <v>22</v>
       </c>
       <c r="AR3">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT3">
         <v>9</v>
-      </c>
-      <c r="AT3">
-        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AW3">
+        <v>9.4</v>
+      </c>
+      <c r="AX3">
         <v>8.6</v>
       </c>
-      <c r="AX3">
+      <c r="AY3">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY3">
-        <v>9</v>
-      </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BA3">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC3">
         <v>13.5</v>
@@ -1386,13 +1386,13 @@
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
@@ -1401,49 +1401,49 @@
         <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BM3">
         <v>1.02</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
@@ -1452,7 +1452,7 @@
         <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
@@ -1475,10 +1475,10 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H4">
         <v>5.6</v>
@@ -1490,7 +1490,7 @@
         <v>3.95</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.43</v>
@@ -1499,7 +1499,7 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
         <v>1.36</v>
@@ -1517,16 +1517,16 @@
         <v>3.85</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X4">
         <v>16.5</v>
@@ -1583,58 +1583,58 @@
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR4">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
         <v>10</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
@@ -1717,22 +1717,22 @@
         <v>115</v>
       </c>
       <c r="F5">
+        <v>1.16</v>
+      </c>
+      <c r="G5">
         <v>1.18</v>
       </c>
-      <c r="G5">
-        <v>1.2</v>
-      </c>
       <c r="H5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>29</v>
       </c>
       <c r="J5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1741,37 +1741,37 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V5">
         <v>1.03</v>
       </c>
       <c r="W5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y5">
         <v>75</v>
@@ -1783,13 +1783,13 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>22</v>
       </c>
       <c r="AD5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1807,13 +1807,13 @@
         <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AK5">
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1825,28 +1825,28 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
         <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AV5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX5">
         <v>5.6</v>
@@ -1855,10 +1855,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB5">
         <v>6.4</v>
@@ -1867,34 +1867,34 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ5">
         <v>23</v>
       </c>
       <c r="BK5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
         <v>380</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN5">
         <v>3.4</v>
@@ -1906,37 +1906,37 @@
         <v>5.9</v>
       </c>
       <c r="BQ5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
         <v>36</v>
       </c>
       <c r="BU5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BV5">
         <v>430</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX5">
         <v>320</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
         <v>10.5</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="s">
         <v>127</v>
@@ -1962,7 +1962,7 @@
         <v>6.6</v>
       </c>
       <c r="G6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>1.55</v>
@@ -1977,40 +1977,40 @@
         <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
         <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R6">
         <v>1.62</v>
       </c>
       <c r="S6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6">
         <v>2.78</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
         <v>24</v>
@@ -2019,10 +2019,10 @@
         <v>11.5</v>
       </c>
       <c r="Z6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB6">
         <v>28</v>
@@ -2052,7 +2052,7 @@
         <v>200</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL6">
         <v>70</v>
@@ -2061,31 +2061,31 @@
         <v>85</v>
       </c>
       <c r="AN6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO6">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ6">
         <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU6">
         <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
         <v>13.5</v>
@@ -2103,7 +2103,7 @@
         <v>25</v>
       </c>
       <c r="BB6">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BC6">
         <v>65</v>
@@ -2118,67 +2118,67 @@
         <v>65</v>
       </c>
       <c r="BG6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH6">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BI6">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
+        <v>16</v>
+      </c>
+      <c r="BK6">
+        <v>7</v>
+      </c>
+      <c r="BL6">
+        <v>100</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>16.5</v>
+      </c>
+      <c r="BO6">
+        <v>7</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>5.1</v>
+      </c>
+      <c r="BU6">
+        <v>3.6</v>
+      </c>
+      <c r="BV6">
+        <v>16</v>
+      </c>
+      <c r="BW6">
+        <v>6.8</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
         <v>12</v>
       </c>
-      <c r="BK6">
-        <v>8.6</v>
-      </c>
-      <c r="BL6">
-        <v>120</v>
-      </c>
-      <c r="BM6">
-        <v>21</v>
-      </c>
-      <c r="BN6">
-        <v>12</v>
-      </c>
-      <c r="BO6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BP6">
-        <v>60</v>
-      </c>
-      <c r="BQ6">
-        <v>34</v>
-      </c>
-      <c r="BR6">
-        <v>55</v>
-      </c>
-      <c r="BS6">
-        <v>32</v>
-      </c>
-      <c r="BT6">
-        <v>4.4</v>
-      </c>
-      <c r="BU6">
-        <v>4</v>
-      </c>
-      <c r="BV6">
-        <v>9.4</v>
-      </c>
-      <c r="BW6">
-        <v>8.4</v>
-      </c>
-      <c r="BX6">
-        <v>25</v>
-      </c>
-      <c r="BY6">
-        <v>17</v>
-      </c>
       <c r="BZ6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>127</v>
@@ -2201,34 +2201,34 @@
         <v>117</v>
       </c>
       <c r="F7">
+        <v>1.26</v>
+      </c>
+      <c r="G7">
         <v>1.27</v>
       </c>
-      <c r="G7">
-        <v>1.28</v>
-      </c>
       <c r="H7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="I7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="J7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M7">
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P7">
         <v>3.15</v>
@@ -2237,43 +2237,43 @@
         <v>1.44</v>
       </c>
       <c r="R7">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="S7">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T7">
         <v>1.9</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
         <v>1.07</v>
       </c>
       <c r="W7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X7">
         <v>36</v>
       </c>
       <c r="Y7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z7">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA7">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
         <v>16</v>
       </c>
       <c r="AD7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AE7">
         <v>190</v>
@@ -2291,7 +2291,7 @@
         <v>140</v>
       </c>
       <c r="AJ7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK7">
         <v>13.5</v>
@@ -2306,7 +2306,7 @@
         <v>3.6</v>
       </c>
       <c r="AO7">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP7">
         <v>30</v>
@@ -2315,7 +2315,7 @@
         <v>48</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS7">
         <v>17.5</v>
@@ -2330,7 +2330,7 @@
         <v>38</v>
       </c>
       <c r="AW7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2342,7 +2342,7 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB7">
         <v>9.6</v>
@@ -2354,10 +2354,10 @@
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BG7">
         <v>55</v>
@@ -2443,13 +2443,13 @@
         <v>118</v>
       </c>
       <c r="F8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G8">
         <v>3.4</v>
       </c>
       <c r="H8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
         <v>2.38</v>
@@ -2461,7 +2461,7 @@
         <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2482,10 +2482,10 @@
         <v>1.36</v>
       </c>
       <c r="S8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U8">
         <v>2.16</v>
@@ -2500,7 +2500,7 @@
         <v>14</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
         <v>15.5</v>
@@ -2512,7 +2512,7 @@
         <v>13.5</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2596,7 +2596,7 @@
         <v>42</v>
       </c>
       <c r="BE8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF8">
         <v>30</v>
@@ -2685,7 +2685,7 @@
         <v>119</v>
       </c>
       <c r="F9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G9">
         <v>3.7</v>
@@ -2703,7 +2703,7 @@
         <v>3.85</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2721,7 +2721,7 @@
         <v>1.76</v>
       </c>
       <c r="R9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
         <v>2.88</v>
@@ -2730,10 +2730,10 @@
         <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W9">
         <v>1.37</v>
@@ -2766,7 +2766,7 @@
         <v>28</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH9">
         <v>16</v>
@@ -2775,7 +2775,7 @@
         <v>32</v>
       </c>
       <c r="AJ9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK9">
         <v>38</v>
@@ -2790,13 +2790,13 @@
         <v>32</v>
       </c>
       <c r="AO9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP9">
         <v>17</v>
       </c>
       <c r="AQ9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR9">
         <v>13.5</v>
@@ -2808,7 +2808,7 @@
         <v>15</v>
       </c>
       <c r="AU9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV9">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>18.5</v>
       </c>
       <c r="AX9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY9">
         <v>13.5</v>
@@ -2835,13 +2835,13 @@
         <v>34</v>
       </c>
       <c r="BD9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BF9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG9">
         <v>11.5</v>
@@ -2850,7 +2850,7 @@
         <v>3.8</v>
       </c>
       <c r="BI9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ9">
         <v>9</v>
@@ -2901,7 +2901,7 @@
         <v>19.5</v>
       </c>
       <c r="BZ9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA9">
         <v>15.5</v>
@@ -2927,13 +2927,13 @@
         <v>120</v>
       </c>
       <c r="F10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
         <v>1.32</v>
       </c>
       <c r="H10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I10">
         <v>16</v>
@@ -2945,19 +2945,19 @@
         <v>6.2</v>
       </c>
       <c r="L10">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
         <v>1.98</v>
@@ -2969,10 +2969,10 @@
         <v>3.9</v>
       </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V10">
         <v>1.06</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>14</v>
@@ -3011,10 +3011,10 @@
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI10">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="AJ10">
         <v>10</v>
@@ -3023,7 +3023,7 @@
         <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AM10">
         <v>510</v>
@@ -3035,40 +3035,40 @@
         <v>990</v>
       </c>
       <c r="AP10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AR10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY10">
         <v>11</v>
       </c>
       <c r="AZ10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BA10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10">
         <v>8.199999999999999</v>
@@ -3080,19 +3080,19 @@
         <v>55</v>
       </c>
       <c r="BE10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF10">
         <v>6.6</v>
       </c>
       <c r="BG10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH10">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BI10">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BJ10">
         <v>17.5</v>
@@ -3107,10 +3107,10 @@
         <v>21</v>
       </c>
       <c r="BN10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BP10">
         <v>7.8</v>
@@ -3125,7 +3125,7 @@
         <v>21</v>
       </c>
       <c r="BT10">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BU10">
         <v>14.5</v>
@@ -3169,16 +3169,16 @@
         <v>121</v>
       </c>
       <c r="F11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G11">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I11">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3199,7 +3199,7 @@
         <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
         <v>2.3</v>
@@ -3214,7 +3214,7 @@
         <v>1.99</v>
       </c>
       <c r="U11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V11">
         <v>1.78</v>
@@ -3244,10 +3244,10 @@
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG11">
         <v>16</v>
@@ -3274,13 +3274,13 @@
         <v>65</v>
       </c>
       <c r="AO11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP11">
         <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR11">
         <v>11.5</v>
@@ -3310,16 +3310,16 @@
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BC11">
         <v>44</v>
       </c>
       <c r="BD11">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="BE11">
         <v>14.5</v>
@@ -3334,7 +3334,7 @@
         <v>3</v>
       </c>
       <c r="BI11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3373,7 +3373,7 @@
         <v>4.4</v>
       </c>
       <c r="BV11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW11">
         <v>15</v>
@@ -3414,10 +3414,10 @@
         <v>3.65</v>
       </c>
       <c r="G12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I12">
         <v>2.18</v>
@@ -3426,7 +3426,7 @@
         <v>3.7</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
         <v>1.34</v>
@@ -3441,34 +3441,34 @@
         <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S12">
         <v>2.8</v>
       </c>
       <c r="T12">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U12">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z12">
         <v>15</v>
@@ -3519,7 +3519,7 @@
         <v>12</v>
       </c>
       <c r="AP12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12">
         <v>11</v>
@@ -3534,13 +3534,13 @@
         <v>16</v>
       </c>
       <c r="AU12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV12">
         <v>10</v>
       </c>
       <c r="AW12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX12">
         <v>26</v>
@@ -3552,22 +3552,22 @@
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD12">
         <v>38</v>
       </c>
       <c r="BE12">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG12">
         <v>11</v>
@@ -3612,13 +3612,13 @@
         <v>5.2</v>
       </c>
       <c r="BU12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV12">
         <v>17.5</v>
       </c>
       <c r="BW12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX12">
         <v>30</v>
@@ -3656,13 +3656,13 @@
         <v>1.68</v>
       </c>
       <c r="G13">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>3.35</v>
@@ -3677,22 +3677,22 @@
         <v>1.1</v>
       </c>
       <c r="N13">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="O13">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P13">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q13">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="S13">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="T13">
         <v>2.16</v>
@@ -3704,7 +3704,7 @@
         <v>1.16</v>
       </c>
       <c r="W13">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4137,37 +4137,37 @@
         <v>125</v>
       </c>
       <c r="F15">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="G15">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="H15">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J15">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
@@ -4179,124 +4179,124 @@
         <v>3.7</v>
       </c>
       <c r="T15">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U15">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="V15">
         <v>1.19</v>
       </c>
       <c r="W15">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X15">
         <v>16.5</v>
       </c>
       <c r="Y15">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Z15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA15">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE15">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF15">
         <v>10.5</v>
       </c>
       <c r="AG15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH15">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AI15">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ15">
+        <v>17.5</v>
+      </c>
+      <c r="AK15">
         <v>19</v>
       </c>
-      <c r="AK15">
-        <v>20</v>
-      </c>
       <c r="AL15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM15">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN15">
+        <v>14.5</v>
+      </c>
+      <c r="AO15">
+        <v>150</v>
+      </c>
+      <c r="AP15">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15">
         <v>15.5</v>
       </c>
-      <c r="AO15">
-        <v>130</v>
-      </c>
-      <c r="AP15">
-        <v>12</v>
-      </c>
-      <c r="AQ15">
-        <v>15</v>
-      </c>
       <c r="AR15">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="AS15">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AT15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU15">
         <v>7.6</v>
       </c>
       <c r="AV15">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="AW15">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX15">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AY15">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BA15">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD15">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE15">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BF15">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG15">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4385,7 +4385,7 @@
         <v>2.82</v>
       </c>
       <c r="H16">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I16">
         <v>3.15</v>
@@ -4400,19 +4400,19 @@
         <v>1.41</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O16">
         <v>1.41</v>
       </c>
       <c r="P16">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Q16">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R16">
         <v>1.27</v>
@@ -4427,10 +4427,10 @@
         <v>2.02</v>
       </c>
       <c r="V16">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X16">
         <v>12.5</v>
@@ -4457,7 +4457,7 @@
         <v>40</v>
       </c>
       <c r="AF16">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG16">
         <v>14.5</v>
@@ -4496,49 +4496,49 @@
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT16">
         <v>8.6</v>
       </c>
       <c r="AU16">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV16">
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX16">
         <v>15</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
+        <v>6.2</v>
+      </c>
+      <c r="BB16">
         <v>6</v>
       </c>
-      <c r="BB16">
-        <v>5.8</v>
-      </c>
       <c r="BC16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD16">
+        <v>6</v>
+      </c>
+      <c r="BE16">
+        <v>6.4</v>
+      </c>
+      <c r="BF16">
+        <v>5.7</v>
+      </c>
+      <c r="BG16">
         <v>5.9</v>
-      </c>
-      <c r="BE16">
-        <v>6.2</v>
-      </c>
-      <c r="BF16">
-        <v>5.5</v>
-      </c>
-      <c r="BG16">
-        <v>5.7</v>
       </c>
       <c r="BH16">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -340,7 +340,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 07:58:21</t>
+    <t>2026-09-30 10:09:30</t>
   </si>
 </sst>
 </file>
@@ -937,19 +937,19 @@
         <v>2.08</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
         <v>3.8</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -961,13 +961,13 @@
         <v>4.1</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
         <v>2.08</v>
       </c>
       <c r="Q2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
         <v>1.42</v>
@@ -976,7 +976,7 @@
         <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -985,13 +985,13 @@
         <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z2">
         <v>28</v>
@@ -1003,19 +1003,19 @@
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>18.5</v>
@@ -1036,7 +1036,7 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO2">
         <v>44</v>
@@ -1048,10 +1048,10 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1063,7 +1063,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1075,7 +1075,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BB2">
         <v>20</v>
@@ -1084,16 +1084,16 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BH2">
         <v>4.1</v>
@@ -1176,22 +1176,22 @@
         <v>102</v>
       </c>
       <c r="F3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G3">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>8.6</v>
       </c>
       <c r="J3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.32</v>
@@ -1203,7 +1203,7 @@
         <v>5</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
         <v>2.34</v>
@@ -1218,7 +1218,7 @@
         <v>2.76</v>
       </c>
       <c r="T3">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
         <v>2.04</v>
@@ -1227,19 +1227,19 @@
         <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z3">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AA3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1251,73 +1251,73 @@
         <v>32</v>
       </c>
       <c r="AE3">
+        <v>150</v>
+      </c>
+      <c r="AF3">
+        <v>11</v>
+      </c>
+      <c r="AG3">
+        <v>12</v>
+      </c>
+      <c r="AH3">
+        <v>22</v>
+      </c>
+      <c r="AI3">
         <v>120</v>
       </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>10.5</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>100</v>
-      </c>
       <c r="AJ3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO3">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
+        <v>26</v>
+      </c>
+      <c r="AR3">
+        <v>55</v>
+      </c>
+      <c r="AS3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3">
         <v>23</v>
       </c>
-      <c r="AR3">
-        <v>6.6</v>
-      </c>
-      <c r="AS3">
-        <v>7</v>
-      </c>
-      <c r="AT3">
-        <v>9</v>
-      </c>
-      <c r="AU3">
-        <v>9.4</v>
-      </c>
-      <c r="AV3">
-        <v>5.9</v>
-      </c>
       <c r="AW3">
-        <v>6.8</v>
+        <v>65</v>
       </c>
       <c r="AX3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>11.5</v>
@@ -1326,25 +1326,25 @@
         <v>13</v>
       </c>
       <c r="BD3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BE3">
-        <v>6.8</v>
+        <v>65</v>
       </c>
       <c r="BF3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>70</v>
       </c>
       <c r="BH3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
         <v>3.2</v>
       </c>
       <c r="BJ3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1353,19 +1353,19 @@
         <v>150</v>
       </c>
       <c r="BM3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
         <v>9.4</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
         <v>24</v>
@@ -1377,7 +1377,7 @@
         <v>11.5</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BV3">
         <v>65</v>
@@ -1392,7 +1392,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1418,13 +1418,13 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>6.2</v>
@@ -1433,49 +1433,49 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
+        <v>3.75</v>
+      </c>
+      <c r="O4">
+        <v>1.33</v>
+      </c>
+      <c r="P4">
+        <v>1.94</v>
+      </c>
+      <c r="Q4">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <v>1.36</v>
+      </c>
+      <c r="S4">
         <v>3.6</v>
       </c>
-      <c r="O4">
-        <v>1.35</v>
-      </c>
-      <c r="P4">
-        <v>1.88</v>
-      </c>
-      <c r="Q4">
-        <v>2.06</v>
-      </c>
-      <c r="R4">
-        <v>1.33</v>
-      </c>
-      <c r="S4">
-        <v>3.75</v>
-      </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V4">
         <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X4">
         <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z4">
         <v>60</v>
@@ -1484,7 +1484,7 @@
         <v>210</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>9.4</v>
@@ -1502,52 +1502,52 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS4">
         <v>6.6</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX4">
         <v>8.199999999999999</v>
@@ -1559,31 +1559,31 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC4">
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
         <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1592,34 +1592,34 @@
         <v>8</v>
       </c>
       <c r="BL4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
         <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS4">
         <v>20</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV4">
         <v>70</v>
@@ -1660,7 +1660,7 @@
         <v>104</v>
       </c>
       <c r="F5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G5">
         <v>1.92</v>
@@ -1684,7 +1684,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
         <v>1.45</v>
@@ -1693,7 +1693,7 @@
         <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
         <v>1.13</v>
@@ -1705,13 +1705,13 @@
         <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
         <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1902,10 +1902,10 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="G6">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="H6">
         <v>1.29</v>
@@ -1914,13 +1914,13 @@
         <v>1.31</v>
       </c>
       <c r="J6">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="K6">
         <v>6.8</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -1932,16 +1932,16 @@
         <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
         <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T6">
         <v>2.28</v>
@@ -1977,7 +1977,7 @@
         <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AF6">
         <v>220</v>
@@ -1986,7 +1986,7 @@
         <v>75</v>
       </c>
       <c r="AH6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI6">
         <v>65</v>
@@ -2010,58 +2010,58 @@
         <v>5.6</v>
       </c>
       <c r="AP6">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6">
         <v>7.2</v>
       </c>
       <c r="AR6">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6">
         <v>4.6</v>
       </c>
       <c r="AX6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY6">
+        <v>5.9</v>
+      </c>
+      <c r="AZ6">
         <v>5.7</v>
       </c>
-      <c r="AZ6">
-        <v>5.6</v>
-      </c>
       <c r="BA6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB6">
+        <v>6.4</v>
+      </c>
+      <c r="BC6">
+        <v>6.4</v>
+      </c>
+      <c r="BD6">
         <v>6.2</v>
       </c>
-      <c r="BC6">
+      <c r="BE6">
         <v>6.2</v>
       </c>
-      <c r="BD6">
-        <v>6</v>
-      </c>
-      <c r="BE6">
-        <v>6</v>
-      </c>
       <c r="BF6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2144,19 +2144,19 @@
         <v>106</v>
       </c>
       <c r="F7">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -2168,22 +2168,22 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T7">
         <v>2</v>
@@ -2192,88 +2192,88 @@
         <v>1.88</v>
       </c>
       <c r="V7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y7">
         <v>18</v>
       </c>
       <c r="Z7">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB7">
         <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM7">
         <v>180</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR7">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AS7">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
       </c>
       <c r="AU7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AW7">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="AX7">
         <v>8.199999999999999</v>
@@ -2282,10 +2282,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BB7">
         <v>14.5</v>
@@ -2294,16 +2294,16 @@
         <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="BE7">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2386,7 +2386,7 @@
         <v>107</v>
       </c>
       <c r="F8">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G8">
         <v>2.8</v>
@@ -2404,13 +2404,13 @@
         <v>3.4</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
         <v>1.42</v>
@@ -2419,10 +2419,10 @@
         <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
         <v>4.2</v>
@@ -2434,37 +2434,37 @@
         <v>2</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
         <v>11</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA8">
         <v>60</v>
       </c>
       <c r="AB8">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2476,10 +2476,10 @@
         <v>65</v>
       </c>
       <c r="AJ8">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AK8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL8">
         <v>60</v>
@@ -2488,10 +2488,10 @@
         <v>140</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP8">
         <v>9.800000000000001</v>
@@ -2503,7 +2503,7 @@
         <v>16.5</v>
       </c>
       <c r="AS8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT8">
         <v>8.4</v>
@@ -2515,97 +2515,97 @@
         <v>12</v>
       </c>
       <c r="AW8">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX8">
         <v>15</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
         <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB8">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC8">
+        <v>7.2</v>
+      </c>
+      <c r="BD8">
+        <v>8</v>
+      </c>
+      <c r="BE8">
+        <v>7.8</v>
+      </c>
+      <c r="BF8">
+        <v>7.4</v>
+      </c>
+      <c r="BG8">
+        <v>7.6</v>
+      </c>
+      <c r="BH8">
+        <v>3.4</v>
+      </c>
+      <c r="BI8">
+        <v>2.54</v>
+      </c>
+      <c r="BJ8">
+        <v>11.5</v>
+      </c>
+      <c r="BK8">
+        <v>3.95</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
         <v>5.8</v>
       </c>
-      <c r="BD8">
-        <v>6</v>
-      </c>
-      <c r="BE8">
+      <c r="BN8">
         <v>6.4</v>
       </c>
-      <c r="BF8">
-        <v>5.8</v>
-      </c>
-      <c r="BG8">
-        <v>5.9</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.01</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB8" t="s">
         <v>108</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>CONCACAF Nations League B</t>
   </si>
   <si>
@@ -310,6 +313,9 @@
     <t>Envigado</t>
   </si>
   <si>
+    <t>Cumbaya FC</t>
+  </si>
+  <si>
     <t>Dominica</t>
   </si>
   <si>
@@ -331,6 +337,9 @@
     <t>Orsomarso</t>
   </si>
   <si>
+    <t>Deportivo Santo Domingo</t>
+  </si>
+  <si>
     <t>Guyana</t>
   </si>
   <si>
@@ -340,7 +349,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 10:09:30</t>
+    <t>2026-09-30 12:19:18</t>
   </si>
 </sst>
 </file>
@@ -672,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -922,16 +931,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F2">
         <v>2.08</v>
@@ -949,7 +958,7 @@
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -958,25 +967,25 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
         <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2">
         <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -997,19 +1006,19 @@
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
@@ -1021,7 +1030,7 @@
         <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
         <v>28</v>
@@ -1036,10 +1045,10 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP2">
         <v>14</v>
@@ -1054,7 +1063,7 @@
         <v>50</v>
       </c>
       <c r="AT2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
@@ -1063,7 +1072,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1090,22 +1099,22 @@
         <v>65</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG2">
         <v>24</v>
       </c>
       <c r="BH2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>120</v>
@@ -1126,28 +1135,28 @@
         <v>11</v>
       </c>
       <c r="BR2">
+        <v>30</v>
+      </c>
+      <c r="BS2">
+        <v>19.5</v>
+      </c>
+      <c r="BT2">
+        <v>8</v>
+      </c>
+      <c r="BU2">
+        <v>5.5</v>
+      </c>
+      <c r="BV2">
         <v>32</v>
-      </c>
-      <c r="BS2">
-        <v>20</v>
-      </c>
-      <c r="BT2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU2">
-        <v>5.6</v>
-      </c>
-      <c r="BV2">
-        <v>34</v>
       </c>
       <c r="BW2">
         <v>21</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1156,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1164,25 +1173,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>8.6</v>
@@ -1191,7 +1200,7 @@
         <v>4.5</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
         <v>1.32</v>
@@ -1200,13 +1209,13 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
@@ -1215,7 +1224,7 @@
         <v>1.53</v>
       </c>
       <c r="S3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
         <v>1.87</v>
@@ -1227,7 +1236,7 @@
         <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X3">
         <v>25</v>
@@ -1236,10 +1245,10 @@
         <v>32</v>
       </c>
       <c r="Z3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA3">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1254,16 +1263,16 @@
         <v>150</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>22</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
         <v>13.5</v>
@@ -1287,13 +1296,13 @@
         <v>18</v>
       </c>
       <c r="AQ3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR3">
         <v>55</v>
       </c>
       <c r="AS3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT3">
         <v>9.199999999999999</v>
@@ -1302,7 +1311,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3">
         <v>65</v>
@@ -1347,13 +1356,13 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3">
         <v>150</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN3">
         <v>4.3</v>
@@ -1395,10 +1404,10 @@
         <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1406,16 +1415,16 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F4">
         <v>1.67</v>
@@ -1424,7 +1433,7 @@
         <v>1.71</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
         <v>6.2</v>
@@ -1433,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.41</v>
@@ -1442,28 +1451,28 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
         <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R4">
         <v>1.36</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
         <v>1.19</v>
@@ -1475,13 +1484,13 @@
         <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z4">
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -1490,67 +1499,67 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE4">
         <v>110</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM4">
         <v>160</v>
       </c>
       <c r="AN4">
+        <v>11</v>
+      </c>
+      <c r="AO4">
+        <v>130</v>
+      </c>
+      <c r="AP4">
         <v>13</v>
       </c>
-      <c r="AO4">
-        <v>140</v>
-      </c>
-      <c r="AP4">
-        <v>12.5</v>
-      </c>
       <c r="AQ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR4">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AS4">
-        <v>6.6</v>
+        <v>100</v>
       </c>
       <c r="AT4">
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="AX4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
@@ -1559,7 +1568,7 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>14.5</v>
@@ -1568,16 +1577,16 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>5.9</v>
+        <v>26</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>90</v>
       </c>
       <c r="BF4">
         <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
@@ -1622,7 +1631,7 @@
         <v>7</v>
       </c>
       <c r="BV4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW4">
         <v>38</v>
@@ -1640,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1648,34 +1657,34 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G5">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1693,13 +1702,13 @@
         <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T5">
         <v>2.16</v>
@@ -1711,7 +1720,7 @@
         <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1882,7 +1891,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1890,178 +1899,178 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F6">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
-        <v>1.31</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>1.24</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2124,7 +2133,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2132,184 +2141,184 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>1.66</v>
+        <v>15.5</v>
       </c>
       <c r="G7">
-        <v>1.68</v>
+        <v>16.5</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>1.29</v>
       </c>
       <c r="I7">
+        <v>1.31</v>
+      </c>
+      <c r="J7">
+        <v>5.7</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1.3</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
+        <v>4.5</v>
+      </c>
+      <c r="O7">
+        <v>1.22</v>
+      </c>
+      <c r="P7">
+        <v>2.2</v>
+      </c>
+      <c r="Q7">
+        <v>1.64</v>
+      </c>
+      <c r="R7">
+        <v>1.49</v>
+      </c>
+      <c r="S7">
+        <v>2.62</v>
+      </c>
+      <c r="T7">
+        <v>2.28</v>
+      </c>
+      <c r="U7">
+        <v>1.61</v>
+      </c>
+      <c r="V7">
+        <v>4.2</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>26</v>
+      </c>
+      <c r="Y7">
+        <v>9</v>
+      </c>
+      <c r="Z7">
+        <v>7.8</v>
+      </c>
+      <c r="AA7">
+        <v>9.6</v>
+      </c>
+      <c r="AB7">
+        <v>55</v>
+      </c>
+      <c r="AC7">
+        <v>15.5</v>
+      </c>
+      <c r="AD7">
+        <v>12.5</v>
+      </c>
+      <c r="AE7">
+        <v>16.5</v>
+      </c>
+      <c r="AF7">
+        <v>220</v>
+      </c>
+      <c r="AG7">
+        <v>75</v>
+      </c>
+      <c r="AH7">
+        <v>48</v>
+      </c>
+      <c r="AI7">
+        <v>65</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>440</v>
+      </c>
+      <c r="AL7">
+        <v>310</v>
+      </c>
+      <c r="AM7">
+        <v>320</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>5.6</v>
+      </c>
+      <c r="AP7">
+        <v>17.5</v>
+      </c>
+      <c r="AQ7">
+        <v>7.2</v>
+      </c>
+      <c r="AR7">
+        <v>6.2</v>
+      </c>
+      <c r="AS7">
+        <v>7.6</v>
+      </c>
+      <c r="AT7">
+        <v>5.8</v>
+      </c>
+      <c r="AU7">
+        <v>10.5</v>
+      </c>
+      <c r="AV7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW7">
+        <v>4.6</v>
+      </c>
+      <c r="AX7">
+        <v>6.2</v>
+      </c>
+      <c r="AY7">
+        <v>14.5</v>
+      </c>
+      <c r="AZ7">
+        <v>5.7</v>
+      </c>
+      <c r="BA7">
+        <v>13</v>
+      </c>
+      <c r="BB7">
         <v>6.4</v>
       </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4.2</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.07</v>
-      </c>
-      <c r="N7">
-        <v>3.55</v>
-      </c>
-      <c r="O7">
-        <v>1.34</v>
-      </c>
-      <c r="P7">
-        <v>1.86</v>
-      </c>
-      <c r="Q7">
-        <v>2.04</v>
-      </c>
-      <c r="R7">
-        <v>1.33</v>
-      </c>
-      <c r="S7">
-        <v>3.65</v>
-      </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7">
-        <v>1.88</v>
-      </c>
-      <c r="V7">
-        <v>1.18</v>
-      </c>
-      <c r="W7">
-        <v>2.46</v>
-      </c>
-      <c r="X7">
-        <v>14</v>
-      </c>
-      <c r="Y7">
-        <v>18</v>
-      </c>
-      <c r="Z7">
-        <v>70</v>
-      </c>
-      <c r="AA7">
-        <v>200</v>
-      </c>
-      <c r="AB7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>25</v>
-      </c>
-      <c r="AE7">
-        <v>110</v>
-      </c>
-      <c r="AF7">
-        <v>9.4</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>32</v>
-      </c>
-      <c r="AI7">
-        <v>110</v>
-      </c>
-      <c r="AJ7">
-        <v>16.5</v>
-      </c>
-      <c r="AK7">
-        <v>19</v>
-      </c>
-      <c r="AL7">
-        <v>48</v>
-      </c>
-      <c r="AM7">
-        <v>180</v>
-      </c>
-      <c r="AN7">
-        <v>12</v>
-      </c>
-      <c r="AO7">
-        <v>150</v>
-      </c>
-      <c r="AP7">
-        <v>12</v>
-      </c>
-      <c r="AQ7">
-        <v>16</v>
-      </c>
-      <c r="AR7">
-        <v>40</v>
-      </c>
-      <c r="AS7">
-        <v>12</v>
-      </c>
-      <c r="AT7">
-        <v>7.2</v>
-      </c>
-      <c r="AU7">
-        <v>8</v>
-      </c>
-      <c r="AV7">
-        <v>20</v>
-      </c>
-      <c r="AW7">
-        <v>12</v>
-      </c>
-      <c r="AX7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7">
-        <v>20</v>
-      </c>
-      <c r="BA7">
-        <v>12</v>
-      </c>
-      <c r="BB7">
-        <v>14.5</v>
-      </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD7">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>12.5</v>
+        <v>3.7</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2366,7 +2375,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2374,241 +2383,483 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F8">
+        <v>1.66</v>
+      </c>
+      <c r="G8">
+        <v>1.68</v>
+      </c>
+      <c r="H8">
+        <v>5.8</v>
+      </c>
+      <c r="I8">
+        <v>6.4</v>
+      </c>
+      <c r="J8">
+        <v>3.95</v>
+      </c>
+      <c r="K8">
+        <v>4.2</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.07</v>
+      </c>
+      <c r="N8">
+        <v>3.55</v>
+      </c>
+      <c r="O8">
+        <v>1.34</v>
+      </c>
+      <c r="P8">
+        <v>1.86</v>
+      </c>
+      <c r="Q8">
+        <v>2.04</v>
+      </c>
+      <c r="R8">
+        <v>1.33</v>
+      </c>
+      <c r="S8">
+        <v>3.65</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8">
+        <v>1.88</v>
+      </c>
+      <c r="V8">
+        <v>1.19</v>
+      </c>
+      <c r="W8">
+        <v>2.46</v>
+      </c>
+      <c r="X8">
+        <v>14</v>
+      </c>
+      <c r="Y8">
+        <v>18</v>
+      </c>
+      <c r="Z8">
+        <v>70</v>
+      </c>
+      <c r="AA8">
+        <v>200</v>
+      </c>
+      <c r="AB8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD8">
+        <v>25</v>
+      </c>
+      <c r="AE8">
+        <v>110</v>
+      </c>
+      <c r="AF8">
+        <v>9.4</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+      <c r="AH8">
+        <v>32</v>
+      </c>
+      <c r="AI8">
+        <v>110</v>
+      </c>
+      <c r="AJ8">
+        <v>16.5</v>
+      </c>
+      <c r="AK8">
+        <v>19</v>
+      </c>
+      <c r="AL8">
+        <v>48</v>
+      </c>
+      <c r="AM8">
+        <v>180</v>
+      </c>
+      <c r="AN8">
+        <v>12</v>
+      </c>
+      <c r="AO8">
+        <v>150</v>
+      </c>
+      <c r="AP8">
+        <v>12</v>
+      </c>
+      <c r="AQ8">
+        <v>16</v>
+      </c>
+      <c r="AR8">
+        <v>40</v>
+      </c>
+      <c r="AS8">
+        <v>12.5</v>
+      </c>
+      <c r="AT8">
+        <v>7.2</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AW8">
+        <v>12</v>
+      </c>
+      <c r="AX8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY8">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8">
+        <v>20</v>
+      </c>
+      <c r="BA8">
+        <v>12</v>
+      </c>
+      <c r="BB8">
+        <v>14.5</v>
+      </c>
+      <c r="BC8">
+        <v>16.5</v>
+      </c>
+      <c r="BD8">
+        <v>17.5</v>
+      </c>
+      <c r="BE8">
+        <v>12.5</v>
+      </c>
+      <c r="BF8">
+        <v>10</v>
+      </c>
+      <c r="BG8">
+        <v>12.5</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>2.8</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
         <v>2.68</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>2.8</v>
       </c>
-      <c r="H8">
-        <v>2.98</v>
-      </c>
-      <c r="I8">
+      <c r="H9">
+        <v>2.96</v>
+      </c>
+      <c r="I9">
         <v>3.1</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <v>3.2</v>
       </c>
-      <c r="K8">
+      <c r="K9">
         <v>3.4</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <v>1.47</v>
       </c>
-      <c r="M8">
+      <c r="M9">
         <v>1.09</v>
       </c>
-      <c r="N8">
-        <v>3.2</v>
-      </c>
-      <c r="O8">
+      <c r="N9">
+        <v>3.15</v>
+      </c>
+      <c r="O9">
         <v>1.42</v>
       </c>
-      <c r="P8">
+      <c r="P9">
         <v>1.72</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <v>2.26</v>
       </c>
-      <c r="R8">
+      <c r="R9">
         <v>1.28</v>
       </c>
-      <c r="S8">
+      <c r="S9">
         <v>4.2</v>
       </c>
-      <c r="T8">
+      <c r="T9">
         <v>1.89</v>
       </c>
-      <c r="U8">
+      <c r="U9">
         <v>2</v>
       </c>
-      <c r="V8">
+      <c r="V9">
         <v>1.48</v>
       </c>
-      <c r="W8">
+      <c r="W9">
         <v>1.56</v>
       </c>
-      <c r="X8">
+      <c r="X9">
         <v>11.5</v>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <v>11</v>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <v>21</v>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <v>60</v>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <v>9.6</v>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <v>7.4</v>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <v>14.5</v>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <v>42</v>
       </c>
-      <c r="AF8">
+      <c r="AF9">
         <v>18.5</v>
       </c>
-      <c r="AG8">
+      <c r="AG9">
         <v>14.5</v>
       </c>
-      <c r="AH8">
+      <c r="AH9">
         <v>22</v>
       </c>
-      <c r="AI8">
+      <c r="AI9">
         <v>65</v>
       </c>
-      <c r="AJ8">
+      <c r="AJ9">
         <v>110</v>
       </c>
-      <c r="AK8">
+      <c r="AK9">
         <v>36</v>
       </c>
-      <c r="AL8">
+      <c r="AL9">
         <v>60</v>
       </c>
-      <c r="AM8">
+      <c r="AM9">
         <v>140</v>
       </c>
-      <c r="AN8">
+      <c r="AN9">
         <v>38</v>
       </c>
-      <c r="AO8">
+      <c r="AO9">
         <v>42</v>
       </c>
-      <c r="AP8">
+      <c r="AP9">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ8">
+      <c r="AQ9">
         <v>9.4</v>
       </c>
-      <c r="AR8">
+      <c r="AR9">
         <v>16.5</v>
       </c>
-      <c r="AS8">
+      <c r="AS9">
         <v>8</v>
       </c>
-      <c r="AT8">
+      <c r="AT9">
         <v>8.4</v>
       </c>
-      <c r="AU8">
+      <c r="AU9">
         <v>6.4</v>
       </c>
-      <c r="AV8">
+      <c r="AV9">
         <v>12</v>
       </c>
-      <c r="AW8">
+      <c r="AW9">
         <v>7.6</v>
       </c>
-      <c r="AX8">
+      <c r="AX9">
         <v>15</v>
       </c>
-      <c r="AY8">
+      <c r="AY9">
         <v>11</v>
       </c>
-      <c r="AZ8">
+      <c r="AZ9">
         <v>16.5</v>
       </c>
-      <c r="BA8">
+      <c r="BA9">
         <v>8</v>
       </c>
-      <c r="BB8">
+      <c r="BB9">
         <v>7.6</v>
       </c>
-      <c r="BC8">
+      <c r="BC9">
         <v>7.2</v>
       </c>
-      <c r="BD8">
+      <c r="BD9">
         <v>8</v>
       </c>
-      <c r="BE8">
+      <c r="BE9">
         <v>7.8</v>
       </c>
-      <c r="BF8">
+      <c r="BF9">
         <v>7.4</v>
       </c>
-      <c r="BG8">
+      <c r="BG9">
         <v>7.6</v>
       </c>
-      <c r="BH8">
+      <c r="BH9">
         <v>3.4</v>
       </c>
-      <c r="BI8">
+      <c r="BI9">
         <v>2.54</v>
       </c>
-      <c r="BJ8">
+      <c r="BJ9">
         <v>11.5</v>
       </c>
-      <c r="BK8">
+      <c r="BK9">
         <v>3.95</v>
       </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
         <v>5.8</v>
       </c>
-      <c r="BN8">
+      <c r="BN9">
         <v>6.4</v>
       </c>
-      <c r="BO8">
+      <c r="BO9">
         <v>5.1</v>
       </c>
-      <c r="BP8">
+      <c r="BP9">
         <v>27</v>
       </c>
-      <c r="BQ8">
+      <c r="BQ9">
         <v>4.9</v>
       </c>
-      <c r="BR8">
+      <c r="BR9">
         <v>46</v>
       </c>
-      <c r="BS8">
+      <c r="BS9">
         <v>5.3</v>
       </c>
-      <c r="BT8">
+      <c r="BT9">
         <v>6.6</v>
       </c>
-      <c r="BU8">
+      <c r="BU9">
         <v>5.2</v>
       </c>
-      <c r="BV8">
+      <c r="BV9">
         <v>28</v>
       </c>
-      <c r="BW8">
+      <c r="BW9">
         <v>4.9</v>
       </c>
-      <c r="BX8">
+      <c r="BX9">
         <v>46</v>
       </c>
-      <c r="BY8">
+      <c r="BY9">
         <v>5.3</v>
       </c>
-      <c r="BZ8">
+      <c r="BZ9">
         <v>42</v>
       </c>
-      <c r="CA8">
+      <c r="CA9">
         <v>5.2</v>
       </c>
-      <c r="CB8" t="s">
-        <v>108</v>
+      <c r="CB9" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -349,7 +349,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 12:19:18</t>
+    <t>2026-09-30 14:31:07</t>
   </si>
 </sst>
 </file>
@@ -943,19 +943,19 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
         <v>3.9</v>
@@ -970,31 +970,31 @@
         <v>4.2</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R2">
         <v>1.43</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X2">
         <v>19</v>
@@ -1009,7 +1009,7 @@
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2">
         <v>9</v>
@@ -1024,10 +1024,10 @@
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI2">
         <v>48</v>
@@ -1039,28 +1039,28 @@
         <v>23</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP2">
         <v>14</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT2">
         <v>9.4</v>
@@ -1084,10 +1084,10 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
@@ -1096,31 +1096,31 @@
         <v>25</v>
       </c>
       <c r="BE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>120</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>5.7</v>
@@ -1132,31 +1132,31 @@
         <v>17</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>19.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW2">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>27</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1185,49 +1185,49 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>4.5</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S3">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T3">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U3">
         <v>2.04</v>
@@ -1239,19 +1239,19 @@
         <v>2.92</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z3">
         <v>90</v>
       </c>
       <c r="AA3">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
         <v>11</v>
@@ -1263,37 +1263,37 @@
         <v>150</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>22</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
         <v>13.5</v>
       </c>
       <c r="AK3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AN3">
         <v>6.6</v>
       </c>
       <c r="AO3">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3">
         <v>25</v>
@@ -1302,22 +1302,22 @@
         <v>55</v>
       </c>
       <c r="AS3">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV3">
         <v>24</v>
       </c>
       <c r="AW3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
@@ -1335,16 +1335,16 @@
         <v>13</v>
       </c>
       <c r="BD3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF3">
         <v>5.7</v>
       </c>
       <c r="BG3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
@@ -1362,16 +1362,16 @@
         <v>150</v>
       </c>
       <c r="BM3">
-        <v>1.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO3">
         <v>3.55</v>
       </c>
       <c r="BP3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ3">
         <v>6.8</v>
@@ -1380,7 +1380,7 @@
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT3">
         <v>11.5</v>
@@ -1392,19 +1392,19 @@
         <v>65</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>70</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
         <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,67 +1427,67 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
         <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q4">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U4">
         <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="X4">
         <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA4">
         <v>200</v>
@@ -1496,16 +1496,16 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE4">
         <v>110</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1514,22 +1514,22 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
+        <v>17</v>
+      </c>
+      <c r="AK4">
         <v>18.5</v>
       </c>
-      <c r="AK4">
-        <v>19.5</v>
-      </c>
       <c r="AL4">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM4">
         <v>160</v>
       </c>
       <c r="AN4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
         <v>130</v>
@@ -1538,25 +1538,25 @@
         <v>13</v>
       </c>
       <c r="AQ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS4">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AT4">
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV4">
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX4">
         <v>8.6</v>
@@ -1565,7 +1565,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA4">
         <v>50</v>
@@ -1574,7 +1574,7 @@
         <v>14.5</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD4">
         <v>26</v>
@@ -1583,28 +1583,28 @@
         <v>90</v>
       </c>
       <c r="BF4">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>180</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>4.8</v>
@@ -1613,34 +1613,34 @@
         <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS4">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>65</v>
       </c>
       <c r="BW4">
-        <v>38</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>44</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>1.66</v>
       </c>
       <c r="G5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H5">
         <v>5.3</v>
@@ -1684,7 +1684,7 @@
         <v>3.45</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1702,7 +1702,7 @@
         <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1720,7 +1720,7 @@
         <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1834,61 +1834,61 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>111</v>
@@ -1914,13 +1914,13 @@
         <v>1.1</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H6">
         <v>1.1</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J6">
         <v>1.1</v>
@@ -1935,22 +1935,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2076,61 +2076,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M7">
         <v>1.04</v>
@@ -2192,7 +2192,7 @@
         <v>1.49</v>
       </c>
       <c r="S7">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T7">
         <v>2.28</v>
@@ -2288,13 +2288,13 @@
         <v>6.2</v>
       </c>
       <c r="AY7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AZ7">
         <v>5.7</v>
       </c>
       <c r="BA7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7">
         <v>6.4</v>
@@ -2318,61 +2318,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,19 +2395,19 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H8">
         <v>5.8</v>
       </c>
       <c r="I8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>4.2</v>
@@ -2428,16 +2428,16 @@
         <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>1.33</v>
       </c>
       <c r="S8">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U8">
         <v>1.88</v>
@@ -2446,13 +2446,13 @@
         <v>1.19</v>
       </c>
       <c r="W8">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z8">
         <v>70</v>
@@ -2467,7 +2467,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE8">
         <v>110</v>
@@ -2479,7 +2479,7 @@
         <v>10</v>
       </c>
       <c r="AH8">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI8">
         <v>110</v>
@@ -2488,16 +2488,16 @@
         <v>16.5</v>
       </c>
       <c r="AK8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL8">
         <v>48</v>
       </c>
       <c r="AM8">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO8">
         <v>150</v>
@@ -2512,7 +2512,7 @@
         <v>40</v>
       </c>
       <c r="AS8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT8">
         <v>7.2</v>
@@ -2524,7 +2524,7 @@
         <v>20</v>
       </c>
       <c r="AW8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX8">
         <v>8.199999999999999</v>
@@ -2536,7 +2536,7 @@
         <v>20</v>
       </c>
       <c r="BA8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB8">
         <v>14.5</v>
@@ -2545,76 +2545,76 @@
         <v>16.5</v>
       </c>
       <c r="BD8">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF8">
         <v>10</v>
       </c>
       <c r="BG8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2661,7 +2661,7 @@
         <v>1.09</v>
       </c>
       <c r="N9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
         <v>1.42</v>
@@ -2670,7 +2670,7 @@
         <v>1.72</v>
       </c>
       <c r="Q9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R9">
         <v>1.28</v>
@@ -2760,7 +2760,7 @@
         <v>8.4</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
         <v>12</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -349,7 +349,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 14:31:07</t>
+    <t>2026-09-30 16:43:55</t>
   </si>
 </sst>
 </file>
@@ -943,13 +943,13 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
         <v>2.16</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
         <v>3.75</v>
@@ -979,7 +979,7 @@
         <v>1.84</v>
       </c>
       <c r="R2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S2">
         <v>3.15</v>
@@ -988,7 +988,7 @@
         <v>1.72</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
         <v>1.36</v>
@@ -997,7 +997,7 @@
         <v>1.86</v>
       </c>
       <c r="X2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y2">
         <v>16</v>
@@ -1042,7 +1042,7 @@
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN2">
         <v>14</v>
@@ -1057,13 +1057,13 @@
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS2">
         <v>46</v>
       </c>
       <c r="AT2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
@@ -1087,7 +1087,7 @@
         <v>32</v>
       </c>
       <c r="BB2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
@@ -1108,19 +1108,19 @@
         <v>4.1</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL2">
         <v>120</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
         <v>5.7</v>
@@ -1132,31 +1132,31 @@
         <v>17</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU2">
         <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1185,19 +1185,19 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
         <v>4.9</v>
@@ -1218,7 +1218,7 @@
         <v>2.3</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
         <v>1.51</v>
@@ -1230,67 +1230,67 @@
         <v>1.91</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V3">
         <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA3">
         <v>280</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC3">
         <v>11</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE3">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AF3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
         <v>22</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
         <v>13.5</v>
       </c>
       <c r="AK3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL3">
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AN3">
         <v>6.6</v>
       </c>
       <c r="AO3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP3">
         <v>17.5</v>
@@ -1302,7 +1302,7 @@
         <v>55</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
@@ -1311,37 +1311,37 @@
         <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW3">
         <v>70</v>
       </c>
       <c r="AX3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE3">
         <v>70</v>
       </c>
       <c r="BF3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG3">
         <v>75</v>
@@ -1362,7 +1362,7 @@
         <v>150</v>
       </c>
       <c r="BM3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BN3">
         <v>4.2</v>
@@ -1380,7 +1380,7 @@
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT3">
         <v>11.5</v>
@@ -1389,7 +1389,7 @@
         <v>7.8</v>
       </c>
       <c r="BV3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW3">
         <v>7.6</v>
@@ -1404,7 +1404,7 @@
         <v>14.5</v>
       </c>
       <c r="CA3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,28 +1427,28 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G4">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>4.2</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>1.4</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
         <v>3.9</v>
@@ -1460,25 +1460,25 @@
         <v>1.98</v>
       </c>
       <c r="Q4">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R4">
         <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X4">
         <v>16.5</v>
@@ -1490,22 +1490,22 @@
         <v>55</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>26</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1514,37 +1514,37 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK4">
         <v>18.5</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM4">
         <v>160</v>
       </c>
       <c r="AN4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AP4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR4">
         <v>36</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -1559,37 +1559,37 @@
         <v>55</v>
       </c>
       <c r="AX4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC4">
         <v>15.5</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE4">
         <v>90</v>
       </c>
       <c r="BF4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI4">
         <v>2.8</v>
@@ -1598,49 +1598,49 @@
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL4">
         <v>180</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT4">
         <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV4">
         <v>65</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1962,7 +1962,7 @@
         <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2168,7 +2168,7 @@
         <v>5.7</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L7">
         <v>1.32</v>
@@ -2273,7 +2273,7 @@
         <v>7.6</v>
       </c>
       <c r="AT7">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
         <v>10.5</v>
@@ -2288,13 +2288,13 @@
         <v>6.2</v>
       </c>
       <c r="AY7">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BA7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BB7">
         <v>6.4</v>
@@ -2395,22 +2395,22 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G8">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2419,88 +2419,88 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q8">
         <v>2</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="U8">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="X8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z8">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AA8">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE8">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AF8">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
         <v>10</v>
       </c>
       <c r="AH8">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AK8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL8">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM8">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP8">
         <v>12</v>
@@ -2509,37 +2509,37 @@
         <v>16</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AS8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU8">
         <v>8</v>
       </c>
       <c r="AV8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW8">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AX8">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BA8">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BB8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC8">
         <v>16.5</v>
@@ -2548,13 +2548,13 @@
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2640,7 +2640,7 @@
         <v>2.68</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H9">
         <v>2.96</v>
@@ -2715,7 +2715,7 @@
         <v>42</v>
       </c>
       <c r="AF9">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2754,7 +2754,7 @@
         <v>16.5</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT9">
         <v>8.4</v>
@@ -2763,10 +2763,10 @@
         <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
         <v>15</v>
@@ -2778,25 +2778,25 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB9">
+        <v>7.4</v>
+      </c>
+      <c r="BC9">
+        <v>7</v>
+      </c>
+      <c r="BD9">
         <v>7.6</v>
       </c>
-      <c r="BC9">
+      <c r="BE9">
+        <v>7.6</v>
+      </c>
+      <c r="BF9">
         <v>7.2</v>
       </c>
-      <c r="BD9">
-        <v>8</v>
-      </c>
-      <c r="BE9">
-        <v>7.8</v>
-      </c>
-      <c r="BF9">
-        <v>7.4</v>
-      </c>
       <c r="BG9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH9">
         <v>3.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -349,7 +349,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 16:43:55</t>
+    <t>2026-09-30 18:55:38</t>
   </si>
 </sst>
 </file>
@@ -943,13 +943,13 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
         <v>2.16</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
         <v>3.75</v>
@@ -958,7 +958,7 @@
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -976,7 +976,7 @@
         <v>2.12</v>
       </c>
       <c r="Q2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R2">
         <v>1.44</v>
@@ -985,10 +985,10 @@
         <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V2">
         <v>1.36</v>
@@ -997,43 +997,43 @@
         <v>1.86</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB2">
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
         <v>18</v>
       </c>
       <c r="AI2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1048,10 +1048,10 @@
         <v>14</v>
       </c>
       <c r="AO2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
         <v>13.5</v>
@@ -1072,10 +1072,10 @@
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
         <v>9.800000000000001</v>
@@ -1087,13 +1087,13 @@
         <v>32</v>
       </c>
       <c r="BB2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE2">
         <v>60</v>
@@ -1102,43 +1102,43 @@
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH2">
         <v>4.1</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BL2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN2">
         <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
         <v>17</v>
       </c>
       <c r="BQ2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
         <v>8</v>
@@ -1150,13 +1150,13 @@
         <v>32</v>
       </c>
       <c r="BW2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1191,13 +1191,13 @@
         <v>1.51</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K3">
         <v>4.9</v>
@@ -1209,19 +1209,19 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S3">
         <v>2.84</v>
@@ -1230,7 +1230,7 @@
         <v>1.91</v>
       </c>
       <c r="U3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
         <v>1.13</v>
@@ -1242,7 +1242,7 @@
         <v>20</v>
       </c>
       <c r="Y3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z3">
         <v>85</v>
@@ -1251,7 +1251,7 @@
         <v>280</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>11</v>
@@ -1275,16 +1275,16 @@
         <v>110</v>
       </c>
       <c r="AJ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL3">
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN3">
         <v>6.6</v>
@@ -1293,7 +1293,7 @@
         <v>160</v>
       </c>
       <c r="AP3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
         <v>25</v>
@@ -1302,19 +1302,19 @@
         <v>55</v>
       </c>
       <c r="AS3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3">
         <v>25</v>
       </c>
       <c r="AW3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX3">
         <v>8.199999999999999</v>
@@ -1329,7 +1329,7 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC3">
         <v>13.5</v>
@@ -1344,7 +1344,7 @@
         <v>6</v>
       </c>
       <c r="BG3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH3">
         <v>4.7</v>
@@ -1427,16 +1427,16 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>4.2</v>
@@ -1445,64 +1445,64 @@
         <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4">
+        <v>1.94</v>
+      </c>
+      <c r="R4">
+        <v>1.38</v>
+      </c>
+      <c r="S4">
+        <v>3.4</v>
+      </c>
+      <c r="T4">
         <v>1.98</v>
-      </c>
-      <c r="Q4">
-        <v>1.96</v>
-      </c>
-      <c r="R4">
-        <v>1.37</v>
-      </c>
-      <c r="S4">
-        <v>3.45</v>
-      </c>
-      <c r="T4">
-        <v>2.02</v>
       </c>
       <c r="U4">
         <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA4">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AB4">
         <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF4">
         <v>9.199999999999999</v>
@@ -1511,49 +1511,49 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL4">
         <v>40</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO4">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AP4">
         <v>13.5</v>
       </c>
       <c r="AQ4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW4">
         <v>55</v>
@@ -1562,13 +1562,13 @@
         <v>8</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>13.5</v>
@@ -1577,22 +1577,22 @@
         <v>15.5</v>
       </c>
       <c r="BD4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE4">
         <v>90</v>
       </c>
       <c r="BF4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1604,7 +1604,7 @@
         <v>180</v>
       </c>
       <c r="BM4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1616,31 +1616,31 @@
         <v>12.5</v>
       </c>
       <c r="BQ4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT4">
         <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV4">
         <v>65</v>
       </c>
       <c r="BW4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1669,58 +1669,58 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="G5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H5">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
+        <v>1.2</v>
+      </c>
+      <c r="S5">
+        <v>3.45</v>
+      </c>
+      <c r="T5">
+        <v>2.22</v>
+      </c>
+      <c r="U5">
+        <v>1.63</v>
+      </c>
+      <c r="V5">
         <v>1.18</v>
       </c>
-      <c r="S5">
-        <v>3.4</v>
-      </c>
-      <c r="T5">
-        <v>2.16</v>
-      </c>
-      <c r="U5">
-        <v>1.11</v>
-      </c>
-      <c r="V5">
-        <v>1.16</v>
-      </c>
       <c r="W5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1735,10 +1735,10 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5">
         <v>1000</v>
@@ -1777,58 +1777,58 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1935,22 +1935,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P6">
         <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -1962,7 +1962,7 @@
         <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2019,52 +2019,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2153,7 +2153,7 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="G7">
         <v>16.5</v>
@@ -2171,34 +2171,34 @@
         <v>7.2</v>
       </c>
       <c r="L7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O7">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S7">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="T7">
         <v>2.28</v>
       </c>
       <c r="U7">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V7">
         <v>4.2</v>
@@ -2231,10 +2231,10 @@
         <v>16.5</v>
       </c>
       <c r="AF7">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AH7">
         <v>48</v>
@@ -2246,10 +2246,10 @@
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AL7">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AM7">
         <v>320</v>
@@ -2264,7 +2264,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR7">
         <v>6.2</v>
@@ -2273,7 +2273,7 @@
         <v>7.6</v>
       </c>
       <c r="AT7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
         <v>10.5</v>
@@ -2282,37 +2282,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX7">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="AY7">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC7">
         <v>6.4</v>
       </c>
       <c r="BD7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG7">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2395,22 +2395,22 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="G8">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H8">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2419,16 +2419,16 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
         <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R8">
         <v>1.35</v>
@@ -2440,46 +2440,46 @@
         <v>1.92</v>
       </c>
       <c r="U8">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W8">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z8">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA8">
         <v>180</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE8">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI8">
         <v>100</v>
@@ -2494,64 +2494,64 @@
         <v>40</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN8">
         <v>12.5</v>
       </c>
       <c r="AO8">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR8">
+        <v>10</v>
+      </c>
+      <c r="AS8">
         <v>11</v>
       </c>
-      <c r="AS8">
-        <v>12.5</v>
-      </c>
       <c r="AT8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8">
         <v>18.5</v>
       </c>
       <c r="AW8">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AX8">
         <v>8.800000000000001</v>
       </c>
       <c r="AY8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BA8">
         <v>65</v>
       </c>
       <c r="BB8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="BE8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8">
         <v>44</v>
@@ -2643,7 +2643,7 @@
         <v>2.78</v>
       </c>
       <c r="H9">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I9">
         <v>3.1</v>
@@ -2673,16 +2673,16 @@
         <v>2.24</v>
       </c>
       <c r="R9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
         <v>4.2</v>
       </c>
       <c r="T9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V9">
         <v>1.48</v>
@@ -2715,7 +2715,7 @@
         <v>42</v>
       </c>
       <c r="AF9">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2748,13 +2748,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9">
         <v>16.5</v>
       </c>
       <c r="AS9">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="AT9">
         <v>8.4</v>
@@ -2763,10 +2763,10 @@
         <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW9">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AX9">
         <v>15</v>
@@ -2778,19 +2778,19 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BB9">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC9">
         <v>7</v>
       </c>
       <c r="BD9">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BE9">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9">
         <v>7.2</v>
@@ -2802,7 +2802,7 @@
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -349,7 +349,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 18:55:38</t>
+    <t>2026-09-30 21:08:44</t>
   </si>
 </sst>
 </file>
@@ -943,25 +943,25 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="G2">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -970,193 +970,193 @@
         <v>4.2</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
         <v>17</v>
       </c>
-      <c r="Y2">
-        <v>16.5</v>
-      </c>
       <c r="Z2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL2">
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AO2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AP2">
         <v>15</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AS2">
-        <v>46</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
+        <v>9.4</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>15</v>
+      </c>
+      <c r="AW2">
+        <v>42</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
         <v>9.6</v>
-      </c>
-      <c r="AU2">
-        <v>7.6</v>
-      </c>
-      <c r="AV2">
-        <v>13.5</v>
-      </c>
-      <c r="AW2">
-        <v>29</v>
-      </c>
-      <c r="AX2">
-        <v>12.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
+        <v>29</v>
+      </c>
+      <c r="BE2">
+        <v>7.2</v>
+      </c>
+      <c r="BF2">
+        <v>11</v>
+      </c>
+      <c r="BG2">
+        <v>40</v>
+      </c>
+      <c r="BH2">
+        <v>3.9</v>
+      </c>
+      <c r="BI2">
+        <v>3.3</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
+        <v>7.2</v>
+      </c>
+      <c r="BL2">
+        <v>120</v>
+      </c>
+      <c r="BM2">
+        <v>6.6</v>
+      </c>
+      <c r="BN2">
+        <v>5.3</v>
+      </c>
+      <c r="BO2">
+        <v>4</v>
+      </c>
+      <c r="BP2">
+        <v>15</v>
+      </c>
+      <c r="BQ2">
+        <v>10.5</v>
+      </c>
+      <c r="BR2">
+        <v>29</v>
+      </c>
+      <c r="BS2">
         <v>18.5</v>
       </c>
-      <c r="BD2">
-        <v>27</v>
-      </c>
-      <c r="BE2">
-        <v>60</v>
-      </c>
-      <c r="BF2">
-        <v>12</v>
-      </c>
-      <c r="BG2">
-        <v>24</v>
-      </c>
-      <c r="BH2">
-        <v>4.1</v>
-      </c>
-      <c r="BI2">
-        <v>3.35</v>
-      </c>
-      <c r="BJ2">
-        <v>10.5</v>
-      </c>
-      <c r="BK2">
-        <v>3.95</v>
-      </c>
-      <c r="BL2">
-        <v>110</v>
-      </c>
-      <c r="BM2">
-        <v>5.8</v>
-      </c>
-      <c r="BN2">
-        <v>5.7</v>
-      </c>
-      <c r="BO2">
-        <v>4.6</v>
-      </c>
-      <c r="BP2">
-        <v>17</v>
-      </c>
-      <c r="BQ2">
-        <v>4.5</v>
-      </c>
-      <c r="BR2">
+      <c r="BT2">
+        <v>9</v>
+      </c>
+      <c r="BU2">
+        <v>6.8</v>
+      </c>
+      <c r="BV2">
+        <v>40</v>
+      </c>
+      <c r="BW2">
+        <v>25</v>
+      </c>
+      <c r="BX2">
+        <v>48</v>
+      </c>
+      <c r="BY2">
         <v>30</v>
-      </c>
-      <c r="BS2">
-        <v>5.1</v>
-      </c>
-      <c r="BT2">
-        <v>8</v>
-      </c>
-      <c r="BU2">
-        <v>5.6</v>
-      </c>
-      <c r="BV2">
-        <v>32</v>
-      </c>
-      <c r="BW2">
-        <v>5.1</v>
-      </c>
-      <c r="BX2">
-        <v>40</v>
-      </c>
-      <c r="BY2">
-        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G3">
         <v>1.51</v>
@@ -1194,13 +1194,13 @@
         <v>7.6</v>
       </c>
       <c r="I3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>1.33</v>
@@ -1209,31 +1209,31 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S3">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
         <v>2.96</v>
@@ -1248,19 +1248,19 @@
         <v>85</v>
       </c>
       <c r="AA3">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC3">
         <v>11</v>
       </c>
       <c r="AD3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF3">
         <v>9</v>
@@ -1269,52 +1269,52 @@
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK3">
         <v>15</v>
       </c>
       <c r="AL3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM3">
         <v>190</v>
       </c>
       <c r="AN3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR3">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="AX3">
         <v>8.199999999999999</v>
@@ -1326,43 +1326,43 @@
         <v>20</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="BB3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC3">
         <v>13.5</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BF3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BL3">
         <v>150</v>
       </c>
       <c r="BM3">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="BN3">
         <v>4.2</v>
@@ -1371,10 +1371,10 @@
         <v>3.55</v>
       </c>
       <c r="BP3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BR3">
         <v>24</v>
@@ -1386,19 +1386,19 @@
         <v>11.5</v>
       </c>
       <c r="BU3">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BV3">
         <v>70</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3">
         <v>14.5</v>
@@ -1430,10 +1430,10 @@
         <v>1.59</v>
       </c>
       <c r="G4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>7.2</v>
@@ -1445,13 +1445,13 @@
         <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>1.31</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
         <v>1.38</v>
@@ -1469,16 +1469,16 @@
         <v>3.4</v>
       </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X4">
         <v>15.5</v>
@@ -1487,10 +1487,10 @@
         <v>23</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA4">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB4">
         <v>8.199999999999999</v>
@@ -1499,13 +1499,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1517,7 +1517,7 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK4">
         <v>18</v>
@@ -1529,7 +1529,7 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO4">
         <v>140</v>
@@ -1541,7 +1541,7 @@
         <v>19</v>
       </c>
       <c r="AR4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS4">
         <v>120</v>
@@ -1553,7 +1553,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW4">
         <v>55</v>
@@ -1568,10 +1568,10 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC4">
         <v>15.5</v>
@@ -1580,31 +1580,31 @@
         <v>32</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK4">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
         <v>180</v>
       </c>
       <c r="BM4">
-        <v>4.9</v>
+        <v>130</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1616,7 +1616,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ4">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>32</v>
@@ -1628,16 +1628,16 @@
         <v>11.5</v>
       </c>
       <c r="BU4">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BW4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX4">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BY4">
         <v>4.7</v>
@@ -1669,22 +1669,22 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="G5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K5">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1693,34 +1693,34 @@
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="O5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P5">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S5">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="T5">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1738,7 +1738,7 @@
         <v>970</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
         <v>1000</v>
@@ -1777,10 +1777,10 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AQ5">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>1.14</v>
@@ -1789,22 +1789,22 @@
         <v>1.14</v>
       </c>
       <c r="AT5">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
         <v>1.14</v>
       </c>
       <c r="AV5">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AW5">
         <v>1.14</v>
       </c>
       <c r="AX5">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AY5">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AZ5">
         <v>1.14</v>
@@ -1813,19 +1813,19 @@
         <v>1.14</v>
       </c>
       <c r="BB5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BC5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BD5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BE5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BF5">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BG5">
         <v>1.14</v>
@@ -1911,7 +1911,7 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G6">
         <v>990</v>
@@ -1935,10 +1935,10 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P6">
         <v>1.25</v>
@@ -1950,7 +1950,7 @@
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -1962,7 +1962,7 @@
         <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2153,166 +2153,166 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="G7">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="H7">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I7">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="J7">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="K7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="L7">
         <v>1.34</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Q7">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="S7">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U7">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V7">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>7.4</v>
+      </c>
+      <c r="AA7">
         <v>9</v>
-      </c>
-      <c r="Z7">
-        <v>7.8</v>
-      </c>
-      <c r="AA7">
-        <v>9.6</v>
       </c>
       <c r="AB7">
         <v>55</v>
       </c>
       <c r="AC7">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF7">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG7">
         <v>70</v>
       </c>
       <c r="AH7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI7">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
       </c>
       <c r="AK7">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AL7">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AM7">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AN7">
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AP7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7">
+        <v>6</v>
+      </c>
+      <c r="AS7">
+        <v>7.2</v>
+      </c>
+      <c r="AT7">
         <v>6.2</v>
       </c>
-      <c r="AS7">
-        <v>7.6</v>
-      </c>
-      <c r="AT7">
-        <v>12.5</v>
-      </c>
       <c r="AU7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW7">
         <v>4.7</v>
       </c>
       <c r="AX7">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="AY7">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA7">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG7">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2395,25 +2395,25 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G8">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I8">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>3.95</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2422,52 +2422,52 @@
         <v>3.7</v>
       </c>
       <c r="O8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T8">
+        <v>1.98</v>
+      </c>
+      <c r="U8">
         <v>1.92</v>
       </c>
-      <c r="U8">
-        <v>1.96</v>
-      </c>
       <c r="V8">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="X8">
         <v>15</v>
       </c>
       <c r="Y8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA8">
         <v>180</v>
       </c>
       <c r="AB8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE8">
         <v>95</v>
@@ -2476,25 +2476,25 @@
         <v>10</v>
       </c>
       <c r="AG8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK8">
         <v>19</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN8">
         <v>12.5</v>
@@ -2509,7 +2509,7 @@
         <v>17</v>
       </c>
       <c r="AR8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS8">
         <v>11</v>
@@ -2518,13 +2518,13 @@
         <v>7.4</v>
       </c>
       <c r="AU8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW8">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AX8">
         <v>8.800000000000001</v>
@@ -2533,25 +2533,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA8">
         <v>65</v>
       </c>
       <c r="BB8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD8">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG8">
         <v>44</v>
@@ -2637,19 +2637,19 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G9">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H9">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="I9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
         <v>3.4</v>
@@ -2667,151 +2667,151 @@
         <v>1.42</v>
       </c>
       <c r="P9">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q9">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T9">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U9">
         <v>1.98</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X9">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Z9">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AA9">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB9">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AE9">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AF9">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AH9">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI9">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ9">
         <v>110</v>
       </c>
       <c r="AK9">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AL9">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM9">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ9">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AR9">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS9">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU9">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV9">
-        <v>12</v>
+        <v>1.74</v>
       </c>
       <c r="AW9">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AX9">
-        <v>15</v>
+        <v>1.77</v>
       </c>
       <c r="AY9">
+        <v>1.73</v>
+      </c>
+      <c r="AZ9">
+        <v>1.79</v>
+      </c>
+      <c r="BA9">
         <v>11</v>
       </c>
-      <c r="AZ9">
-        <v>16.5</v>
-      </c>
-      <c r="BA9">
-        <v>23</v>
-      </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC9">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BE9">
-        <v>8.199999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="BG9">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="BH9">
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM9">
         <v>5.8</v>
@@ -2820,7 +2820,7 @@
         <v>6.4</v>
       </c>
       <c r="BO9">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BP9">
         <v>27</v>
@@ -2838,7 +2838,7 @@
         <v>6.6</v>
       </c>
       <c r="BU9">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV9">
         <v>28</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>US United Soccer League</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -280,9 +280,6 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>01:00:00</t>
   </si>
   <si>
@@ -301,9 +298,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks FC</t>
-  </si>
-  <si>
     <t>Atletico Nacional Medell</t>
   </si>
   <si>
@@ -325,9 +319,6 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
     <t>Junior FC Barranquilla</t>
   </si>
   <si>
@@ -349,7 +340,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 21:08:44</t>
+    <t>2026-09-30 23:19:46</t>
   </si>
 </sst>
 </file>
@@ -681,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -937,226 +928,226 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F2">
-        <v>1.92</v>
+        <v>1.23</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>3.75</v>
+      </c>
+      <c r="S2">
+        <v>1.35</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1.03</v>
+      </c>
+      <c r="W2">
+        <v>5.1</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>3.8</v>
+      </c>
+      <c r="AH2">
+        <v>8.4</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>4.5</v>
+      </c>
+      <c r="AL2">
+        <v>10</v>
+      </c>
+      <c r="AM2">
+        <v>48</v>
+      </c>
+      <c r="AN2">
+        <v>5.6</v>
+      </c>
+      <c r="AO2">
+        <v>150</v>
+      </c>
+      <c r="AP2">
+        <v>11</v>
+      </c>
+      <c r="AQ2">
+        <v>11</v>
+      </c>
+      <c r="AR2">
+        <v>11</v>
+      </c>
+      <c r="AS2">
+        <v>11</v>
+      </c>
+      <c r="AT2">
+        <v>11</v>
+      </c>
+      <c r="AU2">
+        <v>11</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>11</v>
+      </c>
+      <c r="AX2">
+        <v>11</v>
+      </c>
+      <c r="AY2">
+        <v>3.65</v>
+      </c>
+      <c r="AZ2">
+        <v>7.4</v>
+      </c>
+      <c r="BA2">
+        <v>30</v>
+      </c>
+      <c r="BB2">
+        <v>11</v>
+      </c>
+      <c r="BC2">
         <v>4.1</v>
       </c>
-      <c r="L2">
-        <v>1.39</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4.2</v>
-      </c>
-      <c r="O2">
-        <v>1.27</v>
-      </c>
-      <c r="P2">
-        <v>2.16</v>
-      </c>
-      <c r="Q2">
-        <v>1.78</v>
-      </c>
-      <c r="R2">
-        <v>1.43</v>
-      </c>
-      <c r="S2">
-        <v>2.92</v>
-      </c>
-      <c r="T2">
-        <v>1.74</v>
-      </c>
-      <c r="U2">
-        <v>2.18</v>
-      </c>
-      <c r="V2">
-        <v>1.27</v>
-      </c>
-      <c r="W2">
-        <v>2.02</v>
-      </c>
-      <c r="X2">
-        <v>18</v>
-      </c>
-      <c r="Y2">
-        <v>17</v>
-      </c>
-      <c r="Z2">
-        <v>34</v>
-      </c>
-      <c r="AA2">
-        <v>100</v>
-      </c>
-      <c r="AB2">
-        <v>10.5</v>
-      </c>
-      <c r="AC2">
+      <c r="BD2">
         <v>9</v>
       </c>
-      <c r="AD2">
-        <v>17</v>
-      </c>
-      <c r="AE2">
-        <v>55</v>
-      </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>18.5</v>
-      </c>
-      <c r="AI2">
-        <v>60</v>
-      </c>
-      <c r="AJ2">
-        <v>24</v>
-      </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
-        <v>34</v>
-      </c>
-      <c r="AM2">
-        <v>100</v>
-      </c>
-      <c r="AN2">
-        <v>23</v>
-      </c>
-      <c r="AO2">
-        <v>48</v>
-      </c>
-      <c r="AP2">
-        <v>15</v>
-      </c>
-      <c r="AQ2">
-        <v>14.5</v>
-      </c>
-      <c r="AR2">
-        <v>27</v>
-      </c>
-      <c r="AS2">
-        <v>7.2</v>
-      </c>
-      <c r="AT2">
-        <v>9.4</v>
-      </c>
-      <c r="AU2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>15</v>
-      </c>
-      <c r="AW2">
-        <v>42</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
-        <v>20</v>
-      </c>
-      <c r="BC2">
-        <v>17.5</v>
-      </c>
-      <c r="BD2">
-        <v>29</v>
-      </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="BG2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="BH2">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1165,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1179,22 +1170,22 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G3">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>4.8</v>
@@ -1203,216 +1194,216 @@
         <v>5</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
+        <v>3.9</v>
+      </c>
+      <c r="O3">
+        <v>1.32</v>
+      </c>
+      <c r="P3">
+        <v>2.02</v>
+      </c>
+      <c r="Q3">
+        <v>1.92</v>
+      </c>
+      <c r="R3">
+        <v>1.37</v>
+      </c>
+      <c r="S3">
+        <v>3.4</v>
+      </c>
+      <c r="T3">
+        <v>2.04</v>
+      </c>
+      <c r="U3">
+        <v>1.78</v>
+      </c>
+      <c r="V3">
+        <v>1.13</v>
+      </c>
+      <c r="W3">
+        <v>2.8</v>
+      </c>
+      <c r="X3">
+        <v>18</v>
+      </c>
+      <c r="Y3">
+        <v>26</v>
+      </c>
+      <c r="Z3">
+        <v>70</v>
+      </c>
+      <c r="AA3">
+        <v>270</v>
+      </c>
+      <c r="AB3">
+        <v>9</v>
+      </c>
+      <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>34</v>
+      </c>
+      <c r="AE3">
+        <v>140</v>
+      </c>
+      <c r="AF3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>36</v>
+      </c>
+      <c r="AI3">
+        <v>140</v>
+      </c>
+      <c r="AJ3">
+        <v>17</v>
+      </c>
+      <c r="AK3">
+        <v>22</v>
+      </c>
+      <c r="AL3">
+        <v>42</v>
+      </c>
+      <c r="AM3">
+        <v>200</v>
+      </c>
+      <c r="AN3">
+        <v>12</v>
+      </c>
+      <c r="AO3">
+        <v>240</v>
+      </c>
+      <c r="AP3">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3">
+        <v>4.7</v>
+      </c>
+      <c r="AR3">
+        <v>5.8</v>
+      </c>
+      <c r="AS3">
         <v>5.1</v>
       </c>
-      <c r="O3">
-        <v>1.23</v>
-      </c>
-      <c r="P3">
-        <v>2.36</v>
-      </c>
-      <c r="Q3">
-        <v>1.7</v>
-      </c>
-      <c r="R3">
-        <v>1.54</v>
-      </c>
-      <c r="S3">
-        <v>2.78</v>
-      </c>
-      <c r="T3">
-        <v>1.88</v>
-      </c>
-      <c r="U3">
-        <v>2.08</v>
-      </c>
-      <c r="V3">
-        <v>1.14</v>
-      </c>
-      <c r="W3">
-        <v>2.96</v>
-      </c>
-      <c r="X3">
-        <v>20</v>
-      </c>
-      <c r="Y3">
-        <v>30</v>
-      </c>
-      <c r="Z3">
-        <v>85</v>
-      </c>
-      <c r="AA3">
-        <v>240</v>
-      </c>
-      <c r="AB3">
-        <v>10</v>
-      </c>
-      <c r="AC3">
-        <v>11</v>
-      </c>
-      <c r="AD3">
+      <c r="AT3">
+        <v>6.2</v>
+      </c>
+      <c r="AU3">
+        <v>8.6</v>
+      </c>
+      <c r="AV3">
+        <v>4.9</v>
+      </c>
+      <c r="AW3">
+        <v>5.1</v>
+      </c>
+      <c r="AX3">
+        <v>6.4</v>
+      </c>
+      <c r="AY3">
+        <v>3.95</v>
+      </c>
+      <c r="AZ3">
+        <v>4.7</v>
+      </c>
+      <c r="BA3">
+        <v>5.1</v>
+      </c>
+      <c r="BB3">
+        <v>4.3</v>
+      </c>
+      <c r="BC3">
+        <v>4.4</v>
+      </c>
+      <c r="BD3">
+        <v>4.7</v>
+      </c>
+      <c r="BE3">
+        <v>5.1</v>
+      </c>
+      <c r="BF3">
+        <v>3.95</v>
+      </c>
+      <c r="BG3">
+        <v>5.2</v>
+      </c>
+      <c r="BH3">
+        <v>3.25</v>
+      </c>
+      <c r="BI3">
+        <v>2.84</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>10.5</v>
+      </c>
+      <c r="BL3">
+        <v>960</v>
+      </c>
+      <c r="BM3">
+        <v>7.8</v>
+      </c>
+      <c r="BN3">
+        <v>3.9</v>
+      </c>
+      <c r="BO3">
+        <v>3.45</v>
+      </c>
+      <c r="BP3">
+        <v>12.5</v>
+      </c>
+      <c r="BQ3">
+        <v>8.6</v>
+      </c>
+      <c r="BR3">
+        <v>36</v>
+      </c>
+      <c r="BS3">
         <v>28</v>
       </c>
-      <c r="AE3">
-        <v>110</v>
-      </c>
-      <c r="AF3">
-        <v>9</v>
-      </c>
-      <c r="AG3">
-        <v>10.5</v>
-      </c>
-      <c r="AH3">
-        <v>23</v>
-      </c>
-      <c r="AI3">
+      <c r="BT3">
+        <v>13</v>
+      </c>
+      <c r="BU3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BV3">
         <v>95</v>
       </c>
-      <c r="AJ3">
-        <v>13.5</v>
-      </c>
-      <c r="AK3">
-        <v>15</v>
-      </c>
-      <c r="AL3">
-        <v>34</v>
-      </c>
-      <c r="AM3">
-        <v>190</v>
-      </c>
-      <c r="AN3">
-        <v>6.4</v>
-      </c>
-      <c r="AO3">
-        <v>170</v>
-      </c>
-      <c r="AP3">
-        <v>19</v>
-      </c>
-      <c r="AQ3">
-        <v>27</v>
-      </c>
-      <c r="AR3">
-        <v>30</v>
-      </c>
-      <c r="AS3">
-        <v>16</v>
-      </c>
-      <c r="AT3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3">
-        <v>10</v>
-      </c>
-      <c r="AV3">
-        <v>24</v>
-      </c>
-      <c r="AW3">
-        <v>16</v>
-      </c>
-      <c r="AX3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3">
-        <v>20</v>
-      </c>
-      <c r="BA3">
-        <v>16</v>
-      </c>
-      <c r="BB3">
-        <v>12</v>
-      </c>
-      <c r="BC3">
-        <v>13.5</v>
-      </c>
-      <c r="BD3">
-        <v>29</v>
-      </c>
-      <c r="BE3">
-        <v>85</v>
-      </c>
-      <c r="BF3">
-        <v>5.8</v>
-      </c>
-      <c r="BG3">
-        <v>75</v>
-      </c>
-      <c r="BH3">
-        <v>4.8</v>
-      </c>
-      <c r="BI3">
-        <v>3.6</v>
-      </c>
-      <c r="BJ3">
-        <v>11</v>
-      </c>
-      <c r="BK3">
-        <v>4.7</v>
-      </c>
-      <c r="BL3">
-        <v>150</v>
-      </c>
-      <c r="BM3">
-        <v>110</v>
-      </c>
-      <c r="BN3">
-        <v>4.2</v>
-      </c>
-      <c r="BO3">
-        <v>3.55</v>
-      </c>
-      <c r="BP3">
-        <v>9</v>
-      </c>
-      <c r="BQ3">
-        <v>4.3</v>
-      </c>
-      <c r="BR3">
-        <v>24</v>
-      </c>
-      <c r="BS3">
-        <v>6.2</v>
-      </c>
-      <c r="BT3">
-        <v>11.5</v>
-      </c>
-      <c r="BU3">
-        <v>9.6</v>
-      </c>
-      <c r="BV3">
+      <c r="BW3">
+        <v>7.6</v>
+      </c>
+      <c r="BX3">
+        <v>870</v>
+      </c>
+      <c r="BY3">
         <v>70</v>
       </c>
-      <c r="BW3">
-        <v>7.4</v>
-      </c>
-      <c r="BX3">
-        <v>65</v>
-      </c>
-      <c r="BY3">
-        <v>7.4</v>
-      </c>
       <c r="BZ3">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
         <v>87</v>
@@ -1421,306 +1412,306 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F4">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="G4">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
         <v>6.6</v>
       </c>
-      <c r="I4">
-        <v>7.2</v>
-      </c>
       <c r="J4">
+        <v>3.6</v>
+      </c>
+      <c r="K4">
+        <v>3.85</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.1</v>
+      </c>
+      <c r="N4">
+        <v>2.9</v>
+      </c>
+      <c r="O4">
+        <v>1.47</v>
+      </c>
+      <c r="P4">
+        <v>1.64</v>
+      </c>
+      <c r="Q4">
+        <v>2.38</v>
+      </c>
+      <c r="R4">
+        <v>1.24</v>
+      </c>
+      <c r="S4">
         <v>4.2</v>
       </c>
-      <c r="K4">
-        <v>4.5</v>
-      </c>
-      <c r="L4">
-        <v>1.39</v>
-      </c>
-      <c r="M4">
-        <v>1.06</v>
-      </c>
-      <c r="N4">
-        <v>4</v>
-      </c>
-      <c r="O4">
-        <v>1.31</v>
-      </c>
-      <c r="P4">
-        <v>2</v>
-      </c>
-      <c r="Q4">
-        <v>1.92</v>
-      </c>
-      <c r="R4">
-        <v>1.38</v>
-      </c>
-      <c r="S4">
-        <v>3.4</v>
-      </c>
       <c r="T4">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="X4">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z4">
+        <v>65</v>
+      </c>
+      <c r="AA4">
+        <v>280</v>
+      </c>
+      <c r="AB4">
+        <v>6.6</v>
+      </c>
+      <c r="AC4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>34</v>
+      </c>
+      <c r="AE4">
+        <v>160</v>
+      </c>
+      <c r="AF4">
+        <v>9.4</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
+        <v>34</v>
+      </c>
+      <c r="AI4">
+        <v>140</v>
+      </c>
+      <c r="AJ4">
+        <v>22</v>
+      </c>
+      <c r="AK4">
+        <v>27</v>
+      </c>
+      <c r="AL4">
         <v>60</v>
       </c>
-      <c r="AA4">
-        <v>260</v>
-      </c>
-      <c r="AB4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD4">
-        <v>28</v>
-      </c>
-      <c r="AE4">
-        <v>120</v>
-      </c>
-      <c r="AF4">
+      <c r="AM4">
+        <v>220</v>
+      </c>
+      <c r="AN4">
+        <v>17.5</v>
+      </c>
+      <c r="AO4">
+        <v>240</v>
+      </c>
+      <c r="AP4">
         <v>9</v>
       </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>25</v>
-      </c>
-      <c r="AI4">
-        <v>110</v>
-      </c>
-      <c r="AJ4">
-        <v>15</v>
-      </c>
-      <c r="AK4">
-        <v>18</v>
-      </c>
-      <c r="AL4">
-        <v>40</v>
-      </c>
-      <c r="AM4">
-        <v>150</v>
-      </c>
-      <c r="AN4">
-        <v>9</v>
-      </c>
-      <c r="AO4">
-        <v>140</v>
-      </c>
-      <c r="AP4">
-        <v>13.5</v>
-      </c>
       <c r="AQ4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>48</v>
+        <v>5.3</v>
       </c>
       <c r="AS4">
-        <v>120</v>
+        <v>5.7</v>
       </c>
       <c r="AT4">
+        <v>5.7</v>
+      </c>
+      <c r="AU4">
         <v>7.4</v>
       </c>
-      <c r="AU4">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AV4">
-        <v>23</v>
+        <v>4.9</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>5.6</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY4">
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD4">
-        <v>32</v>
+        <v>5.3</v>
       </c>
       <c r="BE4">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="BF4">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>75</v>
+        <v>5.7</v>
       </c>
       <c r="BH4">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>130</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F5">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="G5">
-        <v>1.77</v>
+        <v>990</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>8.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
         <v>1.05</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1735,7 +1726,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
         <v>1000</v>
@@ -1777,58 +1768,58 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
         <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1891,12 +1882,12 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
         <v>87</v>
@@ -1905,172 +1896,172 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>1.13</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>1.29</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
+        <v>1.2</v>
+      </c>
+      <c r="P6">
+        <v>2.38</v>
+      </c>
+      <c r="Q6">
+        <v>1.58</v>
+      </c>
+      <c r="R6">
         <v>1.54</v>
       </c>
-      <c r="P6">
-        <v>1.25</v>
-      </c>
-      <c r="Q6">
-        <v>1.56</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>2.54</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="W6">
         <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN6">
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2133,12 +2124,12 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
@@ -2147,240 +2138,240 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <v>1.67</v>
+      </c>
+      <c r="G7">
+        <v>1.75</v>
+      </c>
+      <c r="H7">
+        <v>5.5</v>
+      </c>
+      <c r="I7">
+        <v>6.2</v>
+      </c>
+      <c r="J7">
+        <v>3.95</v>
+      </c>
+      <c r="K7">
+        <v>4.3</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
+        <v>3.7</v>
+      </c>
+      <c r="O7">
+        <v>1.32</v>
+      </c>
+      <c r="P7">
+        <v>1.92</v>
+      </c>
+      <c r="Q7">
+        <v>1.92</v>
+      </c>
+      <c r="R7">
+        <v>1.34</v>
+      </c>
+      <c r="S7">
+        <v>3.65</v>
+      </c>
+      <c r="T7">
+        <v>1.98</v>
+      </c>
+      <c r="U7">
+        <v>1.92</v>
+      </c>
+      <c r="V7">
+        <v>1.2</v>
+      </c>
+      <c r="W7">
+        <v>2.32</v>
+      </c>
+      <c r="X7">
+        <v>15</v>
+      </c>
+      <c r="Y7">
+        <v>19</v>
+      </c>
+      <c r="Z7">
+        <v>80</v>
+      </c>
+      <c r="AA7">
+        <v>180</v>
+      </c>
+      <c r="AB7">
+        <v>8.4</v>
+      </c>
+      <c r="AC7">
+        <v>11</v>
+      </c>
+      <c r="AD7">
+        <v>24</v>
+      </c>
+      <c r="AE7">
+        <v>95</v>
+      </c>
+      <c r="AF7">
+        <v>10</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>24</v>
+      </c>
+      <c r="AI7">
+        <v>110</v>
+      </c>
+      <c r="AJ7">
+        <v>18</v>
+      </c>
+      <c r="AK7">
+        <v>19</v>
+      </c>
+      <c r="AL7">
+        <v>44</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>12.5</v>
+      </c>
+      <c r="AO7">
+        <v>120</v>
+      </c>
+      <c r="AP7">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7">
+        <v>17</v>
+      </c>
+      <c r="AR7">
+        <v>38</v>
+      </c>
+      <c r="AS7">
+        <v>11</v>
+      </c>
+      <c r="AT7">
+        <v>7.4</v>
+      </c>
+      <c r="AU7">
+        <v>8.4</v>
+      </c>
+      <c r="AV7">
+        <v>19.5</v>
+      </c>
+      <c r="AW7">
+        <v>55</v>
+      </c>
+      <c r="AX7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>65</v>
+      </c>
+      <c r="BB7">
+        <v>16</v>
+      </c>
+      <c r="BC7">
+        <v>15.5</v>
+      </c>
+      <c r="BD7">
+        <v>32</v>
+      </c>
+      <c r="BE7">
+        <v>11.5</v>
+      </c>
+      <c r="BF7">
+        <v>9.6</v>
+      </c>
+      <c r="BG7">
+        <v>44</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.04</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.04</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.04</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.04</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.04</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.04</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.04</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="s">
         <v>108</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>19.5</v>
-      </c>
-      <c r="H7">
-        <v>1.22</v>
-      </c>
-      <c r="I7">
-        <v>1.27</v>
-      </c>
-      <c r="J7">
-        <v>6.2</v>
-      </c>
-      <c r="K7">
-        <v>7.8</v>
-      </c>
-      <c r="L7">
-        <v>1.34</v>
-      </c>
-      <c r="M7">
-        <v>1.04</v>
-      </c>
-      <c r="N7">
-        <v>5.2</v>
-      </c>
-      <c r="O7">
-        <v>1.19</v>
-      </c>
-      <c r="P7">
-        <v>2.38</v>
-      </c>
-      <c r="Q7">
-        <v>1.58</v>
-      </c>
-      <c r="R7">
-        <v>1.55</v>
-      </c>
-      <c r="S7">
-        <v>2.54</v>
-      </c>
-      <c r="T7">
-        <v>2.3</v>
-      </c>
-      <c r="U7">
-        <v>1.6</v>
-      </c>
-      <c r="V7">
-        <v>4.6</v>
-      </c>
-      <c r="W7">
-        <v>1.05</v>
-      </c>
-      <c r="X7">
-        <v>27</v>
-      </c>
-      <c r="Y7">
-        <v>11</v>
-      </c>
-      <c r="Z7">
-        <v>7.4</v>
-      </c>
-      <c r="AA7">
-        <v>9</v>
-      </c>
-      <c r="AB7">
-        <v>55</v>
-      </c>
-      <c r="AC7">
-        <v>18</v>
-      </c>
-      <c r="AD7">
-        <v>13.5</v>
-      </c>
-      <c r="AE7">
-        <v>14.5</v>
-      </c>
-      <c r="AF7">
-        <v>200</v>
-      </c>
-      <c r="AG7">
-        <v>70</v>
-      </c>
-      <c r="AH7">
-        <v>46</v>
-      </c>
-      <c r="AI7">
-        <v>180</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>380</v>
-      </c>
-      <c r="AL7">
-        <v>270</v>
-      </c>
-      <c r="AM7">
-        <v>290</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>5</v>
-      </c>
-      <c r="AP7">
-        <v>18</v>
-      </c>
-      <c r="AQ7">
-        <v>7.6</v>
-      </c>
-      <c r="AR7">
-        <v>6</v>
-      </c>
-      <c r="AS7">
-        <v>7.2</v>
-      </c>
-      <c r="AT7">
-        <v>6.2</v>
-      </c>
-      <c r="AU7">
-        <v>12</v>
-      </c>
-      <c r="AV7">
-        <v>10</v>
-      </c>
-      <c r="AW7">
-        <v>4.7</v>
-      </c>
-      <c r="AX7">
-        <v>6.8</v>
-      </c>
-      <c r="AY7">
-        <v>6.4</v>
-      </c>
-      <c r="AZ7">
-        <v>6</v>
-      </c>
-      <c r="BA7">
-        <v>6.2</v>
-      </c>
-      <c r="BB7">
-        <v>7</v>
-      </c>
-      <c r="BC7">
-        <v>6.8</v>
-      </c>
-      <c r="BD7">
-        <v>6.8</v>
-      </c>
-      <c r="BE7">
-        <v>6.8</v>
-      </c>
-      <c r="BF7">
-        <v>7</v>
-      </c>
-      <c r="BG7">
-        <v>3.3</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.04</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.04</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>1.04</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>1.04</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>1.04</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>1.04</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
@@ -2389,477 +2380,235 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F8">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="G8">
-        <v>1.72</v>
+        <v>2.82</v>
       </c>
       <c r="H8">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>2.96</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
+        <v>3.4</v>
+      </c>
+      <c r="L8">
+        <v>1.47</v>
+      </c>
+      <c r="M8">
+        <v>1.09</v>
+      </c>
+      <c r="N8">
+        <v>3.25</v>
+      </c>
+      <c r="O8">
+        <v>1.42</v>
+      </c>
+      <c r="P8">
+        <v>1.73</v>
+      </c>
+      <c r="Q8">
+        <v>2.26</v>
+      </c>
+      <c r="R8">
+        <v>1.28</v>
+      </c>
+      <c r="S8">
         <v>4.3</v>
       </c>
-      <c r="L8">
-        <v>1.4</v>
-      </c>
-      <c r="M8">
-        <v>1.07</v>
-      </c>
-      <c r="N8">
-        <v>3.7</v>
-      </c>
-      <c r="O8">
-        <v>1.33</v>
-      </c>
-      <c r="P8">
-        <v>1.92</v>
-      </c>
-      <c r="Q8">
-        <v>1.92</v>
-      </c>
-      <c r="R8">
-        <v>1.34</v>
-      </c>
-      <c r="S8">
-        <v>3.65</v>
-      </c>
       <c r="T8">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="U8">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="X8">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
+        <v>10.5</v>
+      </c>
+      <c r="Z8">
         <v>19</v>
       </c>
-      <c r="Z8">
-        <v>48</v>
-      </c>
       <c r="AA8">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE8">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AJ8">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AK8">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AM8">
         <v>140</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AO8">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AP8">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AR8">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AS8">
+        <v>20</v>
+      </c>
+      <c r="AT8">
+        <v>8.6</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>11.5</v>
+      </c>
+      <c r="AW8">
+        <v>15.5</v>
+      </c>
+      <c r="AX8">
+        <v>15</v>
+      </c>
+      <c r="AY8">
         <v>11</v>
       </c>
-      <c r="AT8">
+      <c r="AZ8">
+        <v>16.5</v>
+      </c>
+      <c r="BA8">
+        <v>21</v>
+      </c>
+      <c r="BB8">
+        <v>19</v>
+      </c>
+      <c r="BC8">
+        <v>14.5</v>
+      </c>
+      <c r="BD8">
+        <v>20</v>
+      </c>
+      <c r="BE8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF8">
+        <v>7.2</v>
+      </c>
+      <c r="BG8">
         <v>7.4</v>
       </c>
-      <c r="AU8">
-        <v>8.4</v>
-      </c>
-      <c r="AV8">
-        <v>19.5</v>
-      </c>
-      <c r="AW8">
-        <v>55</v>
-      </c>
-      <c r="AX8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8">
-        <v>19.5</v>
-      </c>
-      <c r="BA8">
-        <v>65</v>
-      </c>
-      <c r="BB8">
-        <v>15.5</v>
-      </c>
-      <c r="BC8">
-        <v>15.5</v>
-      </c>
-      <c r="BD8">
-        <v>32</v>
-      </c>
-      <c r="BE8">
-        <v>11</v>
-      </c>
-      <c r="BF8">
-        <v>9.6</v>
-      </c>
-      <c r="BG8">
-        <v>44</v>
-      </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9">
-        <v>2.72</v>
-      </c>
-      <c r="G9">
-        <v>2.82</v>
-      </c>
-      <c r="H9">
-        <v>2.88</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>3.25</v>
-      </c>
-      <c r="K9">
-        <v>3.4</v>
-      </c>
-      <c r="L9">
-        <v>1.47</v>
-      </c>
-      <c r="M9">
-        <v>1.09</v>
-      </c>
-      <c r="N9">
-        <v>3.2</v>
-      </c>
-      <c r="O9">
-        <v>1.42</v>
-      </c>
-      <c r="P9">
-        <v>1.69</v>
-      </c>
-      <c r="Q9">
-        <v>2.22</v>
-      </c>
-      <c r="R9">
-        <v>1.28</v>
-      </c>
-      <c r="S9">
-        <v>4.3</v>
-      </c>
-      <c r="T9">
-        <v>1.89</v>
-      </c>
-      <c r="U9">
-        <v>1.98</v>
-      </c>
-      <c r="V9">
-        <v>1.5</v>
-      </c>
-      <c r="W9">
-        <v>1.54</v>
-      </c>
-      <c r="X9">
-        <v>20</v>
-      </c>
-      <c r="Y9">
-        <v>17</v>
-      </c>
-      <c r="Z9">
-        <v>46</v>
-      </c>
-      <c r="AA9">
-        <v>130</v>
-      </c>
-      <c r="AB9">
-        <v>23</v>
-      </c>
-      <c r="AC9">
-        <v>10</v>
-      </c>
-      <c r="AD9">
-        <v>30</v>
-      </c>
-      <c r="AE9">
-        <v>90</v>
-      </c>
-      <c r="AF9">
-        <v>970</v>
-      </c>
-      <c r="AG9">
-        <v>28</v>
-      </c>
-      <c r="AH9">
-        <v>950</v>
-      </c>
-      <c r="AI9">
-        <v>130</v>
-      </c>
-      <c r="AJ9">
-        <v>110</v>
-      </c>
-      <c r="AK9">
-        <v>85</v>
-      </c>
-      <c r="AL9">
-        <v>120</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>8.4</v>
-      </c>
-      <c r="AQ9">
-        <v>7.2</v>
-      </c>
-      <c r="AR9">
-        <v>11.5</v>
-      </c>
-      <c r="AS9">
-        <v>10</v>
-      </c>
-      <c r="AT9">
-        <v>7.2</v>
-      </c>
-      <c r="AU9">
-        <v>5.8</v>
-      </c>
-      <c r="AV9">
-        <v>1.74</v>
-      </c>
-      <c r="AW9">
-        <v>9.4</v>
-      </c>
-      <c r="AX9">
-        <v>1.77</v>
-      </c>
-      <c r="AY9">
-        <v>1.73</v>
-      </c>
-      <c r="AZ9">
-        <v>1.79</v>
-      </c>
-      <c r="BA9">
-        <v>11</v>
-      </c>
-      <c r="BB9">
-        <v>10.5</v>
-      </c>
-      <c r="BC9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD9">
-        <v>11.5</v>
-      </c>
-      <c r="BE9">
-        <v>1.85</v>
-      </c>
-      <c r="BF9">
-        <v>1.85</v>
-      </c>
-      <c r="BG9">
-        <v>1.85</v>
-      </c>
-      <c r="BH9">
-        <v>3.4</v>
-      </c>
-      <c r="BI9">
-        <v>2.72</v>
-      </c>
-      <c r="BJ9">
-        <v>11.5</v>
-      </c>
-      <c r="BK9">
-        <v>4</v>
-      </c>
-      <c r="BL9">
-        <v>170</v>
-      </c>
-      <c r="BM9">
-        <v>5.8</v>
-      </c>
-      <c r="BN9">
-        <v>6.4</v>
-      </c>
-      <c r="BO9">
-        <v>4.9</v>
-      </c>
-      <c r="BP9">
-        <v>27</v>
-      </c>
-      <c r="BQ9">
-        <v>4.9</v>
-      </c>
-      <c r="BR9">
-        <v>46</v>
-      </c>
-      <c r="BS9">
-        <v>5.3</v>
-      </c>
-      <c r="BT9">
-        <v>6.6</v>
-      </c>
-      <c r="BU9">
-        <v>5</v>
-      </c>
-      <c r="BV9">
-        <v>28</v>
-      </c>
-      <c r="BW9">
-        <v>4.9</v>
-      </c>
-      <c r="BX9">
-        <v>46</v>
-      </c>
-      <c r="BY9">
-        <v>5.3</v>
-      </c>
-      <c r="BZ9">
-        <v>42</v>
-      </c>
-      <c r="CA9">
-        <v>5.2</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
-    <t>US United Soccer League</t>
-  </si>
-  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -280,12 +274,6 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>01:00:00</t>
-  </si>
-  <si>
-    <t>02:00:00</t>
-  </si>
-  <si>
     <t>20:30:00</t>
   </si>
   <si>
@@ -298,12 +286,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Atletico Nacional Medell</t>
-  </si>
-  <si>
-    <t>Sacramento Republic</t>
-  </si>
-  <si>
     <t>Envigado</t>
   </si>
   <si>
@@ -319,12 +301,6 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Junior FC Barranquilla</t>
-  </si>
-  <si>
-    <t>Las Vegas Lights FC</t>
-  </si>
-  <si>
     <t>Orsomarso</t>
   </si>
   <si>
@@ -340,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-09-30 23:19:46</t>
+    <t>2026-10-01 01:31:06</t>
   </si>
 </sst>
 </file>
@@ -672,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -922,241 +898,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="G2">
+        <v>1.79</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>3.45</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>1.5</v>
+      </c>
+      <c r="M2">
+        <v>1.1</v>
+      </c>
+      <c r="N2">
+        <v>2.92</v>
+      </c>
+      <c r="O2">
+        <v>1.45</v>
+      </c>
+      <c r="P2">
+        <v>1.66</v>
+      </c>
+      <c r="Q2">
+        <v>2.34</v>
+      </c>
+      <c r="R2">
         <v>1.25</v>
       </c>
-      <c r="H2">
-        <v>24</v>
-      </c>
-      <c r="I2">
-        <v>30</v>
-      </c>
-      <c r="J2">
-        <v>6.4</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>3.75</v>
-      </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
+        <v>2.26</v>
+      </c>
+      <c r="X2">
+        <v>12.5</v>
+      </c>
+      <c r="Y2">
+        <v>21</v>
+      </c>
+      <c r="Z2">
+        <v>65</v>
+      </c>
+      <c r="AA2">
+        <v>270</v>
+      </c>
+      <c r="AB2">
+        <v>8</v>
+      </c>
+      <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>32</v>
+      </c>
+      <c r="AE2">
+        <v>150</v>
+      </c>
+      <c r="AF2">
+        <v>9.4</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>34</v>
+      </c>
+      <c r="AI2">
+        <v>140</v>
+      </c>
+      <c r="AJ2">
+        <v>22</v>
+      </c>
+      <c r="AK2">
+        <v>27</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>210</v>
+      </c>
+      <c r="AN2">
+        <v>17</v>
+      </c>
+      <c r="AO2">
+        <v>220</v>
+      </c>
+      <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
+        <v>12</v>
+      </c>
+      <c r="AR2">
+        <v>4.9</v>
+      </c>
+      <c r="AS2">
+        <v>5.2</v>
+      </c>
+      <c r="AT2">
+        <v>5.7</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>4.5</v>
+      </c>
+      <c r="AW2">
         <v>5.1</v>
       </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>1000</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
-        <v>3.8</v>
-      </c>
-      <c r="AH2">
-        <v>8.4</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>4.5</v>
-      </c>
-      <c r="AL2">
-        <v>10</v>
-      </c>
-      <c r="AM2">
-        <v>48</v>
-      </c>
-      <c r="AN2">
-        <v>5.6</v>
-      </c>
-      <c r="AO2">
-        <v>150</v>
-      </c>
-      <c r="AP2">
-        <v>11</v>
-      </c>
-      <c r="AQ2">
-        <v>11</v>
-      </c>
-      <c r="AR2">
-        <v>11</v>
-      </c>
-      <c r="AS2">
-        <v>11</v>
-      </c>
-      <c r="AT2">
-        <v>11</v>
-      </c>
-      <c r="AU2">
-        <v>11</v>
-      </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>11</v>
-      </c>
       <c r="AX2">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BA2">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="BB2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BC2">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BE2">
-        <v>38</v>
+        <v>5.1</v>
       </c>
       <c r="BF2">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>80</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1164,241 +1140,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="G3">
+        <v>990</v>
+      </c>
+      <c r="H3">
+        <v>1.1</v>
+      </c>
+      <c r="I3">
+        <v>990</v>
+      </c>
+      <c r="J3">
+        <v>1.1</v>
+      </c>
+      <c r="K3">
+        <v>950</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>1.26</v>
+      </c>
+      <c r="O3">
+        <v>1.54</v>
+      </c>
+      <c r="P3">
+        <v>1.25</v>
+      </c>
+      <c r="Q3">
         <v>1.56</v>
       </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>4.8</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>1.45</v>
-      </c>
-      <c r="M3">
+      <c r="R3">
+        <v>1.18</v>
+      </c>
+      <c r="S3">
+        <v>1.05</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.11</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+      <c r="W3">
         <v>1.06</v>
       </c>
-      <c r="N3">
-        <v>3.9</v>
-      </c>
-      <c r="O3">
-        <v>1.32</v>
-      </c>
-      <c r="P3">
-        <v>2.02</v>
-      </c>
-      <c r="Q3">
-        <v>1.92</v>
-      </c>
-      <c r="R3">
-        <v>1.37</v>
-      </c>
-      <c r="S3">
-        <v>3.4</v>
-      </c>
-      <c r="T3">
-        <v>2.04</v>
-      </c>
-      <c r="U3">
-        <v>1.78</v>
-      </c>
-      <c r="V3">
-        <v>1.13</v>
-      </c>
-      <c r="W3">
-        <v>2.8</v>
-      </c>
       <c r="X3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>28</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>70</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1406,178 +1382,178 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
         <v>87</v>
       </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="G4">
-        <v>1.78</v>
+        <v>18.5</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>1.26</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>1.29</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="K4">
+        <v>7.4</v>
+      </c>
+      <c r="L4">
+        <v>1.31</v>
+      </c>
+      <c r="M4">
+        <v>1.05</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>1.21</v>
+      </c>
+      <c r="P4">
+        <v>2.38</v>
+      </c>
+      <c r="Q4">
+        <v>1.65</v>
+      </c>
+      <c r="R4">
+        <v>1.54</v>
+      </c>
+      <c r="S4">
+        <v>2.66</v>
+      </c>
+      <c r="T4">
+        <v>2.26</v>
+      </c>
+      <c r="U4">
+        <v>1.62</v>
+      </c>
+      <c r="V4">
+        <v>4.4</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>25</v>
+      </c>
+      <c r="Y4">
+        <v>10</v>
+      </c>
+      <c r="Z4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA4">
+        <v>9</v>
+      </c>
+      <c r="AB4">
+        <v>46</v>
+      </c>
+      <c r="AC4">
+        <v>17</v>
+      </c>
+      <c r="AD4">
+        <v>13.5</v>
+      </c>
+      <c r="AE4">
+        <v>14.5</v>
+      </c>
+      <c r="AF4">
+        <v>200</v>
+      </c>
+      <c r="AG4">
+        <v>160</v>
+      </c>
+      <c r="AH4">
+        <v>44</v>
+      </c>
+      <c r="AI4">
+        <v>150</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>380</v>
+      </c>
+      <c r="AL4">
+        <v>270</v>
+      </c>
+      <c r="AM4">
+        <v>290</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>5.2</v>
+      </c>
+      <c r="AP4">
+        <v>17</v>
+      </c>
+      <c r="AQ4">
+        <v>4.1</v>
+      </c>
+      <c r="AR4">
         <v>3.85</v>
       </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.1</v>
-      </c>
-      <c r="N4">
-        <v>2.9</v>
-      </c>
-      <c r="O4">
-        <v>1.47</v>
-      </c>
-      <c r="P4">
-        <v>1.64</v>
-      </c>
-      <c r="Q4">
-        <v>2.38</v>
-      </c>
-      <c r="R4">
-        <v>1.24</v>
-      </c>
-      <c r="S4">
-        <v>4.2</v>
-      </c>
-      <c r="T4">
-        <v>2.16</v>
-      </c>
-      <c r="U4">
-        <v>1.72</v>
-      </c>
-      <c r="V4">
-        <v>1.18</v>
-      </c>
-      <c r="W4">
-        <v>2.28</v>
-      </c>
-      <c r="X4">
-        <v>13</v>
-      </c>
-      <c r="Y4">
+      <c r="AS4">
+        <v>4</v>
+      </c>
+      <c r="AT4">
+        <v>22</v>
+      </c>
+      <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>4.7</v>
+      </c>
+      <c r="AW4">
+        <v>4.8</v>
+      </c>
+      <c r="AX4">
+        <v>7</v>
+      </c>
+      <c r="AY4">
+        <v>27</v>
+      </c>
+      <c r="AZ4">
         <v>21</v>
       </c>
-      <c r="Z4">
-        <v>65</v>
-      </c>
-      <c r="AA4">
-        <v>280</v>
-      </c>
-      <c r="AB4">
-        <v>6.6</v>
-      </c>
-      <c r="AC4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD4">
-        <v>34</v>
-      </c>
-      <c r="AE4">
-        <v>160</v>
-      </c>
-      <c r="AF4">
-        <v>9.4</v>
-      </c>
-      <c r="AG4">
-        <v>13</v>
-      </c>
-      <c r="AH4">
-        <v>34</v>
-      </c>
-      <c r="AI4">
-        <v>140</v>
-      </c>
-      <c r="AJ4">
-        <v>22</v>
-      </c>
-      <c r="AK4">
-        <v>27</v>
-      </c>
-      <c r="AL4">
-        <v>60</v>
-      </c>
-      <c r="AM4">
-        <v>220</v>
-      </c>
-      <c r="AN4">
-        <v>17.5</v>
-      </c>
-      <c r="AO4">
-        <v>240</v>
-      </c>
-      <c r="AP4">
-        <v>9</v>
-      </c>
-      <c r="AQ4">
-        <v>12</v>
-      </c>
-      <c r="AR4">
-        <v>5.3</v>
-      </c>
-      <c r="AS4">
-        <v>5.7</v>
-      </c>
-      <c r="AT4">
-        <v>5.7</v>
-      </c>
-      <c r="AU4">
-        <v>7.4</v>
-      </c>
-      <c r="AV4">
-        <v>4.9</v>
-      </c>
-      <c r="AW4">
-        <v>5.6</v>
-      </c>
-      <c r="AX4">
-        <v>7.8</v>
-      </c>
-      <c r="AY4">
-        <v>9</v>
-      </c>
-      <c r="AZ4">
-        <v>22</v>
-      </c>
       <c r="BA4">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="BC4">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BD4">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1640,7 +1616,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1648,178 +1624,178 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5">
+        <v>1.66</v>
+      </c>
+      <c r="G5">
+        <v>1.72</v>
+      </c>
+      <c r="H5">
+        <v>5.4</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>4.1</v>
+      </c>
+      <c r="K5">
+        <v>4.4</v>
+      </c>
+      <c r="L5">
+        <v>1.37</v>
+      </c>
+      <c r="M5">
+        <v>1.05</v>
+      </c>
+      <c r="N5">
+        <v>4.2</v>
+      </c>
+      <c r="O5">
+        <v>1.29</v>
+      </c>
+      <c r="P5">
+        <v>2.1</v>
+      </c>
+      <c r="Q5">
+        <v>1.85</v>
+      </c>
+      <c r="R5">
+        <v>1.43</v>
+      </c>
+      <c r="S5">
+        <v>3.1</v>
+      </c>
+      <c r="T5">
+        <v>1.86</v>
+      </c>
+      <c r="U5">
+        <v>1.98</v>
+      </c>
+      <c r="V5">
+        <v>1.2</v>
+      </c>
+      <c r="W5">
+        <v>2.38</v>
+      </c>
+      <c r="X5">
+        <v>17.5</v>
+      </c>
+      <c r="Y5">
+        <v>22</v>
+      </c>
+      <c r="Z5">
+        <v>48</v>
+      </c>
+      <c r="AA5">
+        <v>170</v>
+      </c>
+      <c r="AB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>21</v>
+      </c>
+      <c r="AE5">
+        <v>85</v>
+      </c>
+      <c r="AF5">
+        <v>10.5</v>
+      </c>
+      <c r="AG5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>22</v>
+      </c>
+      <c r="AI5">
+        <v>100</v>
+      </c>
+      <c r="AJ5">
+        <v>18</v>
+      </c>
+      <c r="AK5">
+        <v>18</v>
+      </c>
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO5">
         <v>90</v>
       </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5">
-        <v>1.13</v>
-      </c>
-      <c r="G5">
-        <v>990</v>
-      </c>
-      <c r="H5">
-        <v>1.1</v>
-      </c>
-      <c r="I5">
-        <v>990</v>
-      </c>
-      <c r="J5">
-        <v>1.1</v>
-      </c>
-      <c r="K5">
-        <v>950</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>1.26</v>
-      </c>
-      <c r="O5">
-        <v>1.54</v>
-      </c>
-      <c r="P5">
-        <v>1.25</v>
-      </c>
-      <c r="Q5">
-        <v>1.56</v>
-      </c>
-      <c r="R5">
-        <v>1.18</v>
-      </c>
-      <c r="S5">
-        <v>1.05</v>
-      </c>
-      <c r="T5">
-        <v>1.11</v>
-      </c>
-      <c r="U5">
-        <v>1.11</v>
-      </c>
-      <c r="V5">
-        <v>1.01</v>
-      </c>
-      <c r="W5">
-        <v>1.06</v>
-      </c>
-      <c r="X5">
-        <v>1000</v>
-      </c>
-      <c r="Y5">
-        <v>1000</v>
-      </c>
-      <c r="Z5">
-        <v>1000</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>1000</v>
-      </c>
-      <c r="AC5">
-        <v>1000</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>1000</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1882,7 +1858,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1890,725 +1866,241 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>2.74</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>2.82</v>
       </c>
       <c r="H6">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="I6">
-        <v>1.29</v>
+        <v>2.96</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="P6">
-        <v>2.38</v>
+        <v>1.74</v>
       </c>
       <c r="Q6">
-        <v>1.58</v>
+        <v>2.26</v>
       </c>
       <c r="R6">
+        <v>1.27</v>
+      </c>
+      <c r="S6">
+        <v>4.3</v>
+      </c>
+      <c r="T6">
+        <v>1.93</v>
+      </c>
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>1.51</v>
+      </c>
+      <c r="W6">
         <v>1.54</v>
       </c>
-      <c r="S6">
-        <v>2.54</v>
-      </c>
-      <c r="T6">
-        <v>2.28</v>
-      </c>
-      <c r="U6">
-        <v>1.62</v>
-      </c>
-      <c r="V6">
-        <v>4.4</v>
-      </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
       <c r="X6">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
         <v>10.5</v>
       </c>
       <c r="Z6">
+        <v>19</v>
+      </c>
+      <c r="AA6">
+        <v>60</v>
+      </c>
+      <c r="AB6">
+        <v>10</v>
+      </c>
+      <c r="AC6">
+        <v>7.6</v>
+      </c>
+      <c r="AD6">
+        <v>14</v>
+      </c>
+      <c r="AE6">
+        <v>44</v>
+      </c>
+      <c r="AF6">
+        <v>18</v>
+      </c>
+      <c r="AG6">
+        <v>13.5</v>
+      </c>
+      <c r="AH6">
+        <v>22</v>
+      </c>
+      <c r="AI6">
+        <v>65</v>
+      </c>
+      <c r="AJ6">
+        <v>55</v>
+      </c>
+      <c r="AK6">
+        <v>40</v>
+      </c>
+      <c r="AL6">
+        <v>60</v>
+      </c>
+      <c r="AM6">
+        <v>140</v>
+      </c>
+      <c r="AN6">
+        <v>40</v>
+      </c>
+      <c r="AO6">
+        <v>44</v>
+      </c>
+      <c r="AP6">
+        <v>10</v>
+      </c>
+      <c r="AQ6">
+        <v>9</v>
+      </c>
+      <c r="AR6">
+        <v>16</v>
+      </c>
+      <c r="AS6">
+        <v>20</v>
+      </c>
+      <c r="AT6">
+        <v>8.6</v>
+      </c>
+      <c r="AU6">
+        <v>6.6</v>
+      </c>
+      <c r="AV6">
+        <v>11.5</v>
+      </c>
+      <c r="AW6">
+        <v>15.5</v>
+      </c>
+      <c r="AX6">
+        <v>15</v>
+      </c>
+      <c r="AY6">
+        <v>11</v>
+      </c>
+      <c r="AZ6">
+        <v>16.5</v>
+      </c>
+      <c r="BA6">
+        <v>21</v>
+      </c>
+      <c r="BB6">
+        <v>19</v>
+      </c>
+      <c r="BC6">
+        <v>14.5</v>
+      </c>
+      <c r="BD6">
+        <v>20</v>
+      </c>
+      <c r="BE6">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AA6">
-        <v>9</v>
-      </c>
-      <c r="AB6">
-        <v>150</v>
-      </c>
-      <c r="AC6">
-        <v>17</v>
-      </c>
-      <c r="AD6">
-        <v>13.5</v>
-      </c>
-      <c r="AE6">
-        <v>14.5</v>
-      </c>
-      <c r="AF6">
-        <v>200</v>
-      </c>
-      <c r="AG6">
-        <v>65</v>
-      </c>
-      <c r="AH6">
-        <v>44</v>
-      </c>
-      <c r="AI6">
-        <v>160</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>380</v>
-      </c>
-      <c r="AL6">
-        <v>270</v>
-      </c>
-      <c r="AM6">
-        <v>290</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>5</v>
-      </c>
-      <c r="AP6">
-        <v>16.5</v>
-      </c>
-      <c r="AQ6">
-        <v>7.6</v>
-      </c>
-      <c r="AR6">
-        <v>6.6</v>
-      </c>
-      <c r="AS6">
-        <v>7.2</v>
-      </c>
-      <c r="AT6">
-        <v>36</v>
-      </c>
-      <c r="AU6">
-        <v>12</v>
-      </c>
-      <c r="AV6">
-        <v>10</v>
-      </c>
-      <c r="AW6">
-        <v>4.8</v>
-      </c>
-      <c r="AX6">
-        <v>6.8</v>
-      </c>
-      <c r="AY6">
-        <v>6.4</v>
-      </c>
-      <c r="AZ6">
-        <v>32</v>
-      </c>
-      <c r="BA6">
-        <v>40</v>
-      </c>
-      <c r="BB6">
-        <v>7.2</v>
-      </c>
-      <c r="BC6">
-        <v>7</v>
-      </c>
-      <c r="BD6">
-        <v>7</v>
-      </c>
-      <c r="BE6">
-        <v>7</v>
       </c>
       <c r="BF6">
         <v>7.2</v>
       </c>
       <c r="BG6">
+        <v>7.4</v>
+      </c>
+      <c r="BH6">
         <v>3.4</v>
       </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:80">
-      <c r="A7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7">
-        <v>1.67</v>
-      </c>
-      <c r="G7">
-        <v>1.75</v>
-      </c>
-      <c r="H7">
-        <v>5.5</v>
-      </c>
-      <c r="I7">
-        <v>6.2</v>
-      </c>
-      <c r="J7">
-        <v>3.95</v>
-      </c>
-      <c r="K7">
-        <v>4.3</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.07</v>
-      </c>
-      <c r="N7">
-        <v>3.7</v>
-      </c>
-      <c r="O7">
-        <v>1.32</v>
-      </c>
-      <c r="P7">
-        <v>1.92</v>
-      </c>
-      <c r="Q7">
-        <v>1.92</v>
-      </c>
-      <c r="R7">
-        <v>1.34</v>
-      </c>
-      <c r="S7">
-        <v>3.65</v>
-      </c>
-      <c r="T7">
-        <v>1.98</v>
-      </c>
-      <c r="U7">
-        <v>1.92</v>
-      </c>
-      <c r="V7">
-        <v>1.2</v>
-      </c>
-      <c r="W7">
-        <v>2.32</v>
-      </c>
-      <c r="X7">
-        <v>15</v>
-      </c>
-      <c r="Y7">
-        <v>19</v>
-      </c>
-      <c r="Z7">
-        <v>80</v>
-      </c>
-      <c r="AA7">
-        <v>180</v>
-      </c>
-      <c r="AB7">
-        <v>8.4</v>
-      </c>
-      <c r="AC7">
-        <v>11</v>
-      </c>
-      <c r="AD7">
-        <v>24</v>
-      </c>
-      <c r="AE7">
-        <v>95</v>
-      </c>
-      <c r="AF7">
-        <v>10</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>24</v>
-      </c>
-      <c r="AI7">
-        <v>110</v>
-      </c>
-      <c r="AJ7">
-        <v>18</v>
-      </c>
-      <c r="AK7">
-        <v>19</v>
-      </c>
-      <c r="AL7">
-        <v>44</v>
-      </c>
-      <c r="AM7">
-        <v>150</v>
-      </c>
-      <c r="AN7">
-        <v>12.5</v>
-      </c>
-      <c r="AO7">
-        <v>120</v>
-      </c>
-      <c r="AP7">
-        <v>12.5</v>
-      </c>
-      <c r="AQ7">
-        <v>17</v>
-      </c>
-      <c r="AR7">
-        <v>38</v>
-      </c>
-      <c r="AS7">
-        <v>11</v>
-      </c>
-      <c r="AT7">
-        <v>7.4</v>
-      </c>
-      <c r="AU7">
-        <v>8.4</v>
-      </c>
-      <c r="AV7">
-        <v>19.5</v>
-      </c>
-      <c r="AW7">
-        <v>55</v>
-      </c>
-      <c r="AX7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7">
-        <v>19.5</v>
-      </c>
-      <c r="BA7">
-        <v>65</v>
-      </c>
-      <c r="BB7">
-        <v>16</v>
-      </c>
-      <c r="BC7">
-        <v>15.5</v>
-      </c>
-      <c r="BD7">
-        <v>32</v>
-      </c>
-      <c r="BE7">
-        <v>11.5</v>
-      </c>
-      <c r="BF7">
-        <v>9.6</v>
-      </c>
-      <c r="BG7">
-        <v>44</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.04</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.04</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>1.04</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>1.04</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>1.04</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>1.04</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:80">
-      <c r="A8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
         <v>100</v>
-      </c>
-      <c r="E8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8">
-        <v>2.74</v>
-      </c>
-      <c r="G8">
-        <v>2.82</v>
-      </c>
-      <c r="H8">
-        <v>2.88</v>
-      </c>
-      <c r="I8">
-        <v>2.96</v>
-      </c>
-      <c r="J8">
-        <v>3.25</v>
-      </c>
-      <c r="K8">
-        <v>3.4</v>
-      </c>
-      <c r="L8">
-        <v>1.47</v>
-      </c>
-      <c r="M8">
-        <v>1.09</v>
-      </c>
-      <c r="N8">
-        <v>3.25</v>
-      </c>
-      <c r="O8">
-        <v>1.42</v>
-      </c>
-      <c r="P8">
-        <v>1.73</v>
-      </c>
-      <c r="Q8">
-        <v>2.26</v>
-      </c>
-      <c r="R8">
-        <v>1.28</v>
-      </c>
-      <c r="S8">
-        <v>4.3</v>
-      </c>
-      <c r="T8">
-        <v>1.89</v>
-      </c>
-      <c r="U8">
-        <v>2</v>
-      </c>
-      <c r="V8">
-        <v>1.51</v>
-      </c>
-      <c r="W8">
-        <v>1.54</v>
-      </c>
-      <c r="X8">
-        <v>11.5</v>
-      </c>
-      <c r="Y8">
-        <v>10.5</v>
-      </c>
-      <c r="Z8">
-        <v>19</v>
-      </c>
-      <c r="AA8">
-        <v>60</v>
-      </c>
-      <c r="AB8">
-        <v>10</v>
-      </c>
-      <c r="AC8">
-        <v>7.6</v>
-      </c>
-      <c r="AD8">
-        <v>14</v>
-      </c>
-      <c r="AE8">
-        <v>44</v>
-      </c>
-      <c r="AF8">
-        <v>18</v>
-      </c>
-      <c r="AG8">
-        <v>13.5</v>
-      </c>
-      <c r="AH8">
-        <v>22</v>
-      </c>
-      <c r="AI8">
-        <v>60</v>
-      </c>
-      <c r="AJ8">
-        <v>55</v>
-      </c>
-      <c r="AK8">
-        <v>42</v>
-      </c>
-      <c r="AL8">
-        <v>60</v>
-      </c>
-      <c r="AM8">
-        <v>140</v>
-      </c>
-      <c r="AN8">
-        <v>40</v>
-      </c>
-      <c r="AO8">
-        <v>44</v>
-      </c>
-      <c r="AP8">
-        <v>10</v>
-      </c>
-      <c r="AQ8">
-        <v>9</v>
-      </c>
-      <c r="AR8">
-        <v>16</v>
-      </c>
-      <c r="AS8">
-        <v>20</v>
-      </c>
-      <c r="AT8">
-        <v>8.6</v>
-      </c>
-      <c r="AU8">
-        <v>6.6</v>
-      </c>
-      <c r="AV8">
-        <v>11.5</v>
-      </c>
-      <c r="AW8">
-        <v>15.5</v>
-      </c>
-      <c r="AX8">
-        <v>15</v>
-      </c>
-      <c r="AY8">
-        <v>11</v>
-      </c>
-      <c r="AZ8">
-        <v>16.5</v>
-      </c>
-      <c r="BA8">
-        <v>21</v>
-      </c>
-      <c r="BB8">
-        <v>19</v>
-      </c>
-      <c r="BC8">
-        <v>14.5</v>
-      </c>
-      <c r="BD8">
-        <v>20</v>
-      </c>
-      <c r="BE8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF8">
-        <v>7.2</v>
-      </c>
-      <c r="BG8">
-        <v>7.4</v>
-      </c>
-      <c r="BH8">
-        <v>3.4</v>
-      </c>
-      <c r="BI8">
-        <v>2.8</v>
-      </c>
-      <c r="BJ8">
-        <v>11.5</v>
-      </c>
-      <c r="BK8">
-        <v>4</v>
-      </c>
-      <c r="BL8">
-        <v>170</v>
-      </c>
-      <c r="BM8">
-        <v>5.8</v>
-      </c>
-      <c r="BN8">
-        <v>6.4</v>
-      </c>
-      <c r="BO8">
-        <v>5.1</v>
-      </c>
-      <c r="BP8">
-        <v>27</v>
-      </c>
-      <c r="BQ8">
-        <v>4.9</v>
-      </c>
-      <c r="BR8">
-        <v>46</v>
-      </c>
-      <c r="BS8">
-        <v>5.3</v>
-      </c>
-      <c r="BT8">
-        <v>6.6</v>
-      </c>
-      <c r="BU8">
-        <v>5.2</v>
-      </c>
-      <c r="BV8">
-        <v>28</v>
-      </c>
-      <c r="BW8">
-        <v>4.9</v>
-      </c>
-      <c r="BX8">
-        <v>46</v>
-      </c>
-      <c r="BY8">
-        <v>5.3</v>
-      </c>
-      <c r="BZ8">
-        <v>42</v>
-      </c>
-      <c r="CA8">
-        <v>5.2</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 01:31:06</t>
+    <t>2026-10-01 03:43:34</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
         <v>1.67</v>
       </c>
       <c r="G2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -925,7 +925,7 @@
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.5</v>
@@ -934,13 +934,13 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O2">
         <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q2">
         <v>2.34</v>
@@ -955,28 +955,28 @@
         <v>2.12</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V2">
         <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X2">
         <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
@@ -985,7 +985,7 @@
         <v>32</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF2">
         <v>9.4</v>
@@ -997,7 +997,7 @@
         <v>34</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
         <v>22</v>
@@ -1015,7 +1015,7 @@
         <v>17</v>
       </c>
       <c r="AO2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP2">
         <v>9</v>
@@ -1024,10 +1024,10 @@
         <v>12</v>
       </c>
       <c r="AR2">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS2">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT2">
         <v>5.7</v>
@@ -1036,22 +1036,22 @@
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="BA2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB2">
         <v>15</v>
@@ -1060,76 +1060,76 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE2">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF2">
         <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
         <v>100</v>
@@ -1152,166 +1152,166 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="G3">
-        <v>990</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>1.26</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1394,7 +1394,7 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="G4">
         <v>18.5</v>
@@ -1403,7 +1403,7 @@
         <v>1.26</v>
       </c>
       <c r="I4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J4">
         <v>5.9</v>
@@ -1418,7 +1418,7 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
         <v>1.21</v>
@@ -1436,10 +1436,10 @@
         <v>2.66</v>
       </c>
       <c r="T4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
         <v>4.4</v>
@@ -1448,112 +1448,112 @@
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="AB4">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AC4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AR4">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AS4">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
         <v>22</v>
       </c>
       <c r="AU4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AV4">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AW4">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX4">
-        <v>7</v>
+        <v>1.61</v>
       </c>
       <c r="AY4">
-        <v>27</v>
+        <v>1.58</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4">
-        <v>6.4</v>
+        <v>1.61</v>
       </c>
       <c r="BB4">
-        <v>7.2</v>
+        <v>1.61</v>
       </c>
       <c r="BC4">
-        <v>7</v>
+        <v>1.61</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>1.61</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>1.61</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>1.61</v>
       </c>
       <c r="BG4">
-        <v>3.05</v>
+        <v>1.61</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1636,22 +1636,22 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G5">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.37</v>
@@ -1660,40 +1660,40 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q5">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R5">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="X5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5">
         <v>48</v>
@@ -1702,34 +1702,34 @@
         <v>170</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL5">
         <v>36</v>
@@ -1738,124 +1738,124 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV5">
         <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX5">
         <v>9</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA5">
+        <v>55</v>
+      </c>
+      <c r="BB5">
+        <v>15</v>
+      </c>
+      <c r="BC5">
+        <v>15</v>
+      </c>
+      <c r="BD5">
+        <v>28</v>
+      </c>
+      <c r="BE5">
+        <v>75</v>
+      </c>
+      <c r="BF5">
+        <v>7.8</v>
+      </c>
+      <c r="BG5">
+        <v>44</v>
+      </c>
+      <c r="BH5">
+        <v>4.4</v>
+      </c>
+      <c r="BI5">
+        <v>2.98</v>
+      </c>
+      <c r="BJ5">
         <v>12.5</v>
       </c>
-      <c r="BB5">
-        <v>14</v>
-      </c>
-      <c r="BC5">
-        <v>16</v>
-      </c>
-      <c r="BD5">
-        <v>27</v>
-      </c>
-      <c r="BE5">
+      <c r="BK5">
+        <v>3.4</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>4.5</v>
+      </c>
+      <c r="BN5">
+        <v>5</v>
+      </c>
+      <c r="BO5">
+        <v>3.35</v>
+      </c>
+      <c r="BP5">
         <v>13</v>
       </c>
-      <c r="BF5">
-        <v>8.4</v>
-      </c>
-      <c r="BG5">
+      <c r="BQ5">
+        <v>3.45</v>
+      </c>
+      <c r="BR5">
+        <v>30</v>
+      </c>
+      <c r="BS5">
+        <v>4</v>
+      </c>
+      <c r="BT5">
+        <v>11.5</v>
+      </c>
+      <c r="BU5">
+        <v>3.35</v>
+      </c>
+      <c r="BV5">
         <v>60</v>
       </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.04</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1896,34 +1896,34 @@
         <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P6">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q6">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T6">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
         <v>1.51</v>
@@ -1932,7 +1932,7 @@
         <v>1.54</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>10.5</v>
@@ -1944,7 +1944,7 @@
         <v>60</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -1962,19 +1962,19 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI6">
         <v>65</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM6">
         <v>140</v>
@@ -1986,19 +1986,19 @@
         <v>44</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6">
         <v>16</v>
       </c>
       <c r="AS6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
@@ -2007,7 +2007,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX6">
         <v>15</v>
@@ -2019,7 +2019,7 @@
         <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB6">
         <v>19</v>
@@ -2028,37 +2028,37 @@
         <v>14.5</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI6">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BL6">
         <v>170</v>
       </c>
       <c r="BM6">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BN6">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO6">
         <v>5</v>
@@ -2067,16 +2067,16 @@
         <v>27</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR6">
         <v>46</v>
       </c>
       <c r="BS6">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BU6">
         <v>5.2</v>
@@ -2085,19 +2085,19 @@
         <v>28</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY6">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BZ6">
         <v>42</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 03:43:34</t>
+    <t>2026-10-01 05:55:51</t>
   </si>
 </sst>
 </file>
@@ -910,19 +910,19 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
         <v>1.8</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>7</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
         <v>3.85</v>
@@ -952,10 +952,10 @@
         <v>4.5</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
         <v>1.16</v>
@@ -964,28 +964,28 @@
         <v>2.24</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB2">
         <v>7</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>32</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF2">
         <v>9.4</v>
@@ -994,82 +994,82 @@
         <v>13</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN2">
         <v>17</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>370</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AS2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>5.1</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>5.8</v>
+        <v>55</v>
       </c>
       <c r="AX2">
         <v>8</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BA2">
-        <v>5.8</v>
+        <v>55</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG2">
-        <v>5.9</v>
+        <v>100</v>
       </c>
       <c r="BH2">
         <v>3.05</v>
@@ -1114,7 +1114,7 @@
         <v>5.3</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>10</v>
@@ -1152,61 +1152,61 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G3">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I3">
         <v>5.6</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
         <v>2.56</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
         <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>15.5</v>
@@ -1242,19 +1242,19 @@
         <v>140</v>
       </c>
       <c r="AJ3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM3">
         <v>270</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO3">
         <v>200</v>
@@ -1263,13 +1263,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR3">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
         <v>5.5</v>
@@ -1278,43 +1278,43 @@
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW3">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY3">
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
+        <v>5</v>
+      </c>
+      <c r="BE3">
+        <v>5.3</v>
+      </c>
+      <c r="BF3">
+        <v>18</v>
+      </c>
+      <c r="BG3">
         <v>5.2</v>
       </c>
-      <c r="BE3">
-        <v>5.5</v>
-      </c>
-      <c r="BF3">
-        <v>21</v>
-      </c>
-      <c r="BG3">
-        <v>5.4</v>
-      </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI3">
         <v>1.04</v>
@@ -1323,55 +1323,55 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1397,16 +1397,16 @@
         <v>12.5</v>
       </c>
       <c r="G4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I4">
         <v>1.28</v>
       </c>
       <c r="J4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7.4</v>
@@ -1415,7 +1415,7 @@
         <v>1.31</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>5.1</v>
@@ -1439,130 +1439,130 @@
         <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AC4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AG4">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
+        <v>4.2</v>
+      </c>
+      <c r="AR4">
+        <v>3.7</v>
+      </c>
+      <c r="AS4">
+        <v>3.9</v>
+      </c>
+      <c r="AT4">
+        <v>36</v>
+      </c>
+      <c r="AU4">
+        <v>13</v>
+      </c>
+      <c r="AV4">
+        <v>10.5</v>
+      </c>
+      <c r="AW4">
+        <v>11.5</v>
+      </c>
+      <c r="AX4">
         <v>6.6</v>
       </c>
-      <c r="AR4">
-        <v>5.4</v>
-      </c>
-      <c r="AS4">
+      <c r="AY4">
         <v>6.2</v>
       </c>
-      <c r="AT4">
-        <v>22</v>
-      </c>
-      <c r="AU4">
-        <v>11</v>
-      </c>
-      <c r="AV4">
-        <v>8.6</v>
-      </c>
-      <c r="AW4">
-        <v>8.6</v>
-      </c>
-      <c r="AX4">
-        <v>1.61</v>
-      </c>
-      <c r="AY4">
-        <v>1.58</v>
-      </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="BA4">
-        <v>1.61</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>1.61</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>1.61</v>
+        <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>1.61</v>
+        <v>6.8</v>
       </c>
       <c r="BE4">
-        <v>1.61</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>1.61</v>
+        <v>7</v>
       </c>
       <c r="BG4">
-        <v>1.61</v>
+        <v>3.35</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK4">
         <v>1.04</v>
@@ -1574,7 +1574,7 @@
         <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BO4">
         <v>1.04</v>
@@ -1592,25 +1592,25 @@
         <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY4">
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA4">
         <v>1.04</v>
@@ -1639,13 +1639,13 @@
         <v>1.65</v>
       </c>
       <c r="G5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>4.3</v>
@@ -1663,22 +1663,22 @@
         <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2.06</v>
@@ -1690,10 +1690,10 @@
         <v>2.48</v>
       </c>
       <c r="X5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z5">
         <v>48</v>
@@ -1702,28 +1702,28 @@
         <v>170</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD5">
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
         <v>17.5</v>
@@ -1732,13 +1732,13 @@
         <v>17.5</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5">
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5">
         <v>85</v>
@@ -1747,28 +1747,28 @@
         <v>16</v>
       </c>
       <c r="AQ5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR5">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS5">
         <v>13</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>9</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW5">
         <v>60</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5">
         <v>9.199999999999999</v>
@@ -1777,7 +1777,7 @@
         <v>19</v>
       </c>
       <c r="BA5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB5">
         <v>15</v>
@@ -1786,37 +1786,37 @@
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE5">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="BF5">
         <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO5">
         <v>3.35</v>
@@ -1825,25 +1825,25 @@
         <v>13</v>
       </c>
       <c r="BQ5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BR5">
         <v>30</v>
       </c>
       <c r="BS5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV5">
         <v>60</v>
       </c>
       <c r="BW5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX5">
         <v>65</v>
@@ -1852,10 +1852,10 @@
         <v>4.4</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA5">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1878,7 +1878,7 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G6">
         <v>2.82</v>
@@ -1893,37 +1893,37 @@
         <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M6">
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
         <v>1.51</v>
@@ -1935,7 +1935,7 @@
         <v>11</v>
       </c>
       <c r="Y6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6">
         <v>19</v>
@@ -1962,7 +1962,7 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6">
         <v>65</v>
@@ -1971,7 +1971,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AL6">
         <v>65</v>
@@ -1980,7 +1980,7 @@
         <v>140</v>
       </c>
       <c r="AN6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO6">
         <v>44</v>
@@ -1989,13 +1989,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR6">
         <v>16</v>
       </c>
       <c r="AS6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2016,88 +2016,88 @@
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB6">
         <v>19</v>
       </c>
       <c r="BC6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BE6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG6">
         <v>7.8</v>
       </c>
       <c r="BH6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="BM6">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN6">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
         <v>5</v>
       </c>
       <c r="BP6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ6">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR6">
+        <v>48</v>
+      </c>
+      <c r="BS6">
+        <v>5.2</v>
+      </c>
+      <c r="BT6">
+        <v>6.6</v>
+      </c>
+      <c r="BU6">
+        <v>5.1</v>
+      </c>
+      <c r="BV6">
+        <v>29</v>
+      </c>
+      <c r="BW6">
+        <v>4.9</v>
+      </c>
+      <c r="BX6">
+        <v>50</v>
+      </c>
+      <c r="BY6">
+        <v>5.3</v>
+      </c>
+      <c r="BZ6">
         <v>46</v>
       </c>
-      <c r="BS6">
-        <v>7</v>
-      </c>
-      <c r="BT6">
-        <v>6</v>
-      </c>
-      <c r="BU6">
+      <c r="CA6">
         <v>5.2</v>
-      </c>
-      <c r="BV6">
-        <v>28</v>
-      </c>
-      <c r="BW6">
-        <v>6.2</v>
-      </c>
-      <c r="BX6">
-        <v>48</v>
-      </c>
-      <c r="BY6">
-        <v>7</v>
-      </c>
-      <c r="BZ6">
-        <v>42</v>
-      </c>
-      <c r="CA6">
-        <v>6.8</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 05:55:51</t>
+    <t>2026-10-01 08:08:20</t>
   </si>
 </sst>
 </file>
@@ -910,16 +910,16 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>3.6</v>
@@ -928,46 +928,46 @@
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R2">
         <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
         <v>55</v>
@@ -976,67 +976,67 @@
         <v>270</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC2">
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF2">
         <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AK2">
         <v>23</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM2">
         <v>220</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AP2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS2">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW2">
         <v>55</v>
@@ -1048,13 +1048,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
@@ -1063,19 +1063,19 @@
         <v>30</v>
       </c>
       <c r="BE2">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>3.05</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
@@ -1129,7 +1129,7 @@
         <v>32</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>100</v>
@@ -1152,31 +1152,31 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G3">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
         <v>1.55</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O3">
         <v>1.55</v>
@@ -1188,34 +1188,34 @@
         <v>2.56</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z3">
         <v>46</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB3">
         <v>6.8</v>
@@ -1224,19 +1224,19 @@
         <v>8</v>
       </c>
       <c r="AD3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE3">
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>140</v>
@@ -1245,10 +1245,10 @@
         <v>30</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM3">
         <v>270</v>
@@ -1263,13 +1263,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT3">
         <v>5.5</v>
@@ -1278,10 +1278,10 @@
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX3">
         <v>9</v>
@@ -1293,85 +1293,85 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC3">
+        <v>19</v>
+      </c>
+      <c r="BD3">
+        <v>6.8</v>
+      </c>
+      <c r="BE3">
+        <v>7</v>
+      </c>
+      <c r="BF3">
         <v>20</v>
       </c>
-      <c r="BD3">
-        <v>5</v>
-      </c>
-      <c r="BE3">
-        <v>5.3</v>
-      </c>
-      <c r="BF3">
-        <v>18</v>
-      </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH3">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>1.49</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>1.49</v>
+        <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ3">
-        <v>1.49</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS3">
-        <v>1.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU3">
-        <v>1.49</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.49</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.49</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.49</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1394,13 +1394,13 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>17.5</v>
       </c>
       <c r="H4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I4">
         <v>1.28</v>
@@ -1424,7 +1424,7 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>1.65</v>
@@ -1436,10 +1436,10 @@
         <v>2.66</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
         <v>4.5</v>
@@ -1454,67 +1454,67 @@
         <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB4">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AC4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD4">
         <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AH4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AL4">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AM4">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AP4">
         <v>17</v>
       </c>
       <c r="AQ4">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS4">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT4">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
         <v>13</v>
@@ -1526,43 +1526,43 @@
         <v>11.5</v>
       </c>
       <c r="AX4">
+        <v>7.2</v>
+      </c>
+      <c r="AY4">
+        <v>6.8</v>
+      </c>
+      <c r="AZ4">
         <v>6.6</v>
       </c>
-      <c r="AY4">
-        <v>6.2</v>
-      </c>
-      <c r="AZ4">
-        <v>6</v>
-      </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG4">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BH4">
         <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK4">
         <v>1.04</v>
@@ -1598,7 +1598,7 @@
         <v>2.84</v>
       </c>
       <c r="BV4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BW4">
         <v>5</v>
@@ -1636,7 +1636,7 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G5">
         <v>1.67</v>
@@ -1660,28 +1660,28 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q5">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R5">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
         <v>1.2</v>
@@ -1690,76 +1690,76 @@
         <v>2.48</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y5">
+        <v>23</v>
+      </c>
+      <c r="Z5">
+        <v>50</v>
+      </c>
+      <c r="AA5">
+        <v>160</v>
+      </c>
+      <c r="AB5">
+        <v>9.4</v>
+      </c>
+      <c r="AC5">
+        <v>10.5</v>
+      </c>
+      <c r="AD5">
         <v>22</v>
       </c>
-      <c r="Z5">
-        <v>48</v>
-      </c>
-      <c r="AA5">
-        <v>170</v>
-      </c>
-      <c r="AB5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC5">
-        <v>12</v>
-      </c>
-      <c r="AD5">
-        <v>21</v>
-      </c>
       <c r="AE5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO5">
         <v>85</v>
       </c>
       <c r="AP5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AS5">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
         <v>20</v>
@@ -1768,13 +1768,13 @@
         <v>60</v>
       </c>
       <c r="AX5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA5">
         <v>60</v>
@@ -1783,40 +1783,40 @@
         <v>15</v>
       </c>
       <c r="BC5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
         <v>29</v>
       </c>
       <c r="BE5">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="BF5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO5">
         <v>3.35</v>
@@ -1825,25 +1825,25 @@
         <v>13</v>
       </c>
       <c r="BQ5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BR5">
         <v>30</v>
       </c>
       <c r="BS5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV5">
         <v>60</v>
       </c>
       <c r="BW5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX5">
         <v>65</v>
@@ -1852,10 +1852,10 @@
         <v>4.4</v>
       </c>
       <c r="BZ5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1878,106 +1878,106 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G6">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I6">
         <v>2.96</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O6">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P6">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q6">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T6">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V6">
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA6">
         <v>60</v>
       </c>
       <c r="AB6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>14</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN6">
         <v>46</v>
@@ -1986,79 +1986,79 @@
         <v>44</v>
       </c>
       <c r="AP6">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AX6">
         <v>15</v>
       </c>
       <c r="AY6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC6">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BD6">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF6">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BL6">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO6">
         <v>5</v>
@@ -2067,37 +2067,37 @@
         <v>28</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT6">
         <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 08:08:20</t>
+    <t>2026-10-01 10:21:32</t>
   </si>
 </sst>
 </file>
@@ -910,64 +910,64 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O2">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P2">
+        <v>1.63</v>
+      </c>
+      <c r="Q2">
+        <v>2.46</v>
+      </c>
+      <c r="R2">
+        <v>1.23</v>
+      </c>
+      <c r="S2">
+        <v>4.8</v>
+      </c>
+      <c r="T2">
+        <v>2.3</v>
+      </c>
+      <c r="U2">
         <v>1.66</v>
-      </c>
-      <c r="Q2">
-        <v>2.36</v>
-      </c>
-      <c r="R2">
-        <v>1.25</v>
-      </c>
-      <c r="S2">
-        <v>4.6</v>
-      </c>
-      <c r="T2">
-        <v>2.14</v>
-      </c>
-      <c r="U2">
-        <v>1.73</v>
       </c>
       <c r="V2">
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z2">
         <v>55</v>
@@ -976,7 +976,7 @@
         <v>270</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC2">
         <v>9</v>
@@ -985,7 +985,7 @@
         <v>28</v>
       </c>
       <c r="AE2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF2">
         <v>9.4</v>
@@ -994,7 +994,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1003,22 +1003,22 @@
         <v>19</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>220</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
         <v>14</v>
@@ -1027,58 +1027,58 @@
         <v>34</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX2">
         <v>8</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB2">
         <v>15.5</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK2">
         <v>6</v>
@@ -1090,28 +1090,28 @@
         <v>11</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS2">
         <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1126,10 +1126,10 @@
         <v>10</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>100</v>
@@ -1152,79 +1152,79 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="G3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
         <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
         <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB3">
         <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AE3">
         <v>120</v>
@@ -1239,7 +1239,7 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ3">
         <v>30</v>
@@ -1251,13 +1251,13 @@
         <v>80</v>
       </c>
       <c r="AM3">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN3">
         <v>30</v>
       </c>
       <c r="AO3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
@@ -1266,55 +1266,55 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="AW3">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="AX3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>60</v>
       </c>
       <c r="BB3">
         <v>20</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
         <v>20</v>
       </c>
       <c r="BG3">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="BH3">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BI3">
         <v>2.46</v>
@@ -1323,55 +1323,55 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN3">
         <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BP3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1400,16 +1400,16 @@
         <v>17.5</v>
       </c>
       <c r="H4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I4">
         <v>1.28</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L4">
         <v>1.31</v>
@@ -1439,7 +1439,7 @@
         <v>2.26</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
         <v>4.5</v>
@@ -1454,13 +1454,13 @@
         <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>9.199999999999999</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AC4">
         <v>16.5</v>
@@ -1481,7 +1481,7 @@
         <v>48</v>
       </c>
       <c r="AI4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
@@ -1526,7 +1526,7 @@
         <v>11.5</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
         <v>6.8</v>
@@ -1538,22 +1538,22 @@
         <v>6.8</v>
       </c>
       <c r="BB4">
+        <v>7.8</v>
+      </c>
+      <c r="BC4">
         <v>7.6</v>
-      </c>
-      <c r="BC4">
-        <v>7.4</v>
       </c>
       <c r="BD4">
         <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BH4">
         <v>4.5</v>
@@ -1565,31 +1565,31 @@
         <v>15</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN4">
         <v>19</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
         <v>3.75</v>
@@ -1607,13 +1607,13 @@
         <v>27</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ4">
         <v>11</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB4" t="s">
         <v>100</v>
@@ -1636,70 +1636,70 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T5">
         <v>1.81</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AA5">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AB5">
         <v>9.4</v>
@@ -1708,154 +1708,154 @@
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS5">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>9.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE5">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
         <v>55</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI5">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
+        <v>3.25</v>
+      </c>
+      <c r="BP5">
+        <v>11.5</v>
+      </c>
+      <c r="BQ5">
         <v>3.35</v>
       </c>
-      <c r="BP5">
-        <v>13</v>
-      </c>
-      <c r="BQ5">
+      <c r="BR5">
+        <v>28</v>
+      </c>
+      <c r="BS5">
+        <v>4.1</v>
+      </c>
+      <c r="BT5">
+        <v>12.5</v>
+      </c>
+      <c r="BU5">
         <v>3.45</v>
       </c>
-      <c r="BR5">
-        <v>30</v>
-      </c>
-      <c r="BS5">
-        <v>4</v>
-      </c>
-      <c r="BT5">
-        <v>11.5</v>
-      </c>
-      <c r="BU5">
-        <v>3.35</v>
-      </c>
       <c r="BV5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BW5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY5">
         <v>4.4</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1878,22 +1878,22 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="I6">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="J6">
         <v>3.2</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L6">
         <v>1.53</v>
@@ -1905,199 +1905,199 @@
         <v>2.98</v>
       </c>
       <c r="O6">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P6">
         <v>1.64</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6">
         <v>4.8</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
         <v>1.92</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AG6">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ6">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AK6">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AL6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM6">
         <v>170</v>
       </c>
       <c r="AN6">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AO6">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AP6">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR6">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AT6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW6">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="AX6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="BB6">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BD6">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BG6">
-        <v>8.4</v>
+        <v>48</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK6">
         <v>4</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM6">
+        <v>6</v>
+      </c>
+      <c r="BN6">
         <v>5.9</v>
       </c>
-      <c r="BN6">
-        <v>6.4</v>
-      </c>
       <c r="BO6">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BQ6">
         <v>5</v>
       </c>
       <c r="BR6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BW6">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BX6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BZ6">
         <v>48</v>
       </c>
       <c r="CA6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 10:21:32</t>
+    <t>2026-10-01 12:35:32</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
         <v>1.75</v>
@@ -928,19 +928,19 @@
         <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O2">
         <v>1.48</v>
       </c>
       <c r="P2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q2">
         <v>2.46</v>
@@ -952,7 +952,7 @@
         <v>4.8</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
         <v>1.66</v>
@@ -970,67 +970,67 @@
         <v>17</v>
       </c>
       <c r="Z2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="AB2">
         <v>6.4</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AJ2">
+        <v>18.5</v>
+      </c>
+      <c r="AK2">
+        <v>24</v>
+      </c>
+      <c r="AL2">
+        <v>65</v>
+      </c>
+      <c r="AM2">
+        <v>260</v>
+      </c>
+      <c r="AN2">
         <v>19</v>
       </c>
-      <c r="AK2">
-        <v>25</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>220</v>
-      </c>
-      <c r="AN2">
-        <v>16.5</v>
-      </c>
       <c r="AO2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS2">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AT2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
@@ -1039,22 +1039,22 @@
         <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
         <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2">
         <v>70</v>
       </c>
       <c r="BB2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
         <v>20</v>
@@ -1063,40 +1063,40 @@
         <v>32</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>13</v>
       </c>
       <c r="BG2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH2">
         <v>2.92</v>
       </c>
       <c r="BI2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ2">
         <v>6.2</v>
@@ -1105,28 +1105,28 @@
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
         <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA2">
         <v>8.800000000000001</v>
@@ -1152,85 +1152,85 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R3">
         <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC3">
         <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3">
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG3">
         <v>12</v>
@@ -1239,91 +1239,91 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>80</v>
       </c>
       <c r="AM3">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AO3">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AT3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AX3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB3">
+        <v>18</v>
+      </c>
+      <c r="BC3">
         <v>20</v>
       </c>
-      <c r="BC3">
-        <v>21</v>
-      </c>
       <c r="BD3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
         <v>20</v>
       </c>
       <c r="BG3">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BH3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1332,16 +1332,16 @@
         <v>11</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1350,16 +1350,16 @@
         <v>9</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1394,16 +1394,16 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="H4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J4">
         <v>6.4</v>
@@ -1418,187 +1418,187 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S4">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AB4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AC4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF4">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AG4">
+        <v>65</v>
+      </c>
+      <c r="AH4">
         <v>60</v>
       </c>
-      <c r="AH4">
-        <v>48</v>
-      </c>
       <c r="AI4">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
       </c>
       <c r="AK4">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="AL4">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AM4">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC4">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI4">
         <v>3.3</v>
       </c>
       <c r="BJ4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>19</v>
       </c>
       <c r="BO4">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BU4">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BV4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BW4">
         <v>5</v>
@@ -1607,13 +1607,13 @@
         <v>27</v>
       </c>
       <c r="BY4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4">
         <v>11</v>
       </c>
       <c r="CA4">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="s">
         <v>100</v>
@@ -1636,61 +1636,61 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H5">
         <v>6.2</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y5">
         <v>25</v>
@@ -1699,10 +1699,10 @@
         <v>60</v>
       </c>
       <c r="AA5">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
@@ -1714,55 +1714,55 @@
         <v>80</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
         <v>21</v>
       </c>
       <c r="AR5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS5">
         <v>110</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5">
         <v>65</v>
@@ -1774,13 +1774,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA5">
         <v>65</v>
       </c>
       <c r="BB5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC5">
         <v>13.5</v>
@@ -1795,43 +1795,43 @@
         <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI5">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO5">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BR5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT5">
         <v>12.5</v>
@@ -1840,22 +1840,22 @@
         <v>3.45</v>
       </c>
       <c r="BV5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW5">
         <v>4.4</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY5">
         <v>4.4</v>
       </c>
       <c r="BZ5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1878,16 +1878,16 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J6">
         <v>3.2</v>
@@ -1902,13 +1902,13 @@
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P6">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q6">
         <v>2.46</v>
@@ -1917,19 +1917,19 @@
         <v>1.24</v>
       </c>
       <c r="S6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T6">
         <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1938,64 +1938,64 @@
         <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AA6">
         <v>75</v>
       </c>
       <c r="AB6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6">
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE6">
         <v>55</v>
       </c>
       <c r="AF6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL6">
         <v>65</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AO6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP6">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS6">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AT6">
         <v>7.8</v>
@@ -2004,49 +2004,49 @@
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AX6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6">
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>46</v>
+        <v>14.5</v>
       </c>
       <c r="BB6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BD6">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="BE6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BG6">
-        <v>48</v>
+        <v>14.5</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
         <v>4</v>
@@ -2055,49 +2055,49 @@
         <v>200</v>
       </c>
       <c r="BM6">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BN6">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR6">
         <v>46</v>
       </c>
       <c r="BS6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ6">
         <v>48</v>
       </c>
       <c r="CA6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 12:35:32</t>
+    <t>2026-10-01 14:51:46</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
         <v>1.69</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -925,7 +925,7 @@
         <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.57</v>
@@ -934,13 +934,13 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2">
         <v>2.46</v>
@@ -949,7 +949,7 @@
         <v>1.23</v>
       </c>
       <c r="S2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T2">
         <v>2.28</v>
@@ -958,10 +958,10 @@
         <v>1.66</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
         <v>10.5</v>
@@ -988,7 +988,7 @@
         <v>180</v>
       </c>
       <c r="AF2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -997,7 +997,7 @@
         <v>30</v>
       </c>
       <c r="AI2">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AJ2">
         <v>18.5</v>
@@ -1015,7 +1015,7 @@
         <v>19</v>
       </c>
       <c r="AO2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AP2">
         <v>8.6</v>
@@ -1027,10 +1027,10 @@
         <v>36</v>
       </c>
       <c r="AS2">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
@@ -1063,13 +1063,13 @@
         <v>32</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>13</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>2.92</v>
@@ -1093,7 +1093,7 @@
         <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
         <v>13</v>
@@ -1152,226 +1152,226 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
+        <v>1.95</v>
+      </c>
+      <c r="H3">
+        <v>4.2</v>
+      </c>
+      <c r="I3">
+        <v>4.7</v>
+      </c>
+      <c r="J3">
+        <v>3.85</v>
+      </c>
+      <c r="K3">
+        <v>4.2</v>
+      </c>
+      <c r="L3">
+        <v>1.38</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>4.3</v>
+      </c>
+      <c r="O3">
+        <v>1.26</v>
+      </c>
+      <c r="P3">
         <v>2.14</v>
       </c>
-      <c r="H3">
-        <v>4.4</v>
-      </c>
-      <c r="I3">
-        <v>4.9</v>
-      </c>
-      <c r="J3">
-        <v>3.15</v>
-      </c>
-      <c r="K3">
-        <v>3.35</v>
-      </c>
-      <c r="L3">
-        <v>1.57</v>
-      </c>
-      <c r="M3">
-        <v>1.13</v>
-      </c>
-      <c r="N3">
-        <v>2.62</v>
-      </c>
-      <c r="O3">
-        <v>1.53</v>
-      </c>
-      <c r="P3">
-        <v>1.53</v>
-      </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="S3">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA3">
         <v>160</v>
       </c>
       <c r="AB3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>19</v>
+      </c>
+      <c r="AE3">
+        <v>65</v>
+      </c>
+      <c r="AF3">
+        <v>13.5</v>
+      </c>
+      <c r="AG3">
+        <v>11</v>
+      </c>
+      <c r="AH3">
+        <v>19</v>
+      </c>
+      <c r="AI3">
+        <v>65</v>
+      </c>
+      <c r="AJ3">
+        <v>22</v>
+      </c>
+      <c r="AK3">
+        <v>20</v>
+      </c>
+      <c r="AL3">
+        <v>38</v>
+      </c>
+      <c r="AM3">
+        <v>95</v>
+      </c>
+      <c r="AN3">
+        <v>11</v>
+      </c>
+      <c r="AO3">
+        <v>55</v>
+      </c>
+      <c r="AP3">
+        <v>15.5</v>
+      </c>
+      <c r="AQ3">
+        <v>15.5</v>
+      </c>
+      <c r="AR3">
         <v>7.8</v>
       </c>
-      <c r="AD3">
-        <v>21</v>
-      </c>
-      <c r="AE3">
-        <v>120</v>
-      </c>
-      <c r="AF3">
-        <v>12</v>
-      </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>34</v>
-      </c>
-      <c r="AI3">
-        <v>160</v>
-      </c>
-      <c r="AJ3">
-        <v>34</v>
-      </c>
-      <c r="AK3">
-        <v>32</v>
-      </c>
-      <c r="AL3">
-        <v>80</v>
-      </c>
-      <c r="AM3">
-        <v>250</v>
-      </c>
-      <c r="AN3">
-        <v>42</v>
-      </c>
-      <c r="AO3">
-        <v>240</v>
-      </c>
-      <c r="AP3">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
-        <v>23</v>
-      </c>
       <c r="AS3">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="AT3">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
+        <v>15.5</v>
+      </c>
+      <c r="BA3">
+        <v>40</v>
+      </c>
+      <c r="BB3">
+        <v>17</v>
+      </c>
+      <c r="BC3">
+        <v>16</v>
+      </c>
+      <c r="BD3">
+        <v>18</v>
+      </c>
+      <c r="BE3">
+        <v>8.4</v>
+      </c>
+      <c r="BF3">
+        <v>9</v>
+      </c>
+      <c r="BG3">
+        <v>20</v>
+      </c>
+      <c r="BH3">
+        <v>3.95</v>
+      </c>
+      <c r="BI3">
+        <v>3.3</v>
+      </c>
+      <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
-      <c r="BA3">
-        <v>55</v>
-      </c>
-      <c r="BB3">
-        <v>18</v>
-      </c>
-      <c r="BC3">
-        <v>20</v>
-      </c>
-      <c r="BD3">
-        <v>36</v>
-      </c>
-      <c r="BE3">
-        <v>10.5</v>
-      </c>
-      <c r="BF3">
-        <v>20</v>
-      </c>
-      <c r="BG3">
-        <v>75</v>
-      </c>
-      <c r="BH3">
-        <v>2.8</v>
-      </c>
-      <c r="BI3">
-        <v>2.44</v>
-      </c>
-      <c r="BJ3">
-        <v>12</v>
-      </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BQ3">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA3">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1397,19 +1397,19 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>1.24</v>
       </c>
       <c r="I4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="J4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L4">
         <v>1.31</v>
@@ -1421,28 +1421,28 @@
         <v>5.3</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q4">
         <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
         <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="W4">
         <v>1.05</v>
@@ -1451,16 +1451,16 @@
         <v>27</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>8.6</v>
       </c>
       <c r="AB4">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AC4">
         <v>17</v>
@@ -1475,10 +1475,10 @@
         <v>210</v>
       </c>
       <c r="AG4">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI4">
         <v>60</v>
@@ -1493,79 +1493,79 @@
         <v>290</v>
       </c>
       <c r="AM4">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AP4">
         <v>18.5</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR4">
         <v>6.4</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT4">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AU4">
         <v>14</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
         <v>12</v>
       </c>
       <c r="AX4">
+        <v>9</v>
+      </c>
+      <c r="AY4">
+        <v>8.4</v>
+      </c>
+      <c r="AZ4">
         <v>8.6</v>
       </c>
-      <c r="AY4">
-        <v>7.8</v>
-      </c>
-      <c r="AZ4">
-        <v>7.8</v>
-      </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD4">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BH4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
         <v>15.5</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1574,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="BN4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BO4">
         <v>6.8</v>
@@ -1589,7 +1589,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT4">
         <v>3.65</v>
@@ -1598,10 +1598,10 @@
         <v>2.82</v>
       </c>
       <c r="BV4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BW4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX4">
         <v>27</v>
@@ -1610,10 +1610,10 @@
         <v>7.6</v>
       </c>
       <c r="BZ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB4" t="s">
         <v>100</v>
@@ -1636,19 +1636,19 @@
         <v>98</v>
       </c>
       <c r="F5">
+        <v>1.54</v>
+      </c>
+      <c r="G5">
         <v>1.56</v>
       </c>
-      <c r="G5">
-        <v>1.58</v>
-      </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -1660,76 +1660,76 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S5">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X5">
         <v>21</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z5">
         <v>60</v>
       </c>
       <c r="AA5">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AF5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
@@ -1738,28 +1738,28 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR5">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AS5">
         <v>110</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV5">
         <v>22</v>
@@ -1774,7 +1774,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
         <v>65</v>
@@ -1792,19 +1792,19 @@
         <v>70</v>
       </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG5">
         <v>65</v>
       </c>
       <c r="BH5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
         <v>3.4</v>
@@ -1819,13 +1819,13 @@
         <v>5</v>
       </c>
       <c r="BO5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BR5">
         <v>27</v>
@@ -1837,22 +1837,22 @@
         <v>12.5</v>
       </c>
       <c r="BU5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BV5">
         <v>65</v>
       </c>
       <c r="BW5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX5">
         <v>65</v>
       </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA5">
         <v>3.7</v>
@@ -1878,25 +1878,25 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G6">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
         <v>3.2</v>
       </c>
       <c r="K6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M6">
         <v>1.11</v>
@@ -1914,7 +1914,7 @@
         <v>2.46</v>
       </c>
       <c r="R6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
         <v>4.9</v>
@@ -1926,10 +1926,10 @@
         <v>1.93</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1938,25 +1938,25 @@
         <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB6">
         <v>8.199999999999999</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
         <v>55</v>
       </c>
       <c r="AF6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -1965,28 +1965,28 @@
         <v>22</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AJ6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK6">
         <v>32</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO6">
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>28</v>
       </c>
       <c r="AT6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
@@ -2022,22 +2022,22 @@
         <v>14.5</v>
       </c>
       <c r="BB6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BE6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BF6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG6">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
@@ -2049,7 +2049,7 @@
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL6">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>7.6</v>
       </c>
       <c r="BU6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV6">
         <v>38</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 14:51:46</t>
+    <t>2026-10-01 17:07:53</t>
   </si>
 </sst>
 </file>
@@ -913,94 +913,94 @@
         <v>1.69</v>
       </c>
       <c r="G2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
         <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O2">
         <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U2">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
         <v>10.5</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB2">
         <v>6.4</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="AF2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="AJ2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK2">
         <v>24</v>
@@ -1012,13 +1012,13 @@
         <v>260</v>
       </c>
       <c r="AN2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
         <v>13.5</v>
@@ -1027,25 +1027,25 @@
         <v>36</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>130</v>
       </c>
       <c r="AT2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AW2">
         <v>65</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
         <v>24</v>
@@ -1060,76 +1060,76 @@
         <v>20</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>130</v>
       </c>
       <c r="BF2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>130</v>
       </c>
       <c r="BH2">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP2">
         <v>13</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>34</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>100</v>
@@ -1152,52 +1152,52 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
         <v>4.7</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>4.3</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P3">
+        <v>2.1</v>
+      </c>
+      <c r="Q3">
+        <v>1.87</v>
+      </c>
+      <c r="R3">
+        <v>1.42</v>
+      </c>
+      <c r="S3">
+        <v>3.15</v>
+      </c>
+      <c r="T3">
+        <v>1.8</v>
+      </c>
+      <c r="U3">
         <v>2.14</v>
-      </c>
-      <c r="Q3">
-        <v>1.8</v>
-      </c>
-      <c r="R3">
-        <v>1.45</v>
-      </c>
-      <c r="S3">
-        <v>2.96</v>
-      </c>
-      <c r="T3">
-        <v>1.7</v>
-      </c>
-      <c r="U3">
-        <v>2.2</v>
       </c>
       <c r="V3">
         <v>1.27</v>
@@ -1206,172 +1206,172 @@
         <v>2.06</v>
       </c>
       <c r="X3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>22</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM3">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AN3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
+        <v>27</v>
+      </c>
+      <c r="AS3">
+        <v>60</v>
+      </c>
+      <c r="AT3">
+        <v>8.6</v>
+      </c>
+      <c r="AU3">
         <v>7.8</v>
-      </c>
-      <c r="AS3">
-        <v>9</v>
-      </c>
-      <c r="AT3">
-        <v>9.4</v>
-      </c>
-      <c r="AU3">
-        <v>8</v>
       </c>
       <c r="AV3">
         <v>15</v>
       </c>
       <c r="AW3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB3">
+        <v>18.5</v>
+      </c>
+      <c r="BC3">
         <v>17</v>
       </c>
-      <c r="BC3">
-        <v>16</v>
-      </c>
       <c r="BD3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BE3">
-        <v>8.4</v>
+        <v>65</v>
       </c>
       <c r="BF3">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BH3">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
         <v>3.3</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU3">
         <v>6.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW3">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1394,22 +1394,22 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H4">
         <v>1.24</v>
       </c>
       <c r="I4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="J4">
         <v>6.6</v>
       </c>
       <c r="K4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L4">
         <v>1.31</v>
@@ -1418,202 +1418,202 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
         <v>1.58</v>
       </c>
       <c r="S4">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U4">
         <v>1.61</v>
       </c>
       <c r="V4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W4">
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AC4">
+        <v>16</v>
+      </c>
+      <c r="AD4">
+        <v>12.5</v>
+      </c>
+      <c r="AE4">
+        <v>15.5</v>
+      </c>
+      <c r="AF4">
+        <v>180</v>
+      </c>
+      <c r="AG4">
+        <v>65</v>
+      </c>
+      <c r="AH4">
+        <v>40</v>
+      </c>
+      <c r="AI4">
+        <v>50</v>
+      </c>
+      <c r="AJ4">
+        <v>990</v>
+      </c>
+      <c r="AK4">
+        <v>390</v>
+      </c>
+      <c r="AL4">
+        <v>270</v>
+      </c>
+      <c r="AM4">
+        <v>290</v>
+      </c>
+      <c r="AN4">
+        <v>500</v>
+      </c>
+      <c r="AO4">
+        <v>4.3</v>
+      </c>
+      <c r="AP4">
+        <v>17.5</v>
+      </c>
+      <c r="AQ4">
+        <v>8.4</v>
+      </c>
+      <c r="AR4">
+        <v>6.8</v>
+      </c>
+      <c r="AS4">
+        <v>8</v>
+      </c>
+      <c r="AT4">
+        <v>34</v>
+      </c>
+      <c r="AU4">
+        <v>13.5</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>12.5</v>
+      </c>
+      <c r="AX4">
+        <v>16.5</v>
+      </c>
+      <c r="AY4">
+        <v>46</v>
+      </c>
+      <c r="AZ4">
+        <v>32</v>
+      </c>
+      <c r="BA4">
+        <v>12.5</v>
+      </c>
+      <c r="BB4">
+        <v>13</v>
+      </c>
+      <c r="BC4">
+        <v>12.5</v>
+      </c>
+      <c r="BD4">
+        <v>14</v>
+      </c>
+      <c r="BE4">
         <v>17</v>
       </c>
-      <c r="AD4">
-        <v>14</v>
-      </c>
-      <c r="AE4">
-        <v>15</v>
-      </c>
-      <c r="AF4">
-        <v>210</v>
-      </c>
-      <c r="AG4">
-        <v>950</v>
-      </c>
-      <c r="AH4">
-        <v>50</v>
-      </c>
-      <c r="AI4">
-        <v>60</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>410</v>
-      </c>
-      <c r="AL4">
-        <v>290</v>
-      </c>
-      <c r="AM4">
-        <v>310</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>4.2</v>
-      </c>
-      <c r="AP4">
-        <v>18.5</v>
-      </c>
-      <c r="AQ4">
-        <v>8</v>
-      </c>
-      <c r="AR4">
-        <v>6.4</v>
-      </c>
-      <c r="AS4">
-        <v>7.2</v>
-      </c>
-      <c r="AT4">
-        <v>38</v>
-      </c>
-      <c r="AU4">
-        <v>14</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>12</v>
-      </c>
-      <c r="AX4">
-        <v>9</v>
-      </c>
-      <c r="AY4">
-        <v>8.4</v>
-      </c>
-      <c r="AZ4">
-        <v>8.6</v>
-      </c>
-      <c r="BA4">
-        <v>8.4</v>
-      </c>
-      <c r="BB4">
-        <v>9.4</v>
-      </c>
-      <c r="BC4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE4">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF4">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BG4">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BH4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI4">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BJ4">
         <v>15.5</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4">
         <v>19.5</v>
       </c>
       <c r="BO4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>3.65</v>
       </c>
       <c r="BU4">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="BV4">
         <v>6.8</v>
       </c>
       <c r="BW4">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BX4">
         <v>27</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
         <v>10.5</v>
       </c>
       <c r="CA4">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="s">
         <v>100</v>
@@ -1636,13 +1636,13 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1651,10 +1651,10 @@
         <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1663,7 +1663,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
         <v>2.34</v>
@@ -1672,13 +1672,13 @@
         <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
         <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U5">
         <v>2.12</v>
@@ -1687,31 +1687,31 @@
         <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="X5">
         <v>21</v>
       </c>
       <c r="Y5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF5">
         <v>9.6</v>
@@ -1723,7 +1723,7 @@
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>14.5</v>
@@ -1732,16 +1732,16 @@
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP5">
         <v>18.5</v>
@@ -1756,7 +1756,7 @@
         <v>110</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -1765,97 +1765,97 @@
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
         <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB5">
         <v>13.5</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD5">
         <v>28</v>
       </c>
       <c r="BE5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF5">
         <v>6.4</v>
       </c>
       <c r="BG5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN5">
         <v>5</v>
       </c>
       <c r="BO5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
         <v>27</v>
       </c>
       <c r="BS5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BX5">
         <v>65</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
         <v>17.5</v>
       </c>
       <c r="CA5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1878,16 +1878,16 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6">
         <v>3.2</v>
@@ -1926,19 +1926,19 @@
         <v>1.93</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA6">
         <v>80</v>
@@ -1956,7 +1956,7 @@
         <v>55</v>
       </c>
       <c r="AF6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -1965,7 +1965,7 @@
         <v>22</v>
       </c>
       <c r="AI6">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>34</v>
@@ -1980,10 +1980,10 @@
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP6">
         <v>9</v>
@@ -1992,13 +1992,13 @@
         <v>10</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
@@ -2007,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="AW6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX6">
         <v>12.5</v>
@@ -2019,7 +2019,7 @@
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB6">
         <v>29</v>
@@ -2028,19 +2028,19 @@
         <v>27</v>
       </c>
       <c r="BD6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG6">
         <v>25</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BI6">
         <v>2.66</v>
@@ -2049,55 +2049,55 @@
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL6">
         <v>200</v>
       </c>
       <c r="BM6">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BN6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO6">
         <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ6">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BR6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS6">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BT6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
         <v>5.9</v>
       </c>
       <c r="BV6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW6">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CA6">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-01.xlsx
@@ -316,7 +316,7 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>2026-10-01 17:07:53</t>
+    <t>2026-10-01 19:24:15</t>
   </si>
 </sst>
 </file>
@@ -910,226 +910,226 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>11.5</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>1.24</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>1.26</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="N2">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>50</v>
       </c>
       <c r="P2">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>150</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>4.9</v>
+        <v>180</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>17</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>1.28</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2">
+        <v>190</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>13.5</v>
+      </c>
+      <c r="AC2">
+        <v>110</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>970</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.26</v>
+      </c>
+      <c r="AQ2">
+        <v>7.8</v>
+      </c>
+      <c r="AR2">
+        <v>85</v>
+      </c>
+      <c r="AS2">
+        <v>200</v>
+      </c>
+      <c r="AT2">
+        <v>11.5</v>
+      </c>
+      <c r="AU2">
+        <v>70</v>
+      </c>
+      <c r="AV2">
+        <v>240</v>
+      </c>
+      <c r="AW2">
         <v>55</v>
       </c>
-      <c r="AA2">
-        <v>290</v>
-      </c>
-      <c r="AB2">
-        <v>6.4</v>
-      </c>
-      <c r="AC2">
-        <v>9</v>
-      </c>
-      <c r="AD2">
-        <v>28</v>
-      </c>
-      <c r="AE2">
-        <v>280</v>
-      </c>
-      <c r="AF2">
-        <v>9</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>390</v>
-      </c>
-      <c r="AJ2">
-        <v>18</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-      <c r="AL2">
+      <c r="AX2">
+        <v>210</v>
+      </c>
+      <c r="AY2">
+        <v>200</v>
+      </c>
+      <c r="AZ2">
+        <v>55</v>
+      </c>
+      <c r="BA2">
+        <v>55</v>
+      </c>
+      <c r="BB2">
+        <v>55</v>
+      </c>
+      <c r="BC2">
+        <v>120</v>
+      </c>
+      <c r="BD2">
+        <v>55</v>
+      </c>
+      <c r="BE2">
+        <v>55</v>
+      </c>
+      <c r="BF2">
         <v>65</v>
       </c>
-      <c r="AM2">
-        <v>260</v>
-      </c>
-      <c r="AN2">
-        <v>16.5</v>
-      </c>
-      <c r="AO2">
-        <v>310</v>
-      </c>
-      <c r="AP2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ2">
-        <v>13.5</v>
-      </c>
-      <c r="AR2">
-        <v>36</v>
-      </c>
-      <c r="AS2">
-        <v>130</v>
-      </c>
-      <c r="AT2">
-        <v>5.8</v>
-      </c>
-      <c r="AU2">
-        <v>7.8</v>
-      </c>
-      <c r="AV2">
-        <v>23</v>
-      </c>
-      <c r="AW2">
+      <c r="BG2">
         <v>65</v>
       </c>
-      <c r="AX2">
-        <v>7.8</v>
-      </c>
-      <c r="AY2">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2">
-        <v>24</v>
-      </c>
-      <c r="BA2">
-        <v>70</v>
-      </c>
-      <c r="BB2">
-        <v>15</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>36</v>
-      </c>
-      <c r="BE2">
-        <v>130</v>
-      </c>
-      <c r="BF2">
-        <v>13.5</v>
-      </c>
-      <c r="BG2">
-        <v>130</v>
-      </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>100</v>
@@ -1155,223 +1155,223 @@
         <v>1.86</v>
       </c>
       <c r="G3">
-        <v>1.94</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>1.07</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>1.78</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>960</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O3">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="R3">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="T3">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR3">
-        <v>27</v>
+        <v>1.05</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>1.05</v>
       </c>
       <c r="AT3">
+        <v>1.05</v>
+      </c>
+      <c r="AU3">
         <v>8.6</v>
       </c>
-      <c r="AU3">
-        <v>7.8</v>
-      </c>
       <c r="AV3">
-        <v>15</v>
+        <v>1.05</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>1.05</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>1.05</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>1.05</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>1.05</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>1.05</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>1.05</v>
       </c>
       <c r="BE3">
-        <v>65</v>
+        <v>1.05</v>
       </c>
       <c r="BF3">
-        <v>9.800000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>1.05</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>100</v>
@@ -1394,226 +1394,226 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>14.5</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="I4">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="J4">
-        <v>6.6</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>3.6</v>
+      </c>
+      <c r="S4">
+        <v>1.38</v>
+      </c>
+      <c r="T4">
         <v>5.1</v>
       </c>
-      <c r="O4">
-        <v>1.22</v>
-      </c>
-      <c r="P4">
-        <v>2.46</v>
-      </c>
-      <c r="Q4">
-        <v>1.65</v>
-      </c>
-      <c r="R4">
-        <v>1.58</v>
-      </c>
-      <c r="S4">
-        <v>2.64</v>
-      </c>
-      <c r="T4">
-        <v>2.34</v>
-      </c>
       <c r="U4">
+        <v>1.2</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>3.8</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>18.5</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
         <v>1.61</v>
       </c>
-      <c r="V4">
-        <v>4.7</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>22</v>
-      </c>
-      <c r="Y4">
-        <v>9.6</v>
-      </c>
-      <c r="Z4">
-        <v>8</v>
-      </c>
-      <c r="AA4">
-        <v>9</v>
-      </c>
-      <c r="AB4">
-        <v>48</v>
-      </c>
-      <c r="AC4">
+      <c r="AP4">
+        <v>46</v>
+      </c>
+      <c r="AQ4">
+        <v>42</v>
+      </c>
+      <c r="AR4">
+        <v>42</v>
+      </c>
+      <c r="AS4">
+        <v>3.7</v>
+      </c>
+      <c r="AT4">
+        <v>42</v>
+      </c>
+      <c r="AU4">
+        <v>46</v>
+      </c>
+      <c r="AV4">
+        <v>42</v>
+      </c>
+      <c r="AW4">
+        <v>15</v>
+      </c>
+      <c r="AX4">
+        <v>130</v>
+      </c>
+      <c r="AY4">
+        <v>130</v>
+      </c>
+      <c r="AZ4">
+        <v>140</v>
+      </c>
+      <c r="BA4">
         <v>16</v>
       </c>
-      <c r="AD4">
-        <v>12.5</v>
-      </c>
-      <c r="AE4">
-        <v>15.5</v>
-      </c>
-      <c r="AF4">
-        <v>180</v>
-      </c>
-      <c r="AG4">
-        <v>65</v>
-      </c>
-      <c r="AH4">
-        <v>40</v>
-      </c>
-      <c r="AI4">
+      <c r="BB4">
+        <v>90</v>
+      </c>
+      <c r="BC4">
+        <v>90</v>
+      </c>
+      <c r="BD4">
+        <v>90</v>
+      </c>
+      <c r="BE4">
+        <v>18</v>
+      </c>
+      <c r="BF4">
         <v>50</v>
       </c>
-      <c r="AJ4">
-        <v>990</v>
-      </c>
-      <c r="AK4">
-        <v>390</v>
-      </c>
-      <c r="AL4">
-        <v>270</v>
-      </c>
-      <c r="AM4">
-        <v>290</v>
-      </c>
-      <c r="AN4">
-        <v>500</v>
-      </c>
-      <c r="AO4">
-        <v>4.3</v>
-      </c>
-      <c r="AP4">
-        <v>17.5</v>
-      </c>
-      <c r="AQ4">
-        <v>8.4</v>
-      </c>
-      <c r="AR4">
-        <v>6.8</v>
-      </c>
-      <c r="AS4">
-        <v>8</v>
-      </c>
-      <c r="AT4">
-        <v>34</v>
-      </c>
-      <c r="AU4">
-        <v>13.5</v>
-      </c>
-      <c r="AV4">
-        <v>11.5</v>
-      </c>
-      <c r="AW4">
-        <v>12.5</v>
-      </c>
-      <c r="AX4">
-        <v>16.5</v>
-      </c>
-      <c r="AY4">
-        <v>46</v>
-      </c>
-      <c r="AZ4">
-        <v>32</v>
-      </c>
-      <c r="BA4">
-        <v>12.5</v>
-      </c>
-      <c r="BB4">
-        <v>13</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
-      </c>
-      <c r="BD4">
-        <v>14</v>
-      </c>
-      <c r="BE4">
-        <v>17</v>
-      </c>
-      <c r="BF4">
-        <v>14.5</v>
-      </c>
       <c r="BG4">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="BH4">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>100</v>
@@ -1636,226 +1636,226 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="G5">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="H5">
+        <v>11.5</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>6.8</v>
+      </c>
+      <c r="K5">
+        <v>7.4</v>
+      </c>
+      <c r="L5">
+        <v>1.36</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>5.4</v>
+      </c>
+      <c r="O5">
+        <v>1.21</v>
+      </c>
+      <c r="P5">
+        <v>2.36</v>
+      </c>
+      <c r="Q5">
+        <v>1.72</v>
+      </c>
+      <c r="R5">
+        <v>1.63</v>
+      </c>
+      <c r="S5">
+        <v>2.58</v>
+      </c>
+      <c r="T5">
+        <v>2.08</v>
+      </c>
+      <c r="U5">
+        <v>1.77</v>
+      </c>
+      <c r="V5">
+        <v>1.08</v>
+      </c>
+      <c r="W5">
+        <v>4.3</v>
+      </c>
+      <c r="X5">
+        <v>25</v>
+      </c>
+      <c r="Y5">
+        <v>42</v>
+      </c>
+      <c r="Z5">
+        <v>150</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>9.4</v>
+      </c>
+      <c r="AC5">
+        <v>16.5</v>
+      </c>
+      <c r="AD5">
+        <v>60</v>
+      </c>
+      <c r="AE5">
+        <v>270</v>
+      </c>
+      <c r="AF5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>50</v>
+      </c>
+      <c r="AI5">
+        <v>250</v>
+      </c>
+      <c r="AJ5">
+        <v>9.4</v>
+      </c>
+      <c r="AK5">
+        <v>16</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>290</v>
+      </c>
+      <c r="AN5">
+        <v>4.7</v>
+      </c>
+      <c r="AO5">
+        <v>430</v>
+      </c>
+      <c r="AP5">
+        <v>21</v>
+      </c>
+      <c r="AQ5">
+        <v>32</v>
+      </c>
+      <c r="AR5">
+        <v>100</v>
+      </c>
+      <c r="AS5">
+        <v>220</v>
+      </c>
+      <c r="AT5">
+        <v>7.8</v>
+      </c>
+      <c r="AU5">
+        <v>13.5</v>
+      </c>
+      <c r="AV5">
+        <v>42</v>
+      </c>
+      <c r="AW5">
+        <v>130</v>
+      </c>
+      <c r="AX5">
         <v>6.6</v>
       </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>4.7</v>
-      </c>
-      <c r="K5">
-        <v>5.1</v>
-      </c>
-      <c r="L5">
-        <v>1.33</v>
-      </c>
-      <c r="M5">
-        <v>1.05</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>1.24</v>
-      </c>
-      <c r="P5">
-        <v>2.34</v>
-      </c>
-      <c r="Q5">
-        <v>1.71</v>
-      </c>
-      <c r="R5">
-        <v>1.53</v>
-      </c>
-      <c r="S5">
-        <v>2.72</v>
-      </c>
-      <c r="T5">
-        <v>1.85</v>
-      </c>
-      <c r="U5">
-        <v>2.12</v>
-      </c>
-      <c r="V5">
-        <v>1.16</v>
-      </c>
-      <c r="W5">
-        <v>2.84</v>
-      </c>
-      <c r="X5">
-        <v>21</v>
-      </c>
-      <c r="Y5">
-        <v>26</v>
-      </c>
-      <c r="Z5">
-        <v>65</v>
-      </c>
-      <c r="AA5">
-        <v>210</v>
-      </c>
-      <c r="AB5">
-        <v>9.6</v>
-      </c>
-      <c r="AC5">
-        <v>11</v>
-      </c>
-      <c r="AD5">
-        <v>26</v>
-      </c>
-      <c r="AE5">
-        <v>95</v>
-      </c>
-      <c r="AF5">
-        <v>9.6</v>
-      </c>
-      <c r="AG5">
+      <c r="AY5">
         <v>10.5</v>
       </c>
-      <c r="AH5">
-        <v>22</v>
-      </c>
-      <c r="AI5">
-        <v>85</v>
-      </c>
-      <c r="AJ5">
-        <v>14.5</v>
-      </c>
-      <c r="AK5">
-        <v>14.5</v>
-      </c>
-      <c r="AL5">
-        <v>30</v>
-      </c>
-      <c r="AM5">
-        <v>110</v>
-      </c>
-      <c r="AN5">
-        <v>7.2</v>
-      </c>
-      <c r="AO5">
-        <v>95</v>
-      </c>
-      <c r="AP5">
-        <v>18.5</v>
-      </c>
-      <c r="AQ5">
-        <v>22</v>
-      </c>
-      <c r="AR5">
-        <v>50</v>
-      </c>
-      <c r="AS5">
-        <v>110</v>
-      </c>
-      <c r="AT5">
-        <v>9</v>
-      </c>
-      <c r="AU5">
-        <v>10</v>
-      </c>
-      <c r="AV5">
-        <v>22</v>
-      </c>
-      <c r="AW5">
-        <v>70</v>
-      </c>
-      <c r="AX5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY5">
-        <v>9.4</v>
-      </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BA5">
         <v>60</v>
       </c>
       <c r="BB5">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5">
+        <v>14</v>
+      </c>
+      <c r="BD5">
+        <v>40</v>
+      </c>
+      <c r="BE5">
+        <v>120</v>
+      </c>
+      <c r="BF5">
+        <v>4.2</v>
+      </c>
+      <c r="BG5">
+        <v>9.4</v>
+      </c>
+      <c r="BH5">
+        <v>3.9</v>
+      </c>
+      <c r="BI5">
+        <v>3.35</v>
+      </c>
+      <c r="BJ5">
+        <v>14</v>
+      </c>
+      <c r="BK5">
+        <v>12.5</v>
+      </c>
+      <c r="BL5">
+        <v>960</v>
+      </c>
+      <c r="BM5">
+        <v>11</v>
+      </c>
+      <c r="BN5">
+        <v>3.55</v>
+      </c>
+      <c r="BO5">
+        <v>3.25</v>
+      </c>
+      <c r="BP5">
+        <v>7.2</v>
+      </c>
+      <c r="BQ5">
+        <v>6.2</v>
+      </c>
+      <c r="BR5">
+        <v>38</v>
+      </c>
+      <c r="BS5">
+        <v>19</v>
+      </c>
+      <c r="BT5">
+        <v>14</v>
+      </c>
+      <c r="BU5">
+        <v>12</v>
+      </c>
+      <c r="BV5">
+        <v>160</v>
+      </c>
+      <c r="BW5">
         <v>13</v>
       </c>
-      <c r="BD5">
-        <v>28</v>
-      </c>
-      <c r="BE5">
-        <v>75</v>
-      </c>
-      <c r="BF5">
-        <v>6.4</v>
-      </c>
-      <c r="BG5">
-        <v>70</v>
-      </c>
-      <c r="BH5">
-        <v>4.7</v>
-      </c>
-      <c r="BI5">
-        <v>3.7</v>
-      </c>
-      <c r="BJ5">
-        <v>12</v>
-      </c>
-      <c r="BK5">
-        <v>3.45</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>4.7</v>
-      </c>
-      <c r="BN5">
-        <v>5</v>
-      </c>
-      <c r="BO5">
-        <v>3.9</v>
-      </c>
-      <c r="BP5">
+      <c r="BX5">
+        <v>130</v>
+      </c>
+      <c r="BY5">
         <v>11.5</v>
       </c>
-      <c r="BQ5">
-        <v>7.2</v>
-      </c>
-      <c r="BR5">
-        <v>27</v>
-      </c>
-      <c r="BS5">
-        <v>4.1</v>
-      </c>
-      <c r="BT5">
-        <v>12</v>
-      </c>
-      <c r="BU5">
-        <v>3.45</v>
-      </c>
-      <c r="BV5">
-        <v>60</v>
-      </c>
-      <c r="BW5">
-        <v>4.5</v>
-      </c>
-      <c r="BX5">
-        <v>65</v>
-      </c>
-      <c r="BY5">
-        <v>4.5</v>
-      </c>
       <c r="BZ5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA5">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
         <v>100</v>
@@ -1878,16 +1878,16 @@
         <v>99</v>
       </c>
       <c r="F6">
+        <v>2.26</v>
+      </c>
+      <c r="G6">
         <v>2.34</v>
       </c>
-      <c r="G6">
-        <v>2.38</v>
-      </c>
       <c r="H6">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I6">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
         <v>3.2</v>
@@ -1896,61 +1896,61 @@
         <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P6">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE6">
         <v>55</v>
@@ -1959,34 +1959,34 @@
         <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6">
         <v>10</v>
@@ -1995,13 +1995,13 @@
         <v>21</v>
       </c>
       <c r="AS6">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>14</v>
@@ -2010,94 +2010,94 @@
         <v>46</v>
       </c>
       <c r="AX6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BC6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD6">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BE6">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="BF6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BG6">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="BH6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BI6">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL6">
         <v>200</v>
       </c>
       <c r="BM6">
+        <v>140</v>
+      </c>
+      <c r="BN6">
+        <v>4.9</v>
+      </c>
+      <c r="BO6">
+        <v>4.4</v>
+      </c>
+      <c r="BP6">
+        <v>21</v>
+      </c>
+      <c r="BQ6">
         <v>7.4</v>
-      </c>
-      <c r="BN6">
-        <v>5.6</v>
-      </c>
-      <c r="BO6">
-        <v>4.5</v>
-      </c>
-      <c r="BP6">
-        <v>22</v>
-      </c>
-      <c r="BQ6">
-        <v>5.7</v>
       </c>
       <c r="BR6">
         <v>44</v>
       </c>
       <c r="BS6">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV6">
         <v>40</v>
       </c>
       <c r="BW6">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="CA6">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>100</v>
